--- a/Infosys.xlsx
+++ b/Infosys.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2855141d0bd7c7e8/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2855141d0bd7c7e8/Desktop/Finance Analytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1994" documentId="8_{516AF91F-FBEC-4432-867B-25B2131D13D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81D0742F-E689-431A-AEBE-4BCE4F51CB4D}"/>
+  <xr:revisionPtr revIDLastSave="2010" documentId="8_{516AF91F-FBEC-4432-867B-25B2131D13D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{009D4A26-D3D4-43B8-A6F0-D8924979AC28}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" tabRatio="828" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" tabRatio="828" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Sheet" sheetId="6" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="562">
   <si>
     <t>COMPANY NAME</t>
   </si>
@@ -341,12 +341,6 @@
     <t>% Other Expenses</t>
   </si>
   <si>
-    <t>Total Shareholer's Funds</t>
-  </si>
-  <si>
-    <t>Shareholder's Funds</t>
-  </si>
-  <si>
     <t>Current Liabilities</t>
   </si>
   <si>
@@ -1734,6 +1728,15 @@
   </si>
   <si>
     <t>&gt;</t>
+  </si>
+  <si>
+    <t>Reuturn on Invested Capital Employed</t>
+  </si>
+  <si>
+    <t>Shareholders Funds</t>
+  </si>
+  <si>
+    <t>Total Shareholers Funds</t>
   </si>
 </sst>
 </file>
@@ -3231,19 +3234,21 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3273,8 +3278,6 @@
     <xf numFmtId="166" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Accent6" xfId="3" builtinId="49"/>
@@ -5821,7 +5824,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B11" s="45" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C11" s="40">
         <f>SUM(C10,C9,C4,)</f>
@@ -6174,7 +6177,7 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B22" s="45" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C22" s="40">
         <f>SUM(C14:C21)</f>
@@ -6422,7 +6425,7 @@
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B30" s="45" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C30" s="40">
         <f>SUM(C25:C29)</f>
@@ -6610,25 +6613,25 @@
       <c r="A1" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="260" t="str">
+      <c r="B1" s="261" t="str">
         <f>"Income Statement for "&amp;'Data Sheet'!B1</f>
         <v>Income Statement for INFOSYS LTD</v>
       </c>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
-      <c r="N1" s="260"/>
-      <c r="O1" s="260"/>
-      <c r="P1" s="260"/>
-      <c r="Q1" s="260"/>
+      <c r="C1" s="261"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="261"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="261"/>
+      <c r="O1" s="261"/>
+      <c r="P1" s="261"/>
+      <c r="Q1" s="261"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A2" s="14"/>
@@ -7968,29 +7971,29 @@
       <c r="A27" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="260" t="str">
+      <c r="B27" s="261" t="str">
         <f>"Balance Sheet For "&amp;'Data Sheet'!B1</f>
         <v>Balance Sheet For INFOSYS LTD</v>
       </c>
-      <c r="C27" s="260"/>
-      <c r="D27" s="260"/>
-      <c r="E27" s="260"/>
-      <c r="F27" s="260"/>
-      <c r="G27" s="260"/>
-      <c r="H27" s="260"/>
-      <c r="I27" s="260"/>
-      <c r="J27" s="260"/>
-      <c r="K27" s="260"/>
-      <c r="L27" s="260"/>
-      <c r="M27" s="260"/>
-      <c r="N27" s="260"/>
-      <c r="O27" s="260"/>
-      <c r="P27" s="260"/>
-      <c r="Q27" s="260"/>
+      <c r="C27" s="261"/>
+      <c r="D27" s="261"/>
+      <c r="E27" s="261"/>
+      <c r="F27" s="261"/>
+      <c r="G27" s="261"/>
+      <c r="H27" s="261"/>
+      <c r="I27" s="261"/>
+      <c r="J27" s="261"/>
+      <c r="K27" s="261"/>
+      <c r="L27" s="261"/>
+      <c r="M27" s="261"/>
+      <c r="N27" s="261"/>
+      <c r="O27" s="261"/>
+      <c r="P27" s="261"/>
+      <c r="Q27" s="261"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.45">
       <c r="B28" s="12" t="s">
-        <v>97</v>
+        <v>560</v>
       </c>
       <c r="M28" s="141"/>
       <c r="N28" s="141"/>
@@ -8132,7 +8135,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.45">
       <c r="B31" s="31" t="s">
-        <v>96</v>
+        <v>561</v>
       </c>
       <c r="C31" s="50">
         <f>SUM(C29:C30)</f>
@@ -8214,7 +8217,7 @@
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B33" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C33" s="51"/>
       <c r="D33" s="51"/>
@@ -8366,7 +8369,7 @@
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B36" s="31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C36" s="50">
         <f t="shared" ref="C36:Q36" si="38">SUM(C34:C35)</f>
@@ -8448,7 +8451,7 @@
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B38" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C38" s="51"/>
       <c r="D38" s="51"/>
@@ -8600,7 +8603,7 @@
     </row>
     <row r="41" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B41" s="31" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C41" s="50">
         <f>SUM(C39:C40)</f>
@@ -8682,7 +8685,7 @@
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B43" s="32" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C43" s="50">
         <f>SUM(C41,C36)</f>
@@ -8764,7 +8767,7 @@
     </row>
     <row r="45" spans="2:22" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B45" s="33" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C45" s="53">
         <f t="shared" ref="C45:Q45" si="42">SUM(C41,C36,C31)</f>
@@ -8846,7 +8849,7 @@
     </row>
     <row r="47" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B47" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C47" s="51"/>
       <c r="D47" s="51"/>
@@ -9135,7 +9138,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B52" s="31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C52" s="50">
         <f>SUM(C48:C51)</f>
@@ -9217,7 +9220,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B54" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C54" s="51"/>
       <c r="D54" s="51"/>
@@ -9435,7 +9438,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B58" s="31" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C58" s="50">
         <f>SUM(C55:C57)</f>
@@ -9507,7 +9510,7 @@
     </row>
     <row r="60" spans="1:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B60" s="35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C60" s="56">
         <f>SUM(C58,C52)</f>
@@ -9597,25 +9600,25 @@
       <c r="A63" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="B63" s="260" t="str">
+      <c r="B63" s="261" t="str">
         <f>"Cash-Flow Statement for "&amp;'Data Sheet'!B1</f>
         <v>Cash-Flow Statement for INFOSYS LTD</v>
       </c>
-      <c r="C63" s="260"/>
-      <c r="D63" s="260"/>
-      <c r="E63" s="260"/>
-      <c r="F63" s="260"/>
-      <c r="G63" s="260"/>
-      <c r="H63" s="260"/>
-      <c r="I63" s="260"/>
-      <c r="J63" s="260"/>
-      <c r="K63" s="260"/>
-      <c r="L63" s="260"/>
-      <c r="M63" s="260"/>
-      <c r="N63" s="260"/>
-      <c r="O63" s="260"/>
-      <c r="P63" s="260"/>
-      <c r="Q63" s="260"/>
+      <c r="C63" s="261"/>
+      <c r="D63" s="261"/>
+      <c r="E63" s="261"/>
+      <c r="F63" s="261"/>
+      <c r="G63" s="261"/>
+      <c r="H63" s="261"/>
+      <c r="I63" s="261"/>
+      <c r="J63" s="261"/>
+      <c r="K63" s="261"/>
+      <c r="L63" s="261"/>
+      <c r="M63" s="261"/>
+      <c r="N63" s="261"/>
+      <c r="O63" s="261"/>
+      <c r="P63" s="261"/>
+      <c r="Q63" s="261"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B64" s="12" t="str">
@@ -10372,7 +10375,7 @@
         <v>89699</v>
       </c>
       <c r="M77" s="142" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N77" s="142">
         <v>0</v>
@@ -10717,7 +10720,7 @@
         <v>31.719116061969316</v>
       </c>
       <c r="T82" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.45">
@@ -11224,7 +11227,7 @@
     </row>
     <row r="93" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B93" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C93" s="60">
         <v>32697</v>
@@ -11355,7 +11358,7 @@
     <row r="95" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A95" s="12"/>
       <c r="B95" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C95" s="52">
         <f>SUM(C93:C94)</f>
@@ -11435,34 +11438,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75629A1-0F23-4F55-ADAC-54438E6BBC3E}">
-  <dimension ref="A1:W44"/>
+  <dimension ref="A1:W45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="1.796875" customWidth="1"/>
-    <col min="2" max="2" width="26.46484375" style="47" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.06640625" style="47" bestFit="1" customWidth="1"/>
     <col min="3" max="17" width="9.265625" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B1" s="260" t="str">
+      <c r="B1" s="261" t="str">
         <f>"Ratios Analysis for "&amp;'Data Sheet'!B1</f>
         <v>Ratios Analysis for INFOSYS LTD</v>
       </c>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
-      <c r="N1" s="260"/>
-      <c r="O1" s="260"/>
-      <c r="P1" s="260"/>
-      <c r="Q1" s="260"/>
+      <c r="C1" s="261"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="261"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="261"/>
+      <c r="O1" s="261"/>
+      <c r="P1" s="261"/>
+      <c r="Q1" s="261"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B2" s="116" t="str">
@@ -11535,7 +11538,7 @@
         <v>78</v>
       </c>
       <c r="B3" s="117" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M3" s="128"/>
       <c r="N3" s="128"/>
@@ -11805,7 +11808,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B8" s="47" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C8" s="123">
         <f>'Historical Financial Statement'!C23/SUM('Historical Financial Statement'!C29:C30)</f>
@@ -11870,7 +11873,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B9" s="47" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C9" s="123">
         <f>'Historical Financial Statement'!C23/'Historical Financial Statement'!C60</f>
@@ -11935,7 +11938,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B10" s="47" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C10" s="123">
         <f>'Historical Financial Statement'!C14/SUM('Historical Financial Statement'!C29:C30,'Historical Financial Statement'!C34)</f>
@@ -11999,19 +12002,71 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="M11" s="128"/>
-      <c r="N11" s="128"/>
-      <c r="O11" s="128"/>
-      <c r="P11" s="128"/>
-      <c r="Q11" s="128"/>
+      <c r="B11" s="47" t="s">
+        <v>559</v>
+      </c>
+      <c r="C11" s="123">
+        <f>'Historical Financial Statement'!C23/SUM('Historical Financial Statement'!C31,'Historical Financial Statement'!C34)</f>
+        <v>0.20806877156359629</v>
+      </c>
+      <c r="D11" s="123">
+        <f>'Historical Financial Statement'!D23/SUM('Historical Financial Statement'!D31,'Historical Financial Statement'!D34)</f>
+        <v>0.24689247262141306</v>
+      </c>
+      <c r="E11" s="123">
+        <f>'Historical Financial Statement'!E23/SUM('Historical Financial Statement'!E31,'Historical Financial Statement'!E34)</f>
+        <v>0.23726673646609595</v>
+      </c>
+      <c r="F11" s="123">
+        <f>'Historical Financial Statement'!F23/SUM('Historical Financial Statement'!F31,'Historical Financial Statement'!F34)</f>
+        <v>0.23741848950530087</v>
+      </c>
+      <c r="G11" s="123">
+        <f>'Historical Financial Statement'!G23/SUM('Historical Financial Statement'!G31,'Historical Financial Statement'!G34)</f>
+        <v>0.23780547529261961</v>
+      </c>
+      <c r="H11" s="123">
+        <f>'Historical Financial Statement'!H23/SUM('Historical Financial Statement'!H31,'Historical Financial Statement'!H34)</f>
+        <v>0.27400277145402357</v>
+      </c>
+      <c r="I11" s="123">
+        <f>'Historical Financial Statement'!I23/SUM('Historical Financial Statement'!I31,'Historical Financial Statement'!I34)</f>
+        <v>0.28800802809834419</v>
+      </c>
+      <c r="J11" s="123">
+        <f>'Historical Financial Statement'!J23/SUM('Historical Financial Statement'!J31,'Historical Financial Statement'!J34)</f>
+        <v>0.2720704845814978</v>
+      </c>
+      <c r="K11" s="123">
+        <f>'Historical Financial Statement'!K23/SUM('Historical Financial Statement'!K31,'Historical Financial Statement'!K34)</f>
+        <v>0.2571002931423903</v>
+      </c>
+      <c r="L11" s="123">
+        <f>'Historical Financial Statement'!L23/SUM('Historical Financial Statement'!L31,'Historical Financial Statement'!L34)</f>
+        <v>0.28888148351432941</v>
+      </c>
+      <c r="M11" s="130">
+        <f>'Historical Financial Statement'!M23/SUM('Historical Financial Statement'!M31,'Historical Financial Statement'!M34)</f>
+        <v>0.31599464960250279</v>
+      </c>
+      <c r="N11" s="130">
+        <f>'Historical Financial Statement'!N23/SUM('Historical Financial Statement'!N31,'Historical Financial Statement'!N34)</f>
+        <v>0.30506727593030802</v>
+      </c>
+      <c r="O11" s="130">
+        <f>'Historical Financial Statement'!O23/SUM('Historical Financial Statement'!O31,'Historical Financial Statement'!O34)</f>
+        <v>0.29456636046058909</v>
+      </c>
+      <c r="P11" s="130">
+        <f>'Historical Financial Statement'!P23/SUM('Historical Financial Statement'!P31,'Historical Financial Statement'!P34)</f>
+        <v>0.28769750134610761</v>
+      </c>
+      <c r="Q11" s="130">
+        <f>'Historical Financial Statement'!Q23/SUM('Historical Financial Statement'!Q31,'Historical Financial Statement'!Q34)</f>
+        <v>0.28115860421816269</v>
+      </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="117" t="s">
-        <v>138</v>
-      </c>
       <c r="M12" s="128"/>
       <c r="N12" s="128"/>
       <c r="O12" s="128"/>
@@ -12019,224 +12074,214 @@
       <c r="Q12" s="128"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B13" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13" s="124">
+      <c r="A13" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="117" t="s">
+        <v>136</v>
+      </c>
+      <c r="M13" s="128"/>
+      <c r="N13" s="128"/>
+      <c r="O13" s="128"/>
+      <c r="P13" s="128"/>
+      <c r="Q13" s="128"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="B14" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="124">
         <f>'Historical Financial Statement'!C34/SUM('Historical Financial Statement'!C29:C30)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="125">
+      <c r="D14" s="125">
         <f>'Historical Financial Statement'!D34/SUM('Historical Financial Statement'!D29:D30)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="125">
+      <c r="E14" s="125">
         <f>'Historical Financial Statement'!E34/SUM('Historical Financial Statement'!E29:E30)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="125">
+      <c r="F14" s="125">
         <f>'Historical Financial Statement'!F34/SUM('Historical Financial Statement'!F29:F30)</f>
         <v>7.0786860198624901E-2</v>
       </c>
-      <c r="G13" s="125">
+      <c r="G14" s="125">
         <f>'Historical Financial Statement'!G34/SUM('Historical Financial Statement'!G29:G30)</f>
         <v>6.9743683776243931E-2</v>
       </c>
-      <c r="H13" s="125">
+      <c r="H14" s="125">
         <f>'Historical Financial Statement'!H34/SUM('Historical Financial Statement'!H29:H30)</f>
         <v>7.264764432647644E-2</v>
       </c>
-      <c r="I13" s="125">
+      <c r="I14" s="125">
         <f>'Historical Financial Statement'!I34/SUM('Historical Financial Statement'!I29:I30)</f>
         <v>0.11005609558794277</v>
       </c>
-      <c r="J13" s="125">
+      <c r="J14" s="125">
         <f>'Historical Financial Statement'!J34/SUM('Historical Financial Statement'!J29:J30)</f>
         <v>9.4863588905533619E-2</v>
       </c>
-      <c r="K13" s="125">
+      <c r="K14" s="125">
         <f>'Historical Financial Statement'!K34/SUM('Historical Financial Statement'!K29:K30)</f>
         <v>8.5860694232816379E-2</v>
       </c>
-      <c r="L13" s="125">
+      <c r="L14" s="125">
         <f>'Historical Financial Statement'!L34/SUM('Historical Financial Statement'!L29:L30)</f>
         <v>9.8823934864084778E-2</v>
       </c>
-      <c r="M13" s="131">
+      <c r="M14" s="131">
         <f>'Historical Financial Statement'!M34/SUM('Historical Financial Statement'!M29:M30)</f>
         <v>8.5189289299472087E-2</v>
       </c>
-      <c r="N13" s="131">
+      <c r="N14" s="131">
         <f>'Historical Financial Statement'!N34/SUM('Historical Financial Statement'!N29:N30)</f>
         <v>7.427521305682061E-2</v>
       </c>
-      <c r="O13" s="131">
+      <c r="O14" s="131">
         <f>'Historical Financial Statement'!O34/SUM('Historical Financial Statement'!O29:O30)</f>
         <v>6.5496378811677344E-2</v>
       </c>
-      <c r="P13" s="131">
+      <c r="P14" s="131">
         <f>'Historical Financial Statement'!P34/SUM('Historical Financial Statement'!P29:P30)</f>
         <v>5.7462758617250212E-2</v>
       </c>
-      <c r="Q13" s="131">
+      <c r="Q14" s="131">
         <f>'Historical Financial Statement'!Q34/SUM('Historical Financial Statement'!Q29:Q30)</f>
         <v>5.0658070844443626E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B14" s="47" t="s">
-        <v>153</v>
-      </c>
-      <c r="C14" s="124">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="B15" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="124">
         <f>'Historical Financial Statement'!C34/'Historical Financial Statement'!C60</f>
         <v>0</v>
       </c>
-      <c r="D14" s="125">
+      <c r="D15" s="125">
         <f>'Historical Financial Statement'!D34/'Historical Financial Statement'!D60</f>
         <v>0</v>
       </c>
-      <c r="E14" s="125">
+      <c r="E15" s="125">
         <f>'Historical Financial Statement'!E34/'Historical Financial Statement'!E60</f>
         <v>0</v>
       </c>
-      <c r="F14" s="125">
+      <c r="F15" s="125">
         <f>'Historical Financial Statement'!F34/'Historical Financial Statement'!F60</f>
         <v>5.0468409586056646E-2</v>
       </c>
-      <c r="G14" s="125">
+      <c r="G15" s="125">
         <f>'Historical Financial Statement'!G34/'Historical Financial Statement'!G60</f>
         <v>4.9529815553757288E-2</v>
       </c>
-      <c r="H14" s="125">
+      <c r="H15" s="125">
         <f>'Historical Financial Statement'!H34/'Historical Financial Statement'!H60</f>
         <v>4.6894944700974051E-2</v>
       </c>
-      <c r="I14" s="125">
+      <c r="I15" s="125">
         <f>'Historical Financial Statement'!I34/'Historical Financial Statement'!I60</f>
         <v>6.6607274711868766E-2</v>
       </c>
-      <c r="J14" s="125">
+      <c r="J15" s="125">
         <f>'Historical Financial Statement'!J34/'Historical Financial Statement'!J60</f>
         <v>6.1454197912071754E-2</v>
       </c>
-      <c r="K14" s="125">
+      <c r="K15" s="125">
         <f>'Historical Financial Statement'!K34/'Historical Financial Statement'!K60</f>
         <v>5.566494130383301E-2</v>
       </c>
-      <c r="L14" s="125">
+      <c r="L15" s="125">
         <f>'Historical Financial Statement'!L34/'Historical Financial Statement'!L60</f>
         <v>5.9473192989733484E-2</v>
       </c>
-      <c r="M14" s="131">
+      <c r="M15" s="131">
         <f>'Historical Financial Statement'!M34/'Historical Financial Statement'!M60</f>
         <v>5.5072050727668673E-2</v>
       </c>
-      <c r="N14" s="131">
+      <c r="N15" s="131">
         <f>'Historical Financial Statement'!N34/'Historical Financial Statement'!N60</f>
         <v>4.8686799910478223E-2</v>
       </c>
-      <c r="O14" s="131">
+      <c r="O15" s="131">
         <f>'Historical Financial Statement'!O34/'Historical Financial Statement'!O60</f>
         <v>4.3298707669026847E-2</v>
       </c>
-      <c r="P14" s="131">
+      <c r="P15" s="131">
         <f>'Historical Financial Statement'!P34/'Historical Financial Statement'!P60</f>
         <v>3.8449070290217713E-2</v>
       </c>
-      <c r="Q14" s="131">
+      <c r="Q15" s="131">
         <f>'Historical Financial Statement'!Q34/'Historical Financial Statement'!Q60</f>
         <v>3.4251293452146538E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B15" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" s="124">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="B16" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="124">
         <f>IFERROR('Historical Financial Statement'!C19/'Historical Financial Statement'!C17,0)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="124">
+      <c r="D16" s="124">
         <f>IFERROR('Historical Financial Statement'!D19/'Historical Financial Statement'!D17,0)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="124">
+      <c r="E16" s="124">
         <f>IFERROR('Historical Financial Statement'!E19/'Historical Financial Statement'!E17,0)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="124">
+      <c r="F16" s="124">
         <f>IFERROR('Historical Financial Statement'!F19/'Historical Financial Statement'!F17,0)</f>
         <v>129.45294117647057</v>
       </c>
-      <c r="G15" s="124">
+      <c r="G16" s="124">
         <f>IFERROR('Historical Financial Statement'!G19/'Historical Financial Statement'!G17,0)</f>
         <v>136.55384615384617</v>
       </c>
-      <c r="H15" s="124">
+      <c r="H16" s="124">
         <f>IFERROR('Historical Financial Statement'!H19/'Historical Financial Statement'!H17,0)</f>
         <v>150.55000000000001</v>
       </c>
-      <c r="I15" s="124">
+      <c r="I16" s="124">
         <f>IFERROR('Historical Financial Statement'!I19/'Historical Financial Statement'!I17,0)</f>
         <v>117.33098591549296</v>
       </c>
-      <c r="J15" s="124">
+      <c r="J16" s="124">
         <f>IFERROR('Historical Financial Statement'!J19/'Historical Financial Statement'!J17,0)</f>
         <v>76.57021276595745</v>
       </c>
-      <c r="K15" s="124">
+      <c r="K16" s="124">
         <f>IFERROR('Historical Financial Statement'!K19/'Historical Financial Statement'!K17,0)</f>
         <v>90.40384615384616</v>
       </c>
-      <c r="L15" s="124">
+      <c r="L16" s="124">
         <f>IFERROR('Historical Financial Statement'!L19/'Historical Financial Statement'!L17,0)</f>
         <v>96.14182692307692</v>
       </c>
-      <c r="M15" s="132">
+      <c r="M16" s="132">
         <f>IFERROR('Historical Financial Statement'!M19/'Historical Financial Statement'!M17,0)</f>
         <v>184.52993653594942</v>
       </c>
-      <c r="N15" s="132">
+      <c r="N16" s="132">
         <f>IFERROR('Historical Financial Statement'!N19/'Historical Financial Statement'!N17,0)</f>
         <v>183.45808348061729</v>
       </c>
-      <c r="O15" s="132">
+      <c r="O16" s="132">
         <f>IFERROR('Historical Financial Statement'!O19/'Historical Financial Statement'!O17,0)</f>
         <v>182.43192256503536</v>
       </c>
-      <c r="P15" s="132">
+      <c r="P16" s="132">
         <f>IFERROR('Historical Financial Statement'!P19/'Historical Financial Statement'!P17,0)</f>
         <v>183.22034898408808</v>
       </c>
-      <c r="Q15" s="132">
+      <c r="Q16" s="132">
         <f>IFERROR('Historical Financial Statement'!Q19/'Historical Financial Statement'!Q17,0)</f>
         <v>201.04685408241855</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="124"/>
-      <c r="H16" s="124"/>
-      <c r="I16" s="124"/>
-      <c r="J16" s="124"/>
-      <c r="K16" s="124"/>
-      <c r="L16" s="124"/>
-      <c r="M16" s="132"/>
-      <c r="N16" s="132"/>
-      <c r="O16" s="132"/>
-      <c r="P16" s="132"/>
-      <c r="Q16" s="132"/>
-    </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A17" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="117" t="s">
-        <v>143</v>
-      </c>
       <c r="C17" s="124"/>
       <c r="D17" s="124"/>
       <c r="E17" s="124"/>
@@ -12252,362 +12297,362 @@
       <c r="O17" s="132"/>
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
-      <c r="S17" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="B18" s="47" t="s">
-        <v>144</v>
-      </c>
-      <c r="C18" s="124">
+      <c r="A18" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="117" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="124"/>
+      <c r="D18" s="124"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="124"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="132"/>
+      <c r="N18" s="132"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="132"/>
+      <c r="Q18" s="132"/>
+      <c r="S18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="B19" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="124">
         <f>'Historical Financial Statement'!C3/'Historical Financial Statement'!C60</f>
         <v>0.82363977485928708</v>
       </c>
-      <c r="D18" s="124">
+      <c r="D19" s="124">
         <f>'Historical Financial Statement'!D3/'Historical Financial Statement'!D60</f>
         <v>0.88875726222132601</v>
       </c>
-      <c r="E18" s="124">
+      <c r="E19" s="124">
         <f>'Historical Financial Statement'!E3/'Historical Financial Statement'!E60</f>
         <v>0.98345347702995267</v>
       </c>
-      <c r="F18" s="124">
+      <c r="F19" s="124">
         <f>'Historical Financial Statement'!F3/'Historical Financial Statement'!F60</f>
         <v>0.98900871459694994</v>
       </c>
-      <c r="G18" s="124">
+      <c r="G19" s="124">
         <f>'Historical Financial Statement'!G3/'Historical Financial Statement'!G60</f>
         <v>0.9345276297309113</v>
       </c>
-      <c r="H18" s="124">
+      <c r="H19" s="124">
         <f>'Historical Financial Statement'!H3/'Historical Financial Statement'!H60</f>
         <v>1.0420803742000702</v>
       </c>
-      <c r="I18" s="124">
+      <c r="I19" s="124">
         <f>'Historical Financial Statement'!I3/'Historical Financial Statement'!I60</f>
         <v>1.1779431121384314</v>
       </c>
-      <c r="J18" s="124">
+      <c r="J19" s="124">
         <f>'Historical Financial Statement'!J3/'Historical Financial Statement'!J60</f>
         <v>1.1297603293633289</v>
       </c>
-      <c r="K18" s="124">
+      <c r="K19" s="124">
         <f>'Historical Financial Statement'!K3/'Historical Financial Statement'!K60</f>
         <v>1.1028113264995434</v>
       </c>
-      <c r="L18" s="124">
+      <c r="L19" s="124">
         <f>'Historical Financial Statement'!L3/'Historical Financial Statement'!L60</f>
         <v>1.1578995125998133</v>
       </c>
-      <c r="M18" s="132">
+      <c r="M19" s="132">
         <f>'Historical Financial Statement'!M3/'Historical Financial Statement'!M60</f>
         <v>1.1801093587817597</v>
       </c>
-      <c r="N18" s="132">
+      <c r="N19" s="132">
         <f>'Historical Financial Statement'!N3/'Historical Financial Statement'!N60</f>
         <v>1.1482689627518088</v>
       </c>
-      <c r="O18" s="132">
+      <c r="O19" s="132">
         <f>'Historical Financial Statement'!O3/'Historical Financial Statement'!O60</f>
         <v>1.1239544740988145</v>
       </c>
-      <c r="P18" s="132">
+      <c r="P19" s="132">
         <f>'Historical Financial Statement'!P3/'Historical Financial Statement'!P60</f>
         <v>1.0985024233150831</v>
       </c>
-      <c r="Q18" s="132">
+      <c r="Q19" s="132">
         <f>'Historical Financial Statement'!Q3/'Historical Financial Statement'!Q60</f>
         <v>1.0770442419908408</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="B19" s="47" t="s">
-        <v>145</v>
-      </c>
-      <c r="C19" s="124">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="B20" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="124">
         <f>'Historical Financial Statement'!C3/'Historical Financial Statement'!C48</f>
         <v>4.8299597997037873</v>
       </c>
-      <c r="D19" s="124">
+      <c r="D20" s="124">
         <f>'Historical Financial Statement'!D3/'Historical Financial Statement'!D48</f>
         <v>5.6085573405439799</v>
       </c>
-      <c r="E19" s="124">
+      <c r="E20" s="124">
         <f>'Historical Financial Statement'!E3/'Historical Financial Statement'!E48</f>
         <v>5.2625716104392106</v>
       </c>
-      <c r="F19" s="124">
+      <c r="F20" s="124">
         <f>'Historical Financial Statement'!F3/'Historical Financial Statement'!F48</f>
         <v>3.8165118332002188</v>
       </c>
-      <c r="G19" s="124">
+      <c r="G20" s="124">
         <f>'Historical Financial Statement'!G3/'Historical Financial Statement'!G48</f>
         <v>3.9393060184277591</v>
       </c>
-      <c r="H19" s="124">
+      <c r="H20" s="124">
         <f>'Historical Financial Statement'!H3/'Historical Financial Statement'!H48</f>
         <v>4.7147674418604648</v>
       </c>
-      <c r="I19" s="124">
+      <c r="I20" s="124">
         <f>'Historical Financial Statement'!I3/'Historical Financial Statement'!I48</f>
         <v>5.0219674935842598</v>
       </c>
-      <c r="J19" s="124">
+      <c r="J20" s="124">
         <f>'Historical Financial Statement'!J3/'Historical Financial Statement'!J48</f>
         <v>5.5633190934762142</v>
       </c>
-      <c r="K19" s="124">
+      <c r="K20" s="124">
         <f>'Historical Financial Statement'!K3/'Historical Financial Statement'!K48</f>
         <v>5.2643648460967025</v>
       </c>
-      <c r="L19" s="124">
+      <c r="L20" s="124">
         <f>'Historical Financial Statement'!L3/'Historical Financial Statement'!L48</f>
         <v>5.2901984009475864</v>
       </c>
-      <c r="M19" s="132">
+      <c r="M20" s="132">
         <f>'Historical Financial Statement'!M3/'Historical Financial Statement'!M48</f>
         <v>5.8408179707535393</v>
       </c>
-      <c r="N19" s="132">
+      <c r="N20" s="132">
         <f>'Historical Financial Statement'!N3/'Historical Financial Statement'!N48</f>
         <v>6.4399483646471651</v>
       </c>
-      <c r="O19" s="132">
+      <c r="O20" s="132">
         <f>'Historical Financial Statement'!O3/'Historical Financial Statement'!O48</f>
         <v>7.0280124904076082</v>
       </c>
-      <c r="P19" s="132">
+      <c r="P20" s="132">
         <f>'Historical Financial Statement'!P3/'Historical Financial Statement'!P48</f>
         <v>7.6251339984669455</v>
       </c>
-      <c r="Q19" s="132">
+      <c r="Q20" s="132">
         <f>'Historical Financial Statement'!Q3/'Historical Financial Statement'!Q48</f>
         <v>8.2904597785601961</v>
       </c>
-      <c r="W19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="B20" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" s="124">
+      <c r="W20" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="B21" s="47" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="124">
         <f>IFERROR('Historical Financial Statement'!C4/'Historical Financial Statement'!C56,0)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="124">
+      <c r="D21" s="124">
         <f>IFERROR('Historical Financial Statement'!D4/'Historical Financial Statement'!D56,0)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="124">
+      <c r="E21" s="124">
         <f>IFERROR('Historical Financial Statement'!E4/'Historical Financial Statement'!E56,0)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="124">
+      <c r="F21" s="124">
         <f>IFERROR('Historical Financial Statement'!F4/'Historical Financial Statement'!F56,0)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="124">
+      <c r="G21" s="124">
         <f>IFERROR('Historical Financial Statement'!G4/'Historical Financial Statement'!G56,0)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="124">
+      <c r="H21" s="124">
         <f>IFERROR('Historical Financial Statement'!H4/'Historical Financial Statement'!H56,0)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="124">
+      <c r="I21" s="124">
         <f>IFERROR('Historical Financial Statement'!I4/'Historical Financial Statement'!I56,0)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="124">
+      <c r="J21" s="124">
         <f>IFERROR('Historical Financial Statement'!J4/'Historical Financial Statement'!J56,0)</f>
         <v>0</v>
       </c>
-      <c r="K20" s="124">
+      <c r="K21" s="124">
         <f>IFERROR('Historical Financial Statement'!K4/'Historical Financial Statement'!K56,0)</f>
         <v>0</v>
       </c>
-      <c r="L20" s="124">
+      <c r="L21" s="124">
         <f>IFERROR('Historical Financial Statement'!L4/'Historical Financial Statement'!L56,0)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="132">
+      <c r="M21" s="132">
         <f>IFERROR('Historical Financial Statement'!M4/'Historical Financial Statement'!M56,0)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="132">
+      <c r="N21" s="132">
         <f>IFERROR('Historical Financial Statement'!N4/'Historical Financial Statement'!N56,0)</f>
         <v>0</v>
       </c>
-      <c r="O20" s="132">
+      <c r="O21" s="132">
         <f>IFERROR('Historical Financial Statement'!O4/'Historical Financial Statement'!O56,0)</f>
         <v>0</v>
       </c>
-      <c r="P20" s="132">
+      <c r="P21" s="132">
         <f>IFERROR('Historical Financial Statement'!P4/'Historical Financial Statement'!P56,0)</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="132">
+      <c r="Q21" s="132">
         <f>IFERROR('Historical Financial Statement'!Q4/'Historical Financial Statement'!Q56,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="B21" s="47" t="s">
-        <v>147</v>
-      </c>
-      <c r="C21" s="124">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="B22" s="47" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="124">
         <f>'Historical Financial Statement'!C4/'Historical Financial Statement'!C39</f>
         <v>121.55040871934605</v>
       </c>
-      <c r="D21" s="124">
+      <c r="D22" s="124">
         <f>'Historical Financial Statement'!D4/'Historical Financial Statement'!D39</f>
         <v>66.851585014409224</v>
       </c>
-      <c r="E21" s="124">
+      <c r="E22" s="124">
         <f>'Historical Financial Statement'!E4/'Historical Financial Statement'!E39</f>
         <v>33.502114803625375</v>
       </c>
-      <c r="F21" s="124">
+      <c r="F22" s="124">
         <f>'Historical Financial Statement'!F4/'Historical Financial Statement'!F39</f>
         <v>21.812762973352033</v>
       </c>
-      <c r="G21" s="124">
+      <c r="G22" s="124">
         <f>'Historical Financial Statement'!G4/'Historical Financial Statement'!G39</f>
         <v>25.894139886578451</v>
       </c>
-      <c r="H21" s="124">
+      <c r="H22" s="124">
         <f>'Historical Financial Statement'!H4/'Historical Financial Statement'!H39</f>
         <v>20.517416545718433</v>
       </c>
-      <c r="I21" s="124">
+      <c r="I22" s="124">
         <f>'Historical Financial Statement'!I4/'Historical Financial Statement'!I39</f>
         <v>27.135834411384216</v>
       </c>
-      <c r="J21" s="124">
+      <c r="J22" s="124">
         <f>'Historical Financial Statement'!J4/'Historical Financial Statement'!J39</f>
         <v>27.813447927199192</v>
       </c>
-      <c r="K21" s="124">
+      <c r="K22" s="124">
         <f>'Historical Financial Statement'!K4/'Historical Financial Statement'!K39</f>
         <v>27.99831892411143</v>
       </c>
-      <c r="L21" s="124">
+      <c r="L22" s="124">
         <f>'Historical Financial Statement'!L4/'Historical Financial Statement'!L39</f>
         <v>27.035623946037099</v>
       </c>
-      <c r="M21" s="132">
+      <c r="M22" s="132">
         <f>'Historical Financial Statement'!M4/'Historical Financial Statement'!M39</f>
         <v>30.143441712628899</v>
       </c>
-      <c r="N21" s="132">
+      <c r="N22" s="132">
         <f>'Historical Financial Statement'!N4/'Historical Financial Statement'!N39</f>
         <v>28.035172314156775</v>
       </c>
-      <c r="O21" s="132">
+      <c r="O22" s="132">
         <f>'Historical Financial Statement'!O4/'Historical Financial Statement'!O39</f>
         <v>26.496680609716485</v>
       </c>
-      <c r="P21" s="132">
+      <c r="P22" s="132">
         <f>'Historical Financial Statement'!P4/'Historical Financial Statement'!P39</f>
         <v>25.953972054264273</v>
       </c>
-      <c r="Q21" s="132">
+      <c r="Q22" s="132">
         <f>'Historical Financial Statement'!Q4/'Historical Financial Statement'!Q39</f>
         <v>26.456250770965404</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="B22" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="C22" s="124">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="B23" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" s="124">
         <f>'Historical Financial Statement'!C3/'Historical Financial Statement'!C55</f>
         <v>5.5578639831196233</v>
       </c>
-      <c r="D22" s="124">
+      <c r="D23" s="124">
         <f>'Historical Financial Statement'!D3/'Historical Financial Statement'!D55</f>
         <v>5.3661543144118093</v>
       </c>
-      <c r="E22" s="124">
+      <c r="E23" s="124">
         <f>'Historical Financial Statement'!E3/'Historical Financial Statement'!E55</f>
         <v>5.5759762595265396</v>
       </c>
-      <c r="F22" s="124">
+      <c r="F23" s="124">
         <f>'Historical Financial Statement'!F3/'Historical Financial Statement'!F55</f>
         <v>4.9110726456428839</v>
       </c>
-      <c r="G22" s="124">
+      <c r="G23" s="124">
         <f>'Historical Financial Statement'!G3/'Historical Financial Statement'!G55</f>
         <v>5.2074219964755883</v>
       </c>
-      <c r="H22" s="124">
+      <c r="H23" s="124">
         <f>'Historical Financial Statement'!H3/'Historical Financial Statement'!H55</f>
         <v>5.3591065292096216</v>
       </c>
-      <c r="I22" s="124">
+      <c r="I23" s="124">
         <f>'Historical Financial Statement'!I3/'Historical Financial Statement'!I55</f>
         <v>5.7727737570799249</v>
       </c>
-      <c r="J22" s="124">
+      <c r="J23" s="124">
         <f>'Historical Financial Statement'!J3/'Historical Financial Statement'!J55</f>
         <v>5.0895903023879709</v>
       </c>
-      <c r="K22" s="124">
+      <c r="K23" s="124">
         <f>'Historical Financial Statement'!K3/'Historical Financial Statement'!K55</f>
         <v>5.2310803004043906</v>
       </c>
-      <c r="L22" s="124">
+      <c r="L23" s="124">
         <f>'Historical Financial Statement'!L3/'Historical Financial Statement'!L55</f>
         <v>5.0703865584378729</v>
       </c>
-      <c r="M22" s="132">
+      <c r="M23" s="132">
         <f>'Historical Financial Statement'!M3/'Historical Financial Statement'!M55</f>
         <v>5.3023176208442653</v>
       </c>
-      <c r="N22" s="132">
+      <c r="N23" s="132">
         <f>'Historical Financial Statement'!N3/'Historical Financial Statement'!N55</f>
         <v>5.2780495501153393</v>
       </c>
-      <c r="O22" s="132">
+      <c r="O23" s="132">
         <f>'Historical Financial Statement'!O3/'Historical Financial Statement'!O55</f>
         <v>5.2693979341577721</v>
       </c>
-      <c r="P22" s="132">
+      <c r="P23" s="132">
         <f>'Historical Financial Statement'!P3/'Historical Financial Statement'!P55</f>
         <v>5.2405841544848215</v>
       </c>
-      <c r="Q22" s="132">
+      <c r="Q23" s="132">
         <f>'Historical Financial Statement'!Q3/'Historical Financial Statement'!Q55</f>
         <v>5.2759836990392737</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="C23" s="124"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="124"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="124"/>
-      <c r="I23" s="124"/>
-      <c r="J23" s="124"/>
-      <c r="K23" s="124"/>
-      <c r="L23" s="124"/>
-      <c r="M23" s="132"/>
-      <c r="N23" s="132"/>
-      <c r="O23" s="132"/>
-      <c r="P23" s="132"/>
-      <c r="Q23" s="132"/>
-    </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A24" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="117" t="s">
-        <v>149</v>
-      </c>
       <c r="C24" s="124"/>
       <c r="D24" s="124"/>
       <c r="E24" s="124"/>
@@ -12625,224 +12670,224 @@
       <c r="Q24" s="132"/>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="B25" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="C25" s="124">
+      <c r="A25" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="117" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="124"/>
+      <c r="D25" s="124"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="124"/>
+      <c r="G25" s="124"/>
+      <c r="H25" s="124"/>
+      <c r="I25" s="124"/>
+      <c r="J25" s="124"/>
+      <c r="K25" s="124"/>
+      <c r="L25" s="124"/>
+      <c r="M25" s="132"/>
+      <c r="N25" s="132"/>
+      <c r="O25" s="132"/>
+      <c r="P25" s="132"/>
+      <c r="Q25" s="132"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="B26" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="124">
         <f>'Historical Financial Statement'!C58/'Historical Financial Statement'!C41</f>
         <v>95.223433242506815</v>
       </c>
-      <c r="D25" s="124">
+      <c r="D26" s="124">
         <f>'Historical Financial Statement'!D58/'Historical Financial Statement'!D41</f>
         <v>47.492795389048993</v>
       </c>
-      <c r="E25" s="124">
+      <c r="E26" s="124">
         <f>'Historical Financial Statement'!E58/'Historical Financial Statement'!E41</f>
         <v>20.782477341389729</v>
       </c>
-      <c r="F25" s="124">
+      <c r="F26" s="124">
         <f>'Historical Financial Statement'!F58/'Historical Financial Statement'!F41</f>
         <v>13.021037868162693</v>
       </c>
-      <c r="G25" s="124">
+      <c r="G26" s="124">
         <f>'Historical Financial Statement'!G58/'Historical Financial Statement'!G41</f>
         <v>16.638185255198486</v>
       </c>
-      <c r="H25" s="124">
+      <c r="H26" s="124">
         <f>'Historical Financial Statement'!H58/'Historical Financial Statement'!H41</f>
         <v>9.7169811320754711</v>
       </c>
-      <c r="I25" s="124">
+      <c r="I26" s="124">
         <f>'Historical Financial Statement'!I58/'Historical Financial Statement'!I41</f>
         <v>9.7275549805950838</v>
       </c>
-      <c r="J25" s="124">
+      <c r="J26" s="124">
         <f>'Historical Financial Statement'!J58/'Historical Financial Statement'!J41</f>
         <v>11.369817997977755</v>
       </c>
-      <c r="K25" s="124">
+      <c r="K26" s="124">
         <f>'Historical Financial Statement'!K58/'Historical Financial Statement'!K41</f>
         <v>13.355667627281461</v>
       </c>
-      <c r="L25" s="124">
+      <c r="L26" s="124">
         <f>'Historical Financial Statement'!L58/'Historical Financial Statement'!L41</f>
         <v>12.106871838111298</v>
       </c>
-      <c r="M25" s="132">
+      <c r="M26" s="132">
         <f>'Historical Financial Statement'!M58/'Historical Financial Statement'!M41</f>
         <v>11.862369767254878</v>
       </c>
-      <c r="N25" s="132">
+      <c r="N26" s="132">
         <f>'Historical Financial Statement'!N58/'Historical Financial Statement'!N41</f>
         <v>12.947117796675577</v>
       </c>
-      <c r="O25" s="132">
+      <c r="O26" s="132">
         <f>'Historical Financial Statement'!O58/'Historical Financial Statement'!O41</f>
         <v>13.706395449805347</v>
       </c>
-      <c r="P25" s="132">
+      <c r="P26" s="132">
         <f>'Historical Financial Statement'!P58/'Historical Financial Statement'!P41</f>
         <v>14.634903303637472</v>
       </c>
-      <c r="Q25" s="132">
+      <c r="Q26" s="132">
         <f>'Historical Financial Statement'!Q58/'Historical Financial Statement'!Q41</f>
         <v>15.789196222842925</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="B26" s="47" t="s">
-        <v>151</v>
-      </c>
-      <c r="C26" s="124">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="B27" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" s="124">
         <f>(SUM('Historical Financial Statement'!C55,'Historical Financial Statement'!C57)-'Historical Financial Statement'!C56)/'Historical Financial Statement'!C41</f>
         <v>95.223433242506815</v>
       </c>
-      <c r="D26" s="124">
+      <c r="D27" s="124">
         <f>(SUM('Historical Financial Statement'!D55,'Historical Financial Statement'!D57)-'Historical Financial Statement'!D56)/'Historical Financial Statement'!D41</f>
         <v>47.492795389048993</v>
       </c>
-      <c r="E26" s="124">
+      <c r="E27" s="124">
         <f>(SUM('Historical Financial Statement'!E55,'Historical Financial Statement'!E57)-'Historical Financial Statement'!E56)/'Historical Financial Statement'!E41</f>
         <v>20.782477341389729</v>
       </c>
-      <c r="F26" s="124">
+      <c r="F27" s="124">
         <f>(SUM('Historical Financial Statement'!F55,'Historical Financial Statement'!F57)-'Historical Financial Statement'!F56)/'Historical Financial Statement'!F41</f>
         <v>13.021037868162693</v>
       </c>
-      <c r="G26" s="124">
+      <c r="G27" s="124">
         <f>(SUM('Historical Financial Statement'!G55,'Historical Financial Statement'!G57)-'Historical Financial Statement'!G56)/'Historical Financial Statement'!G41</f>
         <v>16.638185255198486</v>
       </c>
-      <c r="H26" s="124">
+      <c r="H27" s="124">
         <f>(SUM('Historical Financial Statement'!H55,'Historical Financial Statement'!H57)-'Historical Financial Statement'!H56)/'Historical Financial Statement'!H41</f>
         <v>9.7169811320754711</v>
       </c>
-      <c r="I26" s="124">
+      <c r="I27" s="124">
         <f>(SUM('Historical Financial Statement'!I55,'Historical Financial Statement'!I57)-'Historical Financial Statement'!I56)/'Historical Financial Statement'!I41</f>
         <v>9.7275549805950838</v>
       </c>
-      <c r="J26" s="124">
+      <c r="J27" s="124">
         <f>(SUM('Historical Financial Statement'!J55,'Historical Financial Statement'!J57)-'Historical Financial Statement'!J56)/'Historical Financial Statement'!J41</f>
         <v>11.369817997977755</v>
       </c>
-      <c r="K26" s="124">
+      <c r="K27" s="124">
         <f>(SUM('Historical Financial Statement'!K55,'Historical Financial Statement'!K57)-'Historical Financial Statement'!K56)/'Historical Financial Statement'!K41</f>
         <v>13.355667627281461</v>
       </c>
-      <c r="L26" s="124">
+      <c r="L27" s="124">
         <f>(SUM('Historical Financial Statement'!L55,'Historical Financial Statement'!L57)-'Historical Financial Statement'!L56)/'Historical Financial Statement'!L41</f>
         <v>12.106871838111298</v>
       </c>
-      <c r="M26" s="132">
+      <c r="M27" s="132">
         <f>(SUM('Historical Financial Statement'!M55,'Historical Financial Statement'!M57)-'Historical Financial Statement'!M56)/'Historical Financial Statement'!M41</f>
         <v>11.862369767254878</v>
       </c>
-      <c r="N26" s="132">
+      <c r="N27" s="132">
         <f>(SUM('Historical Financial Statement'!N55,'Historical Financial Statement'!N57)-'Historical Financial Statement'!N56)/'Historical Financial Statement'!N41</f>
         <v>12.947117796675577</v>
       </c>
-      <c r="O26" s="132">
+      <c r="O27" s="132">
         <f>(SUM('Historical Financial Statement'!O55,'Historical Financial Statement'!O57)-'Historical Financial Statement'!O56)/'Historical Financial Statement'!O41</f>
         <v>13.706395449805347</v>
       </c>
-      <c r="P26" s="132">
+      <c r="P27" s="132">
         <f>(SUM('Historical Financial Statement'!P55,'Historical Financial Statement'!P57)-'Historical Financial Statement'!P56)/'Historical Financial Statement'!P41</f>
         <v>14.634903303637472</v>
       </c>
-      <c r="Q26" s="132">
+      <c r="Q27" s="132">
         <f>(SUM('Historical Financial Statement'!Q55,'Historical Financial Statement'!Q57)-'Historical Financial Statement'!Q56)/'Historical Financial Statement'!Q41</f>
         <v>15.789196222842925</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="B27" s="47" t="s">
-        <v>152</v>
-      </c>
-      <c r="C27" s="124">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="B28" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" s="124">
         <f>'Historical Financial Statement'!C57/'Historical Financial Statement'!C41</f>
         <v>61.648501362397823</v>
       </c>
-      <c r="D27" s="124">
+      <c r="D28" s="124">
         <f>'Historical Financial Statement'!D57/'Historical Financial Statement'!D41</f>
         <v>28.556195965417867</v>
       </c>
-      <c r="E27" s="124">
+      <c r="E28" s="124">
         <f>'Historical Financial Statement'!E57/'Historical Financial Statement'!E41</f>
         <v>11.82356495468278</v>
       </c>
-      <c r="F27" s="124">
+      <c r="F28" s="124">
         <f>'Historical Financial Statement'!F57/'Historical Financial Statement'!F41</f>
         <v>6.5389200561009817</v>
       </c>
-      <c r="G27" s="124">
+      <c r="G28" s="124">
         <f>'Historical Financial Statement'!G57/'Historical Financial Statement'!G41</f>
         <v>9.3436672967863892</v>
       </c>
-      <c r="H27" s="124">
+      <c r="H28" s="124">
         <f>'Historical Financial Statement'!H57/'Historical Financial Statement'!H41</f>
         <v>4.2264150943396226</v>
       </c>
-      <c r="I27" s="124">
+      <c r="I28" s="124">
         <f>'Historical Financial Statement'!I57/'Historical Financial Statement'!I41</f>
         <v>3.1495472186287192</v>
       </c>
-      <c r="J27" s="124">
+      <c r="J28" s="124">
         <f>'Historical Financial Statement'!J57/'Historical Financial Statement'!J41</f>
         <v>3.7376137512639027</v>
       </c>
-      <c r="K27" s="124">
+      <c r="K28" s="124">
         <f>'Historical Financial Statement'!K57/'Historical Financial Statement'!K41</f>
         <v>5.8729586935638807</v>
       </c>
-      <c r="L27" s="124">
+      <c r="L28" s="124">
         <f>'Historical Financial Statement'!L57/'Historical Financial Statement'!L41</f>
         <v>4.6798060708263067</v>
       </c>
-      <c r="M27" s="132">
+      <c r="M28" s="132">
         <f>'Historical Financial Statement'!M57/'Historical Financial Statement'!M41</f>
         <v>3.6327374908039443</v>
       </c>
-      <c r="N27" s="132">
+      <c r="N28" s="132">
         <f>'Historical Financial Statement'!N57/'Historical Financial Statement'!N41</f>
         <v>5.3015049059537978</v>
       </c>
-      <c r="O27" s="132">
+      <c r="O28" s="132">
         <f>'Historical Financial Statement'!O57/'Historical Financial Statement'!O41</f>
         <v>6.5066794947847688</v>
       </c>
-      <c r="P27" s="132">
+      <c r="P28" s="132">
         <f>'Historical Financial Statement'!P57/'Historical Financial Statement'!P41</f>
         <v>7.5719587402116328</v>
       </c>
-      <c r="Q27" s="132">
+      <c r="Q28" s="132">
         <f>'Historical Financial Statement'!Q57/'Historical Financial Statement'!Q41</f>
         <v>8.6541461533222677</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="C28" s="124"/>
-      <c r="D28" s="124"/>
-      <c r="E28" s="124"/>
-      <c r="F28" s="124"/>
-      <c r="G28" s="124"/>
-      <c r="H28" s="124"/>
-      <c r="I28" s="124"/>
-      <c r="J28" s="124"/>
-      <c r="K28" s="124"/>
-      <c r="L28" s="124"/>
-      <c r="M28" s="132"/>
-      <c r="N28" s="132"/>
-      <c r="O28" s="132"/>
-      <c r="P28" s="132"/>
-      <c r="Q28" s="132"/>
-    </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A29" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="117" t="s">
-        <v>162</v>
-      </c>
       <c r="C29" s="124"/>
       <c r="D29" s="124"/>
       <c r="E29" s="124"/>
@@ -12860,217 +12905,227 @@
       <c r="Q29" s="132"/>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="B30" s="47" t="s">
-        <v>154</v>
-      </c>
-      <c r="C30" s="120">
+      <c r="A30" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="117" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" s="124"/>
+      <c r="D30" s="124"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="124"/>
+      <c r="G30" s="124"/>
+      <c r="H30" s="124"/>
+      <c r="I30" s="124"/>
+      <c r="J30" s="124"/>
+      <c r="K30" s="124"/>
+      <c r="L30" s="124"/>
+      <c r="M30" s="132"/>
+      <c r="N30" s="132"/>
+      <c r="O30" s="132"/>
+      <c r="P30" s="132"/>
+      <c r="Q30" s="132"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="B31" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="C31" s="120">
         <f>'Historical Financial Statement'!C23/'Data Sheet'!B93</f>
         <v>31.243605650971944</v>
       </c>
-      <c r="D30" s="120">
+      <c r="D31" s="120">
         <f>'Historical Financial Statement'!D23/'Data Sheet'!C93</f>
         <v>36.694748408955633</v>
       </c>
-      <c r="E30" s="120">
+      <c r="E31" s="120">
         <f>'Historical Financial Statement'!E23/'Data Sheet'!D93</f>
         <v>35.272036439378333</v>
       </c>
-      <c r="F30" s="120">
+      <c r="F31" s="120">
         <f>'Historical Financial Statement'!F23/'Data Sheet'!E93</f>
         <v>39.067856304296782</v>
       </c>
-      <c r="G30" s="120">
+      <c r="G31" s="120">
         <f>'Historical Financial Statement'!G23/'Data Sheet'!F93</f>
         <v>45.586405989626115</v>
       </c>
-      <c r="H30" s="120">
+      <c r="H31" s="120">
         <f>'Historical Financial Statement'!H23/'Data Sheet'!G93</f>
         <v>52.644590771863932</v>
       </c>
-      <c r="I30" s="120">
+      <c r="I31" s="120">
         <f>'Historical Financial Statement'!I23/'Data Sheet'!H93</f>
         <v>58.11117003326423</v>
       </c>
-      <c r="J30" s="120">
+      <c r="J31" s="120">
         <f>'Historical Financial Statement'!J23/'Data Sheet'!I93</f>
         <v>63.234479269556005</v>
       </c>
-      <c r="K30" s="120">
+      <c r="K31" s="120">
         <f>'Historical Financial Statement'!K23/'Data Sheet'!J93</f>
         <v>64.406616425492984</v>
       </c>
-      <c r="L30" s="120">
+      <c r="L31" s="120">
         <f>'Historical Financial Statement'!L23/'Data Sheet'!K93</f>
         <v>72.674820001972577</v>
       </c>
-      <c r="M30" s="133">
-        <f>_xlfn.FORECAST.ETS(M$2,$C30:$L30,$C$2:$L$2)</f>
+      <c r="M31" s="133">
+        <f>_xlfn.FORECAST.ETS(M$2,$C31:$L31,$C$2:$L$2)</f>
         <v>76.650633501523259</v>
       </c>
-      <c r="N30" s="133">
-        <f t="shared" ref="N30:Q32" si="1">_xlfn.FORECAST.ETS(N$2,$C30:$L30,$C$2:$L$2)</f>
+      <c r="N31" s="133">
+        <f t="shared" ref="N31:Q33" si="1">_xlfn.FORECAST.ETS(N$2,$C31:$L31,$C$2:$L$2)</f>
         <v>81.308070361617581</v>
       </c>
-      <c r="O30" s="133">
+      <c r="O31" s="133">
         <f t="shared" si="1"/>
         <v>85.978232363517662</v>
       </c>
-      <c r="P30" s="133">
+      <c r="P31" s="133">
         <f t="shared" si="1"/>
         <v>90.648429324598553</v>
       </c>
-      <c r="Q30" s="133">
+      <c r="Q31" s="133">
         <f t="shared" si="1"/>
         <v>95.318626285679443</v>
       </c>
-      <c r="T30" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="B31" s="47" t="s">
-        <v>141</v>
-      </c>
-      <c r="C31" s="120">
-        <f>'Data Sheet'!B90/'Ratios Analysis'!C30</f>
+      <c r="T31" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="B32" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="120">
+        <f>'Data Sheet'!B90/'Ratios Analysis'!C31</f>
         <v>16.359507468821846</v>
       </c>
-      <c r="D31" s="120">
-        <f>'Data Sheet'!C90/'Ratios Analysis'!D30</f>
+      <c r="D32" s="120">
+        <f>'Data Sheet'!C90/'Ratios Analysis'!D31</f>
         <v>15.421825316613639</v>
       </c>
-      <c r="E31" s="120">
-        <f>'Data Sheet'!D90/'Ratios Analysis'!E30</f>
+      <c r="E32" s="120">
+        <f>'Data Sheet'!D90/'Ratios Analysis'!E31</f>
         <v>21.088943964957821</v>
       </c>
-      <c r="F31" s="120">
-        <f>'Data Sheet'!E90/'Ratios Analysis'!F30</f>
+      <c r="F32" s="120">
+        <f>'Data Sheet'!E90/'Ratios Analysis'!F31</f>
         <v>16.420148446421059</v>
       </c>
-      <c r="G31" s="120">
-        <f>'Data Sheet'!F90/'Ratios Analysis'!G30</f>
+      <c r="G32" s="120">
+        <f>'Data Sheet'!F90/'Ratios Analysis'!G31</f>
         <v>30.010042913041239</v>
       </c>
-      <c r="H31" s="120">
-        <f>'Data Sheet'!G90/'Ratios Analysis'!H30</f>
+      <c r="H32" s="120">
+        <f>'Data Sheet'!G90/'Ratios Analysis'!H31</f>
         <v>36.221195227129051</v>
       </c>
-      <c r="I31" s="120">
-        <f>'Data Sheet'!H90/'Ratios Analysis'!I30</f>
+      <c r="I32" s="120">
+        <f>'Data Sheet'!H90/'Ratios Analysis'!I31</f>
         <v>24.572728430396552</v>
       </c>
-      <c r="J31" s="120">
-        <f>'Data Sheet'!I90/'Ratios Analysis'!J30</f>
+      <c r="J32" s="120">
+        <f>'Data Sheet'!I90/'Ratios Analysis'!J31</f>
         <v>23.690398297013104</v>
       </c>
-      <c r="K31" s="120">
-        <f>'Data Sheet'!J90/'Ratios Analysis'!K30</f>
+      <c r="K32" s="120">
+        <f>'Data Sheet'!J90/'Ratios Analysis'!K31</f>
         <v>24.38646970093458</v>
       </c>
-      <c r="L31" s="120">
-        <f>'Data Sheet'!K90/'Ratios Analysis'!L30</f>
+      <c r="L32" s="120">
+        <f>'Data Sheet'!K90/'Ratios Analysis'!L31</f>
         <v>17.208160955418336</v>
       </c>
-      <c r="M31" s="133">
-        <f>_xlfn.FORECAST.ETS(M$2,$C31:$L31,$C$2:$L$2)</f>
+      <c r="M32" s="133">
+        <f>_xlfn.FORECAST.ETS(M$2,$C32:$L32,$C$2:$L$2)</f>
         <v>22.460568869749011</v>
       </c>
-      <c r="N31" s="133">
+      <c r="N32" s="133">
         <f t="shared" si="1"/>
         <v>23.14824779627526</v>
       </c>
-      <c r="O31" s="133">
+      <c r="O32" s="133">
         <f t="shared" si="1"/>
         <v>23.837805612869108</v>
       </c>
-      <c r="P31" s="133">
+      <c r="P32" s="133">
         <f t="shared" si="1"/>
         <v>24.527368591248859</v>
       </c>
-      <c r="Q31" s="133">
+      <c r="Q32" s="133">
         <f t="shared" si="1"/>
         <v>25.216931569628606</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="B32" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="C32" s="120">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="B33" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="120">
         <f>SUM('Historical Financial Statement'!C29:C30)/'Data Sheet'!B93</f>
         <v>150.15999477568079</v>
       </c>
-      <c r="D32" s="120">
+      <c r="D33" s="120">
         <f>SUM('Historical Financial Statement'!D29:D30)/'Data Sheet'!C93</f>
         <v>148.62643651847443</v>
       </c>
-      <c r="E32" s="120">
+      <c r="E33" s="120">
         <f>SUM('Historical Financial Statement'!E29:E30)/'Data Sheet'!D93</f>
         <v>148.65984572775756</v>
       </c>
-      <c r="F32" s="120">
+      <c r="F33" s="120">
         <f>SUM('Historical Financial Statement'!F29:F30)/'Data Sheet'!E93</f>
         <v>153.67457149565627</v>
       </c>
-      <c r="G32" s="120">
+      <c r="G33" s="120">
         <f>SUM('Historical Financial Statement'!G29:G30)/'Data Sheet'!F93</f>
         <v>179.19825380805972</v>
       </c>
-      <c r="H32" s="120">
+      <c r="H33" s="120">
         <f>SUM('Historical Financial Statement'!H29:H30)/'Data Sheet'!G93</f>
         <v>179.11902441343571</v>
       </c>
-      <c r="I32" s="120">
+      <c r="I33" s="120">
         <f>SUM('Historical Financial Statement'!I29:I30)/'Data Sheet'!H93</f>
         <v>181.76493274839703</v>
       </c>
-      <c r="J32" s="120">
+      <c r="J33" s="120">
         <f>SUM('Historical Financial Statement'!J29:J30)/'Data Sheet'!I93</f>
         <v>212.28167385386303</v>
       </c>
-      <c r="K32" s="120">
+      <c r="K33" s="120">
         <f>SUM('Historical Financial Statement'!K29:K30)/'Data Sheet'!J93</f>
         <v>230.70329617412662</v>
       </c>
-      <c r="L32" s="120">
+      <c r="L33" s="120">
         <f>SUM('Historical Financial Statement'!L29:L30)/'Data Sheet'!K93</f>
         <v>228.94762797120032</v>
       </c>
-      <c r="M32" s="133">
-        <f>_xlfn.FORECAST.ETS(M$2,$C32:$L32,$C$2:$L$2)</f>
+      <c r="M33" s="133">
+        <f>_xlfn.FORECAST.ETS(M$2,$C33:$L33,$C$2:$L$2)</f>
         <v>241.34757515128189</v>
       </c>
-      <c r="N32" s="133">
+      <c r="N33" s="133">
         <f t="shared" si="1"/>
         <v>251.52304342627173</v>
       </c>
-      <c r="O32" s="133">
+      <c r="O33" s="133">
         <f t="shared" si="1"/>
         <v>261.72631331846628</v>
       </c>
-      <c r="P32" s="133">
+      <c r="P33" s="133">
         <f t="shared" si="1"/>
         <v>271.92965958873003</v>
       </c>
-      <c r="Q32" s="133">
+      <c r="Q33" s="133">
         <f t="shared" si="1"/>
         <v>282.13300585899384</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="M33" s="128"/>
-      <c r="N33" s="128"/>
-      <c r="O33" s="128"/>
-      <c r="P33" s="128"/>
-      <c r="Q33" s="128"/>
-    </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34" s="117" t="s">
-        <v>161</v>
-      </c>
       <c r="M34" s="128"/>
       <c r="N34" s="128"/>
       <c r="O34" s="128"/>
@@ -13078,293 +13133,283 @@
       <c r="Q34" s="128"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B35" s="47" t="s">
-        <v>156</v>
-      </c>
-      <c r="C35" s="121">
-        <f>IFERROR(365/C20,0)</f>
+      <c r="A35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="117" t="s">
+        <v>159</v>
+      </c>
+      <c r="M35" s="128"/>
+      <c r="N35" s="128"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="B36" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" s="121">
+        <f>IFERROR(365/C21,0)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="121">
-        <f t="shared" ref="D35:Q35" si="2">IFERROR(365/D20,0)</f>
+      <c r="D36" s="121">
+        <f t="shared" ref="D36:Q36" si="2">IFERROR(365/D21,0)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="121">
+      <c r="E36" s="121">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F35" s="121">
+      <c r="F36" s="121">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G35" s="121">
+      <c r="G36" s="121">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H35" s="121">
+      <c r="H36" s="121">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I35" s="121">
+      <c r="I36" s="121">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J35" s="121">
+      <c r="J36" s="121">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K35" s="121">
+      <c r="K36" s="121">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="121">
+      <c r="L36" s="121">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M35" s="134">
+      <c r="M36" s="134">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N35" s="134">
+      <c r="N36" s="134">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O35" s="134">
+      <c r="O36" s="134">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P35" s="134">
+      <c r="P36" s="134">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="134">
+      <c r="Q36" s="134">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B36" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="C36" s="121">
-        <f>365/C21</f>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="B37" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="121">
+        <f>365/C22</f>
         <v>3.0028693761348606</v>
       </c>
-      <c r="D36" s="121">
-        <f t="shared" ref="D36:Q36" si="3">365/D21</f>
+      <c r="D37" s="121">
+        <f t="shared" ref="D37:Q37" si="3">365/D22</f>
         <v>5.4598555878866257</v>
       </c>
-      <c r="E36" s="121">
+      <c r="E37" s="121">
         <f t="shared" si="3"/>
         <v>10.89483461385853</v>
       </c>
-      <c r="F36" s="121">
+      <c r="F37" s="121">
         <f t="shared" si="3"/>
         <v>16.733322616942615</v>
       </c>
-      <c r="G36" s="121">
+      <c r="G37" s="121">
         <f t="shared" si="3"/>
         <v>14.095853409256826</v>
       </c>
-      <c r="H36" s="121">
+      <c r="H37" s="121">
         <f t="shared" si="3"/>
         <v>17.789764085876985</v>
       </c>
-      <c r="I36" s="121">
+      <c r="I37" s="121">
         <f t="shared" si="3"/>
         <v>13.450848588863463</v>
       </c>
-      <c r="J36" s="121">
+      <c r="J37" s="121">
         <f t="shared" si="3"/>
         <v>13.123148232300281</v>
       </c>
-      <c r="K36" s="121">
+      <c r="K37" s="121">
         <f t="shared" si="3"/>
         <v>13.036496976454947</v>
       </c>
-      <c r="L36" s="121">
+      <c r="L37" s="121">
         <f t="shared" si="3"/>
         <v>13.500705614508369</v>
       </c>
-      <c r="M36" s="134">
+      <c r="M37" s="134">
         <f t="shared" si="3"/>
         <v>12.108769910208348</v>
       </c>
-      <c r="N36" s="134">
+      <c r="N37" s="134">
         <f t="shared" si="3"/>
         <v>13.019359963615699</v>
       </c>
-      <c r="O36" s="134">
+      <c r="O37" s="134">
         <f t="shared" si="3"/>
         <v>13.775310401188609</v>
       </c>
-      <c r="P36" s="134">
+      <c r="P37" s="134">
         <f t="shared" si="3"/>
         <v>14.063357979921612</v>
       </c>
-      <c r="Q36" s="134">
+      <c r="Q37" s="134">
         <f t="shared" si="3"/>
         <v>13.796361516219516</v>
       </c>
-      <c r="R36" s="15"/>
-      <c r="S36" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B37" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C37" s="121">
-        <f>365/C22</f>
+      <c r="R37" s="15"/>
+      <c r="S37" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="B38" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="C38" s="121">
+        <f>365/C23</f>
         <v>65.672711874306415</v>
       </c>
-      <c r="D37" s="121">
-        <f t="shared" ref="D37:Q37" si="4">365/D22</f>
+      <c r="D38" s="121">
+        <f t="shared" ref="D38:Q38" si="4">365/D23</f>
         <v>68.018916082924477</v>
       </c>
-      <c r="E37" s="121">
+      <c r="E38" s="121">
         <f t="shared" si="4"/>
         <v>65.459389174478375</v>
       </c>
-      <c r="F37" s="121">
+      <c r="F38" s="121">
         <f t="shared" si="4"/>
         <v>74.321849081957467</v>
       </c>
-      <c r="G37" s="121">
+      <c r="G38" s="121">
         <f t="shared" si="4"/>
         <v>70.092264511505689</v>
       </c>
-      <c r="H37" s="121">
+      <c r="H38" s="121">
         <f t="shared" si="4"/>
         <v>68.108368066688044</v>
       </c>
-      <c r="I37" s="121">
+      <c r="I38" s="121">
         <f t="shared" si="4"/>
         <v>63.227837320378555</v>
       </c>
-      <c r="J37" s="121">
+      <c r="J38" s="121">
         <f t="shared" si="4"/>
         <v>71.715006182078483</v>
       </c>
-      <c r="K37" s="121">
+      <c r="K38" s="121">
         <f t="shared" si="4"/>
         <v>69.775262286029815</v>
       </c>
-      <c r="L37" s="121">
+      <c r="L38" s="121">
         <f t="shared" si="4"/>
         <v>71.986621886369988</v>
       </c>
-      <c r="M37" s="134">
+      <c r="M38" s="134">
         <f t="shared" si="4"/>
         <v>68.837822646671739</v>
       </c>
-      <c r="N37" s="134">
+      <c r="N38" s="134">
         <f t="shared" si="4"/>
         <v>69.154333723908252</v>
       </c>
-      <c r="O37" s="134">
+      <c r="O38" s="134">
         <f t="shared" si="4"/>
         <v>69.267875488006652</v>
       </c>
-      <c r="P37" s="134">
+      <c r="P38" s="134">
         <f t="shared" si="4"/>
         <v>69.648724119359457</v>
       </c>
-      <c r="Q37" s="134">
+      <c r="Q38" s="134">
         <f t="shared" si="4"/>
         <v>69.181411623099663</v>
       </c>
     </row>
-    <row r="38" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B38" s="117" t="s">
-        <v>159</v>
-      </c>
-      <c r="C38" s="122">
-        <f>SUM(C35,C37)-C36</f>
+    <row r="39" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="117" t="s">
+        <v>157</v>
+      </c>
+      <c r="C39" s="122">
+        <f>SUM(C36,C38)-C37</f>
         <v>62.669842498171555</v>
       </c>
-      <c r="D38" s="122">
-        <f t="shared" ref="D38:Q38" si="5">SUM(D35,D37)-D36</f>
+      <c r="D39" s="122">
+        <f t="shared" ref="D39:Q39" si="5">SUM(D36,D38)-D37</f>
         <v>62.559060495037855</v>
       </c>
-      <c r="E38" s="122">
+      <c r="E39" s="122">
         <f t="shared" si="5"/>
         <v>54.564554560619847</v>
       </c>
-      <c r="F38" s="122">
+      <c r="F39" s="122">
         <f t="shared" si="5"/>
         <v>57.588526465014851</v>
       </c>
-      <c r="G38" s="122">
+      <c r="G39" s="122">
         <f t="shared" si="5"/>
         <v>55.996411102248864</v>
       </c>
-      <c r="H38" s="122">
+      <c r="H39" s="122">
         <f t="shared" si="5"/>
         <v>50.318603980811062</v>
       </c>
-      <c r="I38" s="122">
+      <c r="I39" s="122">
         <f t="shared" si="5"/>
         <v>49.77698873151509</v>
       </c>
-      <c r="J38" s="122">
+      <c r="J39" s="122">
         <f t="shared" si="5"/>
         <v>58.591857949778202</v>
       </c>
-      <c r="K38" s="122">
+      <c r="K39" s="122">
         <f t="shared" si="5"/>
         <v>56.738765309574866</v>
       </c>
-      <c r="L38" s="122">
+      <c r="L39" s="122">
         <f t="shared" si="5"/>
         <v>58.485916271861619</v>
       </c>
-      <c r="M38" s="135">
+      <c r="M39" s="135">
         <f t="shared" si="5"/>
         <v>56.729052736463387</v>
       </c>
-      <c r="N38" s="135">
+      <c r="N39" s="135">
         <f t="shared" si="5"/>
         <v>56.134973760292553</v>
       </c>
-      <c r="O38" s="135">
+      <c r="O39" s="135">
         <f t="shared" si="5"/>
         <v>55.492565086818047</v>
       </c>
-      <c r="P38" s="135">
+      <c r="P39" s="135">
         <f t="shared" si="5"/>
         <v>55.585366139437845</v>
       </c>
-      <c r="Q38" s="135">
+      <c r="Q39" s="135">
         <f t="shared" si="5"/>
         <v>55.385050106880144</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="C39" s="121"/>
-      <c r="D39" s="121"/>
-      <c r="E39" s="121"/>
-      <c r="F39" s="121"/>
-      <c r="G39" s="121"/>
-      <c r="H39" s="121"/>
-      <c r="I39" s="121"/>
-      <c r="J39" s="121"/>
-      <c r="K39" s="121"/>
-      <c r="L39" s="121"/>
-      <c r="M39" s="134"/>
-      <c r="N39" s="134"/>
-      <c r="O39" s="134"/>
-      <c r="P39" s="134"/>
-      <c r="Q39" s="134"/>
-    </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="117" t="s">
-        <v>160</v>
-      </c>
       <c r="C40" s="121"/>
       <c r="D40" s="121"/>
       <c r="E40" s="121"/>
@@ -13382,217 +13427,240 @@
       <c r="Q40" s="134"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B41" s="47" t="s">
-        <v>163</v>
-      </c>
-      <c r="C41" s="123">
+      <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="117" t="s">
+        <v>158</v>
+      </c>
+      <c r="C41" s="121"/>
+      <c r="D41" s="121"/>
+      <c r="E41" s="121"/>
+      <c r="F41" s="121"/>
+      <c r="G41" s="121"/>
+      <c r="H41" s="121"/>
+      <c r="I41" s="121"/>
+      <c r="J41" s="121"/>
+      <c r="K41" s="121"/>
+      <c r="L41" s="121"/>
+      <c r="M41" s="134"/>
+      <c r="N41" s="134"/>
+      <c r="O41" s="134"/>
+      <c r="P41" s="134"/>
+      <c r="Q41" s="134"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="B42" s="47" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" s="123">
         <f>'Data Sheet'!B31/'Historical Financial Statement'!C23</f>
         <v>0.4104786455793214</v>
       </c>
-      <c r="D41" s="123">
+      <c r="D42" s="123">
         <f>'Data Sheet'!C31/'Historical Financial Statement'!D23</f>
         <v>0.5905296649822197</v>
       </c>
-      <c r="E41" s="123">
+      <c r="E42" s="123">
         <f>'Data Sheet'!D31/'Historical Financial Statement'!E23</f>
         <v>0.59847501622323163</v>
       </c>
-      <c r="F41" s="123">
+      <c r="F42" s="123">
         <f>'Data Sheet'!E31/'Historical Financial Statement'!F23</f>
         <v>0.44636095919225915</v>
       </c>
-      <c r="G41" s="123">
+      <c r="G42" s="123">
         <f>'Data Sheet'!F31/'Historical Financial Statement'!G23</f>
         <v>0.59051639808474488</v>
       </c>
-      <c r="H41" s="123">
+      <c r="H42" s="123">
         <f>'Data Sheet'!G31/'Historical Financial Statement'!H23</f>
         <v>0.58735663325205456</v>
       </c>
-      <c r="I41" s="123">
+      <c r="I42" s="123">
         <f>'Data Sheet'!H31/'Historical Financial Statement'!I23</f>
         <v>0.58359050937448154</v>
       </c>
-      <c r="J41" s="123">
+      <c r="J42" s="123">
         <f>'Data Sheet'!I31/'Historical Financial Statement'!J23</f>
         <v>0.72589149649497109</v>
       </c>
-      <c r="K41" s="123">
+      <c r="K42" s="123">
         <f>'Data Sheet'!J31/'Historical Financial Statement'!K23</f>
         <v>0.66645981308411217</v>
       </c>
-      <c r="L41" s="123">
+      <c r="L42" s="123">
         <f>'Data Sheet'!K31/'Historical Financial Statement'!L23</f>
         <v>0.65923865101445345</v>
       </c>
-      <c r="M41" s="130">
-        <f>_xlfn.FORECAST.ETS(M$2,$C41:$L41,$C$2:$L$2)</f>
+      <c r="M42" s="130">
+        <f>_xlfn.FORECAST.ETS(M$2,$C42:$L42,$C$2:$L$2)</f>
         <v>0.7085516355880449</v>
       </c>
-      <c r="N41" s="130">
-        <f t="shared" ref="N41:Q41" si="6">_xlfn.FORECAST.ETS(N$2,$C41:$L41,$C$2:$L$2)</f>
+      <c r="N42" s="130">
+        <f t="shared" ref="N42:Q42" si="6">_xlfn.FORECAST.ETS(N$2,$C42:$L42,$C$2:$L$2)</f>
         <v>0.73187380663346102</v>
       </c>
-      <c r="O41" s="130">
+      <c r="O42" s="130">
         <f t="shared" si="6"/>
         <v>0.75525969897938783</v>
       </c>
-      <c r="P41" s="130">
+      <c r="P42" s="130">
         <f t="shared" si="6"/>
         <v>0.77864576638383243</v>
       </c>
-      <c r="Q41" s="130">
+      <c r="Q42" s="130">
         <f t="shared" si="6"/>
         <v>0.80203183378827703</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="B42" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="C42" s="123">
-        <f>1-C41</f>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="B43" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="C43" s="123">
+        <f>1-C42</f>
         <v>0.58952135442067854</v>
       </c>
-      <c r="D42" s="123">
-        <f t="shared" ref="D42:Q42" si="7">1-D41</f>
+      <c r="D43" s="123">
+        <f t="shared" ref="D43:Q43" si="7">1-D42</f>
         <v>0.4094703350177803</v>
       </c>
-      <c r="E42" s="123">
+      <c r="E43" s="123">
         <f t="shared" si="7"/>
         <v>0.40152498377676837</v>
       </c>
-      <c r="F42" s="123">
+      <c r="F43" s="123">
         <f t="shared" si="7"/>
         <v>0.55363904080774085</v>
       </c>
-      <c r="G42" s="123">
+      <c r="G43" s="123">
         <f t="shared" si="7"/>
         <v>0.40948360191525512</v>
       </c>
-      <c r="H42" s="123">
+      <c r="H43" s="123">
         <f t="shared" si="7"/>
         <v>0.41264336674794544</v>
       </c>
-      <c r="I42" s="123">
+      <c r="I43" s="123">
         <f t="shared" si="7"/>
         <v>0.41640949062551846</v>
       </c>
-      <c r="J42" s="123">
+      <c r="J43" s="123">
         <f t="shared" si="7"/>
         <v>0.27410850350502891</v>
       </c>
-      <c r="K42" s="123">
+      <c r="K43" s="123">
         <f t="shared" si="7"/>
         <v>0.33354018691588783</v>
       </c>
-      <c r="L42" s="123">
+      <c r="L43" s="123">
         <f t="shared" si="7"/>
         <v>0.34076134898554655</v>
       </c>
-      <c r="M42" s="130">
+      <c r="M43" s="130">
         <f t="shared" si="7"/>
         <v>0.2914483644119551</v>
       </c>
-      <c r="N42" s="130">
+      <c r="N43" s="130">
         <f t="shared" si="7"/>
         <v>0.26812619336653898</v>
       </c>
-      <c r="O42" s="130">
+      <c r="O43" s="130">
         <f t="shared" si="7"/>
         <v>0.24474030102061217</v>
       </c>
-      <c r="P42" s="130">
+      <c r="P43" s="130">
         <f t="shared" si="7"/>
         <v>0.22135423361616757</v>
       </c>
-      <c r="Q42" s="130">
+      <c r="Q43" s="130">
         <f t="shared" si="7"/>
         <v>0.19796816621172297</v>
       </c>
     </row>
-    <row r="43" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B43" s="117" t="s">
-        <v>165</v>
-      </c>
-      <c r="C43" s="126">
-        <f>C42*C8</f>
+    <row r="44" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B44" s="117" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" s="126">
+        <f>C43*C8</f>
         <v>0.12266098402481805</v>
       </c>
-      <c r="D43" s="126">
-        <f t="shared" ref="D43:Q43" si="8">D42*D8</f>
+      <c r="D44" s="126">
+        <f t="shared" ref="D44:Q44" si="8">D43*D8</f>
         <v>0.10109514347765816</v>
       </c>
-      <c r="E43" s="126">
+      <c r="E44" s="126">
         <f t="shared" si="8"/>
         <v>9.5268522510315951E-2</v>
       </c>
-      <c r="F43" s="126">
+      <c r="F44" s="126">
         <f t="shared" si="8"/>
         <v>0.14074866310160428</v>
       </c>
-      <c r="G43" s="126">
+      <c r="G44" s="126">
         <f t="shared" si="8"/>
         <v>0.10416890414008986</v>
       </c>
-      <c r="H43" s="126">
+      <c r="H44" s="126">
         <f t="shared" si="8"/>
         <v>0.12127936297279363</v>
       </c>
-      <c r="I43" s="126">
+      <c r="I44" s="126">
         <f t="shared" si="8"/>
         <v>0.13312822417016987</v>
       </c>
-      <c r="J43" s="126">
+      <c r="J44" s="126">
         <f t="shared" si="8"/>
         <v>8.1651459439829308E-2</v>
       </c>
-      <c r="K43" s="126">
+      <c r="K44" s="126">
         <f t="shared" si="8"/>
         <v>9.3116115969859525E-2</v>
       </c>
-      <c r="L43" s="126">
+      <c r="L44" s="126">
         <f t="shared" si="8"/>
         <v>0.10816783698789471</v>
       </c>
-      <c r="M43" s="136">
+      <c r="M44" s="136">
         <f t="shared" si="8"/>
         <v>9.994172712244867E-2</v>
       </c>
-      <c r="N43" s="136">
+      <c r="N44" s="136">
         <f t="shared" si="8"/>
         <v>8.7871981917016589E-2</v>
       </c>
-      <c r="O43" s="136">
+      <c r="O44" s="136">
         <f t="shared" si="8"/>
         <v>7.6814041682315065E-2</v>
       </c>
-      <c r="P43" s="136">
+      <c r="P44" s="136">
         <f t="shared" si="8"/>
         <v>6.7342464224160542E-2</v>
       </c>
-      <c r="Q43" s="136">
+      <c r="Q44" s="136">
         <f t="shared" si="8"/>
         <v>5.8480104477802934E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B44" s="44"/>
-      <c r="C44" s="119"/>
-      <c r="D44" s="119"/>
-      <c r="E44" s="119"/>
-      <c r="F44" s="119"/>
-      <c r="G44" s="119"/>
-      <c r="H44" s="119"/>
-      <c r="I44" s="119"/>
-      <c r="J44" s="119"/>
-      <c r="K44" s="119"/>
-      <c r="L44" s="119"/>
-      <c r="M44" s="119"/>
-      <c r="N44" s="119"/>
-      <c r="O44" s="119"/>
-      <c r="P44" s="119"/>
-      <c r="Q44" s="119"/>
+    <row r="45" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B45" s="44"/>
+      <c r="C45" s="119"/>
+      <c r="D45" s="119"/>
+      <c r="E45" s="119"/>
+      <c r="F45" s="119"/>
+      <c r="G45" s="119"/>
+      <c r="H45" s="119"/>
+      <c r="I45" s="119"/>
+      <c r="J45" s="119"/>
+      <c r="K45" s="119"/>
+      <c r="L45" s="119"/>
+      <c r="M45" s="119"/>
+      <c r="N45" s="119"/>
+      <c r="O45" s="119"/>
+      <c r="P45" s="119"/>
+      <c r="Q45" s="119"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13613,25 +13681,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B1" s="260" t="str">
+      <c r="B1" s="261" t="str">
         <f>"DuPont Models for "&amp;'Data Sheet'!B1</f>
         <v>DuPont Models for INFOSYS LTD</v>
       </c>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
-      <c r="N1" s="260"/>
-      <c r="O1" s="260"/>
-      <c r="P1" s="260"/>
-      <c r="Q1" s="260"/>
+      <c r="C1" s="261"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="261"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="261"/>
+      <c r="O1" s="261"/>
+      <c r="P1" s="261"/>
+      <c r="Q1" s="261"/>
     </row>
     <row r="2" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="116" t="str">
@@ -13766,7 +13834,7 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B4" s="153" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C4" s="154">
         <f>'Historical Financial Statement'!C23/'Historical Financial Statement'!C19</f>
@@ -13831,7 +13899,7 @@
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B5" s="153" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C5" s="154">
         <f>'Historical Financial Statement'!C19/'Historical Financial Statement'!C14</f>
@@ -13896,7 +13964,7 @@
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B6" s="153" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C6" s="157">
         <f>'Ratios Analysis'!C6</f>
@@ -13961,72 +14029,72 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B7" s="153" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C7" s="154">
-        <f>'Ratios Analysis'!C18</f>
+        <f>'Ratios Analysis'!C19</f>
         <v>0.82363977485928708</v>
       </c>
       <c r="D7" s="154">
-        <f>'Ratios Analysis'!D18</f>
+        <f>'Ratios Analysis'!D19</f>
         <v>0.88875726222132601</v>
       </c>
       <c r="E7" s="154">
-        <f>'Ratios Analysis'!E18</f>
+        <f>'Ratios Analysis'!E19</f>
         <v>0.98345347702995267</v>
       </c>
       <c r="F7" s="154">
-        <f>'Ratios Analysis'!F18</f>
+        <f>'Ratios Analysis'!F19</f>
         <v>0.98900871459694994</v>
       </c>
       <c r="G7" s="154">
-        <f>'Ratios Analysis'!G18</f>
+        <f>'Ratios Analysis'!G19</f>
         <v>0.9345276297309113</v>
       </c>
       <c r="H7" s="154">
-        <f>'Ratios Analysis'!H18</f>
+        <f>'Ratios Analysis'!H19</f>
         <v>1.0420803742000702</v>
       </c>
       <c r="I7" s="154">
-        <f>'Ratios Analysis'!I18</f>
+        <f>'Ratios Analysis'!I19</f>
         <v>1.1779431121384314</v>
       </c>
       <c r="J7" s="154">
-        <f>'Ratios Analysis'!J18</f>
+        <f>'Ratios Analysis'!J19</f>
         <v>1.1297603293633289</v>
       </c>
       <c r="K7" s="154">
-        <f>'Ratios Analysis'!K18</f>
+        <f>'Ratios Analysis'!K19</f>
         <v>1.1028113264995434</v>
       </c>
       <c r="L7" s="154">
-        <f>'Ratios Analysis'!L18</f>
+        <f>'Ratios Analysis'!L19</f>
         <v>1.1578995125998133</v>
       </c>
       <c r="M7" s="155">
-        <f>'Ratios Analysis'!M18</f>
+        <f>'Ratios Analysis'!M19</f>
         <v>1.1801093587817597</v>
       </c>
       <c r="N7" s="155">
-        <f>'Ratios Analysis'!N18</f>
+        <f>'Ratios Analysis'!N19</f>
         <v>1.1482689627518088</v>
       </c>
       <c r="O7" s="155">
-        <f>'Ratios Analysis'!O18</f>
+        <f>'Ratios Analysis'!O19</f>
         <v>1.1239544740988145</v>
       </c>
       <c r="P7" s="155">
-        <f>'Ratios Analysis'!P18</f>
+        <f>'Ratios Analysis'!P19</f>
         <v>1.0985024233150831</v>
       </c>
       <c r="Q7" s="156">
-        <f>'Ratios Analysis'!Q18</f>
+        <f>'Ratios Analysis'!Q19</f>
         <v>1.0770442419908408</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" s="148" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C8" s="160">
         <f>'Historical Financial Statement'!C60/SUM('Historical Financial Statement'!C29:C30)</f>
@@ -14090,28 +14158,28 @@
       </c>
     </row>
     <row r="10" spans="2:17" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="260" t="s">
-        <v>172</v>
-      </c>
-      <c r="C10" s="260"/>
-      <c r="D10" s="260"/>
-      <c r="E10" s="260"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="260"/>
-      <c r="H10" s="260"/>
-      <c r="I10" s="260"/>
-      <c r="J10" s="260"/>
-      <c r="K10" s="260"/>
-      <c r="L10" s="260"/>
-      <c r="M10" s="260"/>
-      <c r="N10" s="260"/>
-      <c r="O10" s="260"/>
-      <c r="P10" s="260"/>
-      <c r="Q10" s="260"/>
+      <c r="B10" s="261" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10" s="261"/>
+      <c r="D10" s="261"/>
+      <c r="E10" s="261"/>
+      <c r="F10" s="261"/>
+      <c r="G10" s="261"/>
+      <c r="H10" s="261"/>
+      <c r="I10" s="261"/>
+      <c r="J10" s="261"/>
+      <c r="K10" s="261"/>
+      <c r="L10" s="261"/>
+      <c r="M10" s="261"/>
+      <c r="N10" s="261"/>
+      <c r="O10" s="261"/>
+      <c r="P10" s="261"/>
+      <c r="Q10" s="261"/>
     </row>
     <row r="11" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="163" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C11" s="164">
         <f>C3*C7*C8</f>
@@ -14175,28 +14243,28 @@
       </c>
     </row>
     <row r="13" spans="2:17" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="260" t="s">
-        <v>173</v>
-      </c>
-      <c r="C13" s="260"/>
-      <c r="D13" s="260"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="260"/>
-      <c r="G13" s="260"/>
-      <c r="H13" s="260"/>
-      <c r="I13" s="260"/>
-      <c r="J13" s="260"/>
-      <c r="K13" s="260"/>
-      <c r="L13" s="260"/>
-      <c r="M13" s="260"/>
-      <c r="N13" s="260"/>
-      <c r="O13" s="260"/>
-      <c r="P13" s="260"/>
-      <c r="Q13" s="260"/>
+      <c r="B13" s="261" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="261"/>
+      <c r="D13" s="261"/>
+      <c r="E13" s="261"/>
+      <c r="F13" s="261"/>
+      <c r="G13" s="261"/>
+      <c r="H13" s="261"/>
+      <c r="I13" s="261"/>
+      <c r="J13" s="261"/>
+      <c r="K13" s="261"/>
+      <c r="L13" s="261"/>
+      <c r="M13" s="261"/>
+      <c r="N13" s="261"/>
+      <c r="O13" s="261"/>
+      <c r="P13" s="261"/>
+      <c r="Q13" s="261"/>
     </row>
     <row r="14" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B14" s="163" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C14" s="164">
         <f>C4*C5*C6*C7*C8</f>
@@ -14281,20 +14349,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B1" s="260" t="str">
+      <c r="B1" s="261" t="str">
         <f>"BETA Calculation for "&amp;'Data Sheet'!B1</f>
         <v>BETA Calculation for INFOSYS LTD</v>
       </c>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
+      <c r="C1" s="261"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="261"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
       <c r="M1" s="193"/>
       <c r="N1" s="193"/>
       <c r="O1" s="193"/>
@@ -14302,40 +14370,40 @@
       <c r="Q1" s="193"/>
     </row>
     <row r="2" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B2" s="259" t="s">
-        <v>187</v>
-      </c>
-      <c r="C2" s="259"/>
-      <c r="D2" s="259"/>
+      <c r="B2" s="264" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="264"/>
+      <c r="D2" s="264"/>
       <c r="E2" s="191"/>
-      <c r="F2" s="259" t="s">
-        <v>521</v>
-      </c>
-      <c r="G2" s="259"/>
+      <c r="F2" s="264" t="s">
+        <v>519</v>
+      </c>
+      <c r="G2" s="264"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B3" s="190" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C3" s="192" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D3" s="192" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E3" s="192"/>
       <c r="F3" s="192" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G3" s="192" t="s">
-        <v>517</v>
-      </c>
-      <c r="I3" s="261"/>
-      <c r="J3" s="261"/>
+        <v>515</v>
+      </c>
+      <c r="I3" s="265"/>
+      <c r="J3" s="265"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C4" s="256">
         <v>1153.8</v>
@@ -14353,14 +14421,14 @@
         <v>-2.5752075096373783E-2</v>
       </c>
       <c r="I4" s="194" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J4" s="195">
         <f>CORREL(D4:D525,G4:G525)</f>
         <v>0.40394328989545369</v>
       </c>
       <c r="K4" s="194" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L4" s="12">
         <f>_xlfn.COVARIANCE.S(D4:D525,G4:G525)</f>
@@ -14387,14 +14455,14 @@
         <v>1.844818479282373E-2</v>
       </c>
       <c r="I5" s="194" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J5" s="195">
         <f>_xlfn.STDEV.S(D4:D525)</f>
         <v>3.661319787923719E-2</v>
       </c>
       <c r="K5" s="194" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="L5" s="12">
         <f>_xlfn.VAR.S(G4:G525)</f>
@@ -14421,7 +14489,7 @@
         <v>4.0717823197722325E-4</v>
       </c>
       <c r="I6" s="194" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J6" s="195">
         <f>_xlfn.STDEV.S(G4:G525)</f>
@@ -14430,7 +14498,7 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C7" s="256">
         <v>1035</v>
@@ -14450,7 +14518,7 @@
     </row>
     <row r="8" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B8" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C8" s="256">
         <v>1000.2</v>
@@ -14468,7 +14536,7 @@
         <v>-1.037847162174288E-2</v>
       </c>
       <c r="I8" s="235" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J8" s="236">
         <f>J4*(J5/J6)</f>
@@ -14477,7 +14545,7 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C9" s="256">
         <v>1051.4000000000001</v>
@@ -14495,7 +14563,7 @@
         <v>-1.1348479216320984E-3</v>
       </c>
       <c r="I9" s="233" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J9" s="234">
         <f>J8/(1+('DCF Model'!C4/'DCF Model'!C3)*(1-'DCF Model'!C9))</f>
@@ -14525,7 +14593,7 @@
     </row>
     <row r="11" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B11" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C11" s="256">
         <v>1130</v>
@@ -14543,7 +14611,7 @@
         <v>-1.166242713639376E-2</v>
       </c>
       <c r="I11" s="235" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="J11" s="236">
         <f>L4/L5</f>
@@ -14552,7 +14620,7 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C12" s="256">
         <v>1144</v>
@@ -14572,7 +14640,7 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C13" s="256">
         <v>1121</v>
@@ -14632,7 +14700,7 @@
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C16" s="256">
         <v>1130.0999999999999</v>
@@ -14652,7 +14720,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C17" s="256">
         <v>1040.9000000000001</v>
@@ -14712,7 +14780,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C20" s="256">
         <v>1047.2</v>
@@ -14732,7 +14800,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C21" s="256">
         <v>1041.2</v>
@@ -14752,7 +14820,7 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C22" s="256">
         <v>1051.4000000000001</v>
@@ -14792,7 +14860,7 @@
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C24" s="256">
         <v>1197.5</v>
@@ -14812,7 +14880,7 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C25" s="256">
         <v>1160.9000000000001</v>
@@ -14832,7 +14900,7 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C26" s="256">
         <v>1174.5</v>
@@ -14892,7 +14960,7 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C29" s="256">
         <v>1181.8</v>
@@ -14912,7 +14980,7 @@
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C30" s="256">
         <v>1154.5999999999999</v>
@@ -14972,7 +15040,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C33" s="256">
         <v>1300.8</v>
@@ -14992,7 +15060,7 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C34" s="256">
         <v>1269.7</v>
@@ -15012,7 +15080,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C35" s="256">
         <v>1255.9000000000001</v>
@@ -15072,7 +15140,7 @@
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C38" s="256">
         <v>1300.0999999999999</v>
@@ -15092,7 +15160,7 @@
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C39" s="256">
         <v>1353.2</v>
@@ -15152,7 +15220,7 @@
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C42" s="256">
         <v>1641</v>
@@ -15172,7 +15240,7 @@
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C43" s="256">
         <v>1670.8</v>
@@ -15232,7 +15300,7 @@
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C46" s="256">
         <v>1640.4</v>
@@ -15252,7 +15320,7 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C47" s="256">
         <v>1656.1</v>
@@ -15272,7 +15340,7 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C48" s="256">
         <v>1638.7</v>
@@ -15312,7 +15380,7 @@
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C50" s="256">
         <v>1616.2</v>
@@ -15332,7 +15400,7 @@
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C51" s="256">
         <v>1560.1</v>
@@ -15352,7 +15420,7 @@
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C52" s="256">
         <v>1545</v>
@@ -15412,7 +15480,7 @@
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C55" s="256">
         <v>1482.3</v>
@@ -15432,7 +15500,7 @@
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C56" s="256">
         <v>1525.4</v>
@@ -15492,7 +15560,7 @@
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C59" s="256">
         <v>1446.6</v>
@@ -15512,7 +15580,7 @@
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C60" s="256">
         <v>1448.9</v>
@@ -15532,7 +15600,7 @@
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C61" s="256">
         <v>1540.2</v>
@@ -15572,7 +15640,7 @@
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C63" s="256">
         <v>1444.6</v>
@@ -15592,7 +15660,7 @@
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C64" s="256">
         <v>1469.6</v>
@@ -15612,7 +15680,7 @@
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C65" s="256">
         <v>1487.5</v>
@@ -15672,7 +15740,7 @@
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C68" s="256">
         <v>1469.6</v>
@@ -15692,7 +15760,7 @@
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C69" s="256">
         <v>1515.7</v>
@@ -15712,7 +15780,7 @@
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C70" s="256">
         <v>1586.1</v>
@@ -15752,7 +15820,7 @@
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C72" s="256">
         <v>1640.7</v>
@@ -15772,7 +15840,7 @@
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C73" s="256">
         <v>1608</v>
@@ -15792,7 +15860,7 @@
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C74" s="256">
         <v>1622.9</v>
@@ -15852,7 +15920,7 @@
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C77" s="256">
         <v>1562.7</v>
@@ -15872,7 +15940,7 @@
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C78" s="256">
         <v>1564.8</v>
@@ -15932,7 +16000,7 @@
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C81" s="256">
         <v>1506.8</v>
@@ -15952,7 +16020,7 @@
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C82" s="256">
         <v>1480.2</v>
@@ -15972,7 +16040,7 @@
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C83" s="256">
         <v>1419.5</v>
@@ -16012,7 +16080,7 @@
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C85" s="256">
         <v>1451.65</v>
@@ -16032,7 +16100,7 @@
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C86" s="256">
         <v>1570.65</v>
@@ -16052,7 +16120,7 @@
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C87" s="256">
         <v>1592.55</v>
@@ -16112,7 +16180,7 @@
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C90" s="256">
         <v>1687.7</v>
@@ -16132,7 +16200,7 @@
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C91" s="256">
         <v>1815</v>
@@ -16192,7 +16260,7 @@
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C94" s="256">
         <v>1879.8</v>
@@ -16212,7 +16280,7 @@
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C95" s="256">
         <v>1875.45</v>
@@ -16272,7 +16340,7 @@
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C98" s="256">
         <v>1938.75</v>
@@ -16292,7 +16360,7 @@
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C99" s="256">
         <v>1916.75</v>
@@ -16312,7 +16380,7 @@
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C100" s="256">
         <v>1922.15</v>
@@ -16372,7 +16440,7 @@
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C103" s="256">
         <v>1857.85</v>
@@ -16392,7 +16460,7 @@
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C104" s="256">
         <v>1902.25</v>
@@ -16452,7 +16520,7 @@
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C107" s="256">
         <v>1760.85</v>
@@ -16472,7 +16540,7 @@
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C108" s="256">
         <v>1862.05</v>
@@ -16492,7 +16560,7 @@
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C109" s="256">
         <v>1879.6</v>
@@ -16532,7 +16600,7 @@
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C111" s="256">
         <v>1918.15</v>
@@ -16552,7 +16620,7 @@
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C112" s="256">
         <v>1906.75</v>
@@ -16572,7 +16640,7 @@
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C113" s="256">
         <v>1905.75</v>
@@ -16632,7 +16700,7 @@
     </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B116" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C116" s="256">
         <v>1943.7</v>
@@ -16652,7 +16720,7 @@
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B117" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C117" s="256">
         <v>1862.1</v>
@@ -16712,7 +16780,7 @@
     </row>
     <row r="120" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B120" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C120" s="256">
         <v>1821.2</v>
@@ -16732,7 +16800,7 @@
     </row>
     <row r="121" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B121" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C121" s="256">
         <v>1878.9</v>
@@ -16752,7 +16820,7 @@
     </row>
     <row r="122" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B122" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C122" s="256">
         <v>1792.95</v>
@@ -16792,7 +16860,7 @@
     </row>
     <row r="124" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B124" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C124" s="256">
         <v>1647.45</v>
@@ -16812,7 +16880,7 @@
     </row>
     <row r="125" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B125" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C125" s="256">
         <v>1566.75</v>
@@ -16832,7 +16900,7 @@
     </row>
     <row r="126" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B126" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C126" s="256">
         <v>1532.7</v>
@@ -16892,7 +16960,7 @@
     </row>
     <row r="129" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B129" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C129" s="256">
         <v>1406.9</v>
@@ -16912,7 +16980,7 @@
     </row>
     <row r="130" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B130" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C130" s="256">
         <v>1456.89</v>
@@ -16972,7 +17040,7 @@
     </row>
     <row r="133" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B133" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C133" s="256">
         <v>1408.36</v>
@@ -16992,7 +17060,7 @@
     </row>
     <row r="134" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B134" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C134" s="256">
         <v>1422.23</v>
@@ -17012,7 +17080,7 @@
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B135" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C135" s="256">
         <v>1403.34</v>
@@ -17052,7 +17120,7 @@
     </row>
     <row r="137" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B137" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C137" s="256">
         <v>1470.81</v>
@@ -17072,7 +17140,7 @@
     </row>
     <row r="138" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B138" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C138" s="256">
         <v>1489.66</v>
@@ -17092,7 +17160,7 @@
     </row>
     <row r="139" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B139" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C139" s="256">
         <v>1500.39</v>
@@ -17152,7 +17220,7 @@
     </row>
     <row r="142" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B142" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C142" s="256">
         <v>1645.43</v>
@@ -17172,7 +17240,7 @@
     </row>
     <row r="143" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B143" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C143" s="256">
         <v>1667.45</v>
@@ -17232,7 +17300,7 @@
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B146" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C146" s="256">
         <v>1683.86</v>
@@ -17252,7 +17320,7 @@
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B147" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C147" s="256">
         <v>1659.75</v>
@@ -17272,7 +17340,7 @@
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B148" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C148" s="256">
         <v>1649.9</v>
@@ -17312,7 +17380,7 @@
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B150" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C150" s="256">
         <v>1523.96</v>
@@ -17332,7 +17400,7 @@
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B151" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C151" s="256">
         <v>1534.25</v>
@@ -17352,7 +17420,7 @@
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B152" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C152" s="256">
         <v>1554.14</v>
@@ -17412,7 +17480,7 @@
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B155" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C155" s="256">
         <v>1444.16</v>
@@ -17432,7 +17500,7 @@
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B156" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C156" s="256">
         <v>1429.34</v>
@@ -17492,7 +17560,7 @@
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B159" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C159" s="256">
         <v>1381.27</v>
@@ -17512,7 +17580,7 @@
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B160" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C160" s="256">
         <v>1372.61</v>
@@ -17532,7 +17600,7 @@
     </row>
     <row r="161" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B161" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C161" s="256">
         <v>1419.25</v>
@@ -17592,7 +17660,7 @@
     </row>
     <row r="164" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B164" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C164" s="256">
         <v>1427.41</v>
@@ -17612,7 +17680,7 @@
     </row>
     <row r="165" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B165" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C165" s="256">
         <v>1487.77</v>
@@ -17672,7 +17740,7 @@
     </row>
     <row r="168" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B168" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C168" s="256">
         <v>1435.76</v>
@@ -17692,7 +17760,7 @@
     </row>
     <row r="169" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B169" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C169" s="256">
         <v>1412.14</v>
@@ -17712,7 +17780,7 @@
     </row>
     <row r="170" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B170" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C170" s="256">
         <v>1381.02</v>
@@ -17752,7 +17820,7 @@
     </row>
     <row r="172" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B172" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C172" s="256">
         <v>1370.63</v>
@@ -17772,7 +17840,7 @@
     </row>
     <row r="173" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B173" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C173" s="256">
         <v>1332.99</v>
@@ -17792,7 +17860,7 @@
     </row>
     <row r="174" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B174" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C174" s="256">
         <v>1324.14</v>
@@ -17852,7 +17920,7 @@
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B177" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C177" s="256">
         <v>1328.02</v>
@@ -17872,7 +17940,7 @@
     </row>
     <row r="178" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B178" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C178" s="256">
         <v>1257.9100000000001</v>
@@ -17932,7 +18000,7 @@
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B181" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C181" s="256">
         <v>1291.72</v>
@@ -17952,7 +18020,7 @@
     </row>
     <row r="182" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B182" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C182" s="256">
         <v>1310.07</v>
@@ -17972,7 +18040,7 @@
     </row>
     <row r="183" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B183" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C183" s="256">
         <v>1261.79</v>
@@ -18012,7 +18080,7 @@
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B185" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C185" s="256">
         <v>1252.04</v>
@@ -18032,7 +18100,7 @@
     </row>
     <row r="186" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B186" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C186" s="256">
         <v>1245.73</v>
@@ -18052,7 +18120,7 @@
     </row>
     <row r="187" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B187" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C187" s="256">
         <v>1220.47</v>
@@ -18112,7 +18180,7 @@
     </row>
     <row r="190" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B190" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C190" s="256">
         <v>1419.95</v>
@@ -18132,7 +18200,7 @@
     </row>
     <row r="191" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B191" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C191" s="256">
         <v>1372.91</v>
@@ -18192,7 +18260,7 @@
     </row>
     <row r="194" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B194" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C194" s="256">
         <v>1471.01</v>
@@ -18212,7 +18280,7 @@
     </row>
     <row r="195" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B195" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C195" s="256">
         <v>1541.96</v>
@@ -18272,7 +18340,7 @@
     </row>
     <row r="198" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B198" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C198" s="256">
         <v>1590.44</v>
@@ -18292,7 +18360,7 @@
     </row>
     <row r="199" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B199" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C199" s="256">
         <v>1510.64</v>
@@ -18312,7 +18380,7 @@
     </row>
     <row r="200" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B200" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C200" s="256">
         <v>1517</v>
@@ -18372,7 +18440,7 @@
     </row>
     <row r="203" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B203" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C203" s="256">
         <v>1499.75</v>
@@ -18392,7 +18460,7 @@
     </row>
     <row r="204" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B204" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C204" s="256">
         <v>1488.71</v>
@@ -18452,7 +18520,7 @@
     </row>
     <row r="207" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B207" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C207" s="256">
         <v>1628.72</v>
@@ -18472,7 +18540,7 @@
     </row>
     <row r="208" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B208" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C208" s="256">
         <v>1626.48</v>
@@ -18492,7 +18560,7 @@
     </row>
     <row r="209" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B209" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C209" s="256">
         <v>1584.47</v>
@@ -18532,7 +18600,7 @@
     </row>
     <row r="211" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B211" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C211" s="256">
         <v>1505.52</v>
@@ -18552,7 +18620,7 @@
     </row>
     <row r="212" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B212" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C212" s="256">
         <v>1504.77</v>
@@ -18572,7 +18640,7 @@
     </row>
     <row r="213" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B213" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C213" s="256">
         <v>1492.09</v>
@@ -18632,7 +18700,7 @@
     </row>
     <row r="216" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B216" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C216" s="256">
         <v>1405.53</v>
@@ -18652,7 +18720,7 @@
     </row>
     <row r="217" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B217" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C217" s="256">
         <v>1357.8</v>
@@ -18712,7 +18780,7 @@
     </row>
     <row r="220" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B220" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C220" s="256">
         <v>1444.86</v>
@@ -18732,7 +18800,7 @@
     </row>
     <row r="221" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B221" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C221" s="256">
         <v>1513.02</v>
@@ -18752,7 +18820,7 @@
     </row>
     <row r="222" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B222" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C222" s="256">
         <v>1588.15</v>
@@ -18792,7 +18860,7 @@
     </row>
     <row r="224" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B224" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C224" s="256">
         <v>1607.59</v>
@@ -18812,7 +18880,7 @@
     </row>
     <row r="225" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B225" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C225" s="256">
         <v>1541.02</v>
@@ -18832,7 +18900,7 @@
     </row>
     <row r="226" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B226" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C226" s="256">
         <v>1497.86</v>
@@ -18892,7 +18960,7 @@
     </row>
     <row r="229" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B229" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C229" s="256">
         <v>1471.11</v>
@@ -18912,7 +18980,7 @@
     </row>
     <row r="230" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B230" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C230" s="256">
         <v>1433.02</v>
@@ -18972,7 +19040,7 @@
     </row>
     <row r="233" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B233" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C233" s="256">
         <v>1513.17</v>
@@ -18992,7 +19060,7 @@
     </row>
     <row r="234" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C234" s="256">
         <v>1453.16</v>
@@ -19012,7 +19080,7 @@
     </row>
     <row r="235" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B235" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C235" s="256">
         <v>1446.99</v>
@@ -19072,7 +19140,7 @@
     </row>
     <row r="238" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B238" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C238" s="256">
         <v>1558.77</v>
@@ -19092,7 +19160,7 @@
     </row>
     <row r="239" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B239" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C239" s="256">
         <v>1576.56</v>
@@ -19152,7 +19220,7 @@
     </row>
     <row r="242" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B242" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C242" s="256">
         <v>1892.88</v>
@@ -19172,7 +19240,7 @@
     </row>
     <row r="243" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B243" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C243" s="256">
         <v>1866.03</v>
@@ -19192,7 +19260,7 @@
     </row>
     <row r="244" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B244" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C244" s="256">
         <v>1844.21</v>
@@ -19232,7 +19300,7 @@
     </row>
     <row r="246" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B246" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C246" s="256">
         <v>1713.64</v>
@@ -19252,7 +19320,7 @@
     </row>
     <row r="247" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B247" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C247" s="256">
         <v>1685.1</v>
@@ -19272,7 +19340,7 @@
     </row>
     <row r="248" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B248" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C248" s="256">
         <v>1697.38</v>
@@ -19312,7 +19380,7 @@
     </row>
     <row r="250" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B250" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C250" s="256">
         <v>1731.34</v>
@@ -19332,7 +19400,7 @@
     </row>
     <row r="251" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B251" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C251" s="256">
         <v>1676.75</v>
@@ -19352,7 +19420,7 @@
     </row>
     <row r="252" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B252" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C252" s="256">
         <v>1775.69</v>
@@ -19412,7 +19480,7 @@
     </row>
     <row r="255" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B255" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C255" s="256">
         <v>1877.17</v>
@@ -19432,7 +19500,7 @@
     </row>
     <row r="256" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B256" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C256" s="256">
         <v>1853.06</v>
@@ -19492,7 +19560,7 @@
     </row>
     <row r="259" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B259" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C259" s="256">
         <v>1725.82</v>
@@ -19512,7 +19580,7 @@
     </row>
     <row r="260" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B260" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C260" s="256">
         <v>1682.17</v>
@@ -19532,7 +19600,7 @@
     </row>
     <row r="261" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B261" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C261" s="256">
         <v>1769.43</v>
@@ -19572,7 +19640,7 @@
     </row>
     <row r="263" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B263" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C263" s="256">
         <v>1699.12</v>
@@ -19592,7 +19660,7 @@
     </row>
     <row r="264" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B264" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C264" s="256">
         <v>1658.4</v>
@@ -19612,7 +19680,7 @@
     </row>
     <row r="265" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B265" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C265" s="256">
         <v>1710.16</v>
@@ -19672,7 +19740,7 @@
     </row>
     <row r="268" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B268" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C268" s="256">
         <v>1655.82</v>
@@ -19692,7 +19760,7 @@
     </row>
     <row r="269" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B269" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C269" s="256">
         <v>1753.96</v>
@@ -19752,7 +19820,7 @@
     </row>
     <row r="272" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B272" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C272" s="256">
         <v>1691.12</v>
@@ -19772,7 +19840,7 @@
     </row>
     <row r="273" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B273" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C273" s="256">
         <v>1699.22</v>
@@ -19792,7 +19860,7 @@
     </row>
     <row r="274" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B274" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C274" s="256">
         <v>1723.24</v>
@@ -19852,7 +19920,7 @@
     </row>
     <row r="277" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B277" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C277" s="256">
         <v>1601.47</v>
@@ -19872,7 +19940,7 @@
     </row>
     <row r="278" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B278" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C278" s="256">
         <v>1581.54</v>
@@ -19932,7 +20000,7 @@
     </row>
     <row r="281" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B281" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C281" s="256">
         <v>1559.01</v>
@@ -19952,7 +20020,7 @@
     </row>
     <row r="282" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B282" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C282" s="256">
         <v>1565.38</v>
@@ -19972,7 +20040,7 @@
     </row>
     <row r="283" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B283" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C283" s="256">
         <v>1494.88</v>
@@ -20012,7 +20080,7 @@
     </row>
     <row r="285" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B285" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C285" s="256">
         <v>1377.89</v>
@@ -20032,7 +20100,7 @@
     </row>
     <row r="286" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B286" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C286" s="256">
         <v>1397.18</v>
@@ -20052,7 +20120,7 @@
     </row>
     <row r="287" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B287" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C287" s="256">
         <v>1346.91</v>
@@ -20112,7 +20180,7 @@
     </row>
     <row r="290" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B290" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C290" s="256">
         <v>1346.76</v>
@@ -20132,7 +20200,7 @@
     </row>
     <row r="291" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B291" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C291" s="256">
         <v>1326.32</v>
@@ -20192,7 +20260,7 @@
     </row>
     <row r="294" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B294" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C294" s="256">
         <v>1377.44</v>
@@ -20212,7 +20280,7 @@
     </row>
     <row r="295" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B295" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C295" s="256">
         <v>1328.71</v>
@@ -20232,7 +20300,7 @@
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B296" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C296" s="256">
         <v>1336.92</v>
@@ -20272,7 +20340,7 @@
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B298" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C298" s="256">
         <v>1309.32</v>
@@ -20292,7 +20360,7 @@
     </row>
     <row r="299" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B299" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C299" s="256">
         <v>1246.28</v>
@@ -20312,7 +20380,7 @@
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B300" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C300" s="256">
         <v>1284.06</v>
@@ -20352,7 +20420,7 @@
     </row>
     <row r="302" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B302" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C302" s="256">
         <v>1264.97</v>
@@ -20372,7 +20440,7 @@
     </row>
     <row r="303" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B303" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C303" s="256">
         <v>1232.1099999999999</v>
@@ -20392,7 +20460,7 @@
     </row>
     <row r="304" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B304" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C304" s="256">
         <v>1333.34</v>
@@ -20452,7 +20520,7 @@
     </row>
     <row r="307" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B307" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C307" s="256">
         <v>1253.3900000000001</v>
@@ -20472,7 +20540,7 @@
     </row>
     <row r="308" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B308" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C308" s="256">
         <v>1229.1199999999999</v>
@@ -20492,7 +20560,7 @@
     </row>
     <row r="309" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B309" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C309" s="256">
         <v>1183.1300000000001</v>
@@ -20532,7 +20600,7 @@
     </row>
     <row r="311" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B311" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C311" s="256">
         <v>1128.29</v>
@@ -20552,7 +20620,7 @@
     </row>
     <row r="312" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B312" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C312" s="256">
         <v>1093.8399999999999</v>
@@ -20572,7 +20640,7 @@
     </row>
     <row r="313" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B313" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C313" s="256">
         <v>1097.17</v>
@@ -20632,7 +20700,7 @@
     </row>
     <row r="316" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B316" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C316" s="256">
         <v>1054.6600000000001</v>
@@ -20652,7 +20720,7 @@
     </row>
     <row r="317" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B317" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C317" s="256">
         <v>1116.21</v>
@@ -20712,7 +20780,7 @@
     </row>
     <row r="320" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B320" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C320" s="256">
         <v>1011.95</v>
@@ -20732,7 +20800,7 @@
     </row>
     <row r="321" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B321" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C321" s="256">
         <v>1005.78</v>
@@ -20752,7 +20820,7 @@
     </row>
     <row r="322" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B322" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C322" s="257">
         <v>996.53</v>
@@ -20792,7 +20860,7 @@
     </row>
     <row r="324" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B324" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C324" s="257">
         <v>914</v>
@@ -20812,7 +20880,7 @@
     </row>
     <row r="325" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B325" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C325" s="257">
         <v>930.01</v>
@@ -20832,7 +20900,7 @@
     </row>
     <row r="326" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B326" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C326" s="257">
         <v>943.48</v>
@@ -20892,7 +20960,7 @@
     </row>
     <row r="329" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B329" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C329" s="257">
         <v>960.59</v>
@@ -20912,7 +20980,7 @@
     </row>
     <row r="330" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B330" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C330" s="257">
         <v>917.68</v>
@@ -20972,7 +21040,7 @@
     </row>
     <row r="333" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B333" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C333" s="257">
         <v>758.43</v>
@@ -20992,7 +21060,7 @@
     </row>
     <row r="334" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B334" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C334" s="257">
         <v>744.01</v>
@@ -21012,7 +21080,7 @@
     </row>
     <row r="335" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B335" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C335" s="257">
         <v>701.6</v>
@@ -21052,7 +21120,7 @@
     </row>
     <row r="337" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B337" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C337" s="257">
         <v>699.61</v>
@@ -21072,7 +21140,7 @@
     </row>
     <row r="338" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B338" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C338" s="257">
         <v>687.13</v>
@@ -21092,7 +21160,7 @@
     </row>
     <row r="339" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B339" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C339" s="257">
         <v>688.47</v>
@@ -21152,7 +21220,7 @@
     </row>
     <row r="342" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B342" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C342" s="257">
         <v>711.49</v>
@@ -21172,7 +21240,7 @@
     </row>
     <row r="343" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B343" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C343" s="257">
         <v>654.30999999999995</v>
@@ -21232,7 +21300,7 @@
     </row>
     <row r="346" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B346" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C346" s="257">
         <v>582.41999999999996</v>
@@ -21252,7 +21320,7 @@
     </row>
     <row r="347" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B347" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C347" s="257">
         <v>649.04</v>
@@ -21272,7 +21340,7 @@
     </row>
     <row r="348" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B348" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C348" s="257">
         <v>581.91999999999996</v>
@@ -21332,7 +21400,7 @@
     </row>
     <row r="351" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B351" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C351" s="257">
         <v>727.6</v>
@@ -21352,7 +21420,7 @@
     </row>
     <row r="352" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B352" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C352" s="257">
         <v>792.53</v>
@@ -21412,7 +21480,7 @@
     </row>
     <row r="355" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B355" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C355" s="257">
         <v>771.6</v>
@@ -21432,7 +21500,7 @@
     </row>
     <row r="356" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B356" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C356" s="257">
         <v>778.36</v>
@@ -21492,7 +21560,7 @@
     </row>
     <row r="359" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B359" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C359" s="257">
         <v>741.82</v>
@@ -21512,7 +21580,7 @@
     </row>
     <row r="360" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B360" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C360" s="257">
         <v>732.82</v>
@@ -21532,7 +21600,7 @@
     </row>
     <row r="361" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B361" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C361" s="257">
         <v>727.45</v>
@@ -21592,7 +21660,7 @@
     </row>
     <row r="364" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B364" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C364" s="257">
         <v>692.45</v>
@@ -21612,7 +21680,7 @@
     </row>
     <row r="365" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B365" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C365" s="257">
         <v>689.32</v>
@@ -21672,7 +21740,7 @@
     </row>
     <row r="368" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B368" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C368" s="257">
         <v>684.04</v>
@@ -21692,7 +21760,7 @@
     </row>
     <row r="369" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B369" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C369" s="257">
         <v>633.88</v>
@@ -21712,7 +21780,7 @@
     </row>
     <row r="370" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B370" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C370" s="257">
         <v>763.55</v>
@@ -21752,7 +21820,7 @@
     </row>
     <row r="372" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B372" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C372" s="257">
         <v>789</v>
@@ -21772,7 +21840,7 @@
     </row>
     <row r="373" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B373" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C373" s="257">
         <v>777.82</v>
@@ -21792,7 +21860,7 @@
     </row>
     <row r="374" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B374" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C374" s="257">
         <v>800.49</v>
@@ -21852,7 +21920,7 @@
     </row>
     <row r="377" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B377" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C377" s="257">
         <v>810.33</v>
@@ -21872,7 +21940,7 @@
     </row>
     <row r="378" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B378" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C378" s="257">
         <v>797.7</v>
@@ -21932,7 +22000,7 @@
     </row>
     <row r="381" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B381" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C381" s="257">
         <v>771.25</v>
@@ -21952,7 +22020,7 @@
     </row>
     <row r="382" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B382" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C382" s="257">
         <v>782.59</v>
@@ -21972,7 +22040,7 @@
     </row>
     <row r="383" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B383" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C383" s="257">
         <v>781</v>
@@ -22012,7 +22080,7 @@
     </row>
     <row r="385" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B385" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C385" s="257">
         <v>713.98</v>
@@ -22032,7 +22100,7 @@
     </row>
     <row r="386" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B386" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C386" s="257">
         <v>727.9</v>
@@ -22052,7 +22120,7 @@
     </row>
     <row r="387" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B387" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C387" s="257">
         <v>746</v>
@@ -22112,7 +22180,7 @@
     </row>
     <row r="390" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B390" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C390" s="257">
         <v>733.62</v>
@@ -22132,7 +22200,7 @@
     </row>
     <row r="391" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B391" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C391" s="257">
         <v>705.23</v>
@@ -22192,7 +22260,7 @@
     </row>
     <row r="394" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B394" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C394" s="257">
         <v>719.54</v>
@@ -22212,7 +22280,7 @@
     </row>
     <row r="395" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B395" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C395" s="257">
         <v>733.86</v>
@@ -22232,7 +22300,7 @@
     </row>
     <row r="396" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B396" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C396" s="257">
         <v>713.03</v>
@@ -22272,7 +22340,7 @@
     </row>
     <row r="398" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B398" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C398" s="257">
         <v>755.04</v>
@@ -22292,7 +22360,7 @@
     </row>
     <row r="399" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B399" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C399" s="257">
         <v>743.85</v>
@@ -22312,7 +22380,7 @@
     </row>
     <row r="400" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B400" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C400" s="257">
         <v>743.1</v>
@@ -22372,7 +22440,7 @@
     </row>
     <row r="403" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B403" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C403" s="257">
         <v>741.9</v>
@@ -22392,7 +22460,7 @@
     </row>
     <row r="404" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B404" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C404" s="257">
         <v>734.95</v>
@@ -22452,7 +22520,7 @@
     </row>
     <row r="407" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B407" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C407" s="257">
         <v>757.05</v>
@@ -22472,7 +22540,7 @@
     </row>
     <row r="408" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B408" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C408" s="257">
         <v>730.35</v>
@@ -22492,7 +22560,7 @@
     </row>
     <row r="409" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B409" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C409" s="257">
         <v>726.95</v>
@@ -22532,7 +22600,7 @@
     </row>
     <row r="411" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B411" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C411" s="257">
         <v>657.44</v>
@@ -22552,7 +22620,7 @@
     </row>
     <row r="412" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B412" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C412" s="257">
         <v>653.36</v>
@@ -22572,7 +22640,7 @@
     </row>
     <row r="413" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B413" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C413" s="257">
         <v>642.66999999999996</v>
@@ -22632,7 +22700,7 @@
     </row>
     <row r="416" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B416" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C416" s="257">
         <v>663.8</v>
@@ -22652,7 +22720,7 @@
     </row>
     <row r="417" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B417" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C417" s="257">
         <v>617.36</v>
@@ -22712,7 +22780,7 @@
     </row>
     <row r="420" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B420" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C420" s="257">
         <v>658.63</v>
@@ -22732,7 +22800,7 @@
     </row>
     <row r="421" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B421" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C421" s="257">
         <v>630.14</v>
@@ -22752,7 +22820,7 @@
     </row>
     <row r="422" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B422" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C422" s="257">
         <v>679.81</v>
@@ -22792,7 +22860,7 @@
     </row>
     <row r="424" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B424" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C424" s="257">
         <v>720.64</v>
@@ -22812,7 +22880,7 @@
     </row>
     <row r="425" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B425" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C425" s="257">
         <v>726.06</v>
@@ -22832,7 +22900,7 @@
     </row>
     <row r="426" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B426" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C426" s="257">
         <v>701.44</v>
@@ -22892,7 +22960,7 @@
     </row>
     <row r="429" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B429" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C429" s="257">
         <v>716.61</v>
@@ -22912,7 +22980,7 @@
     </row>
     <row r="430" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B430" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C430" s="257">
         <v>685.38</v>
@@ -22972,7 +23040,7 @@
     </row>
     <row r="433" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B433" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C433" s="257">
         <v>678.32</v>
@@ -22992,7 +23060,7 @@
     </row>
     <row r="434" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B434" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C434" s="257">
         <v>682.97</v>
@@ -23012,7 +23080,7 @@
     </row>
     <row r="435" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B435" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C435" s="257">
         <v>670.36</v>
@@ -23072,7 +23140,7 @@
     </row>
     <row r="438" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B438" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C438" s="257">
         <v>650.03</v>
@@ -23092,7 +23160,7 @@
     </row>
     <row r="439" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B439" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C439" s="257">
         <v>620.51</v>
@@ -23152,7 +23220,7 @@
     </row>
     <row r="442" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B442" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C442" s="257">
         <v>602.29999999999995</v>
@@ -23172,7 +23240,7 @@
     </row>
     <row r="443" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B443" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C443" s="257">
         <v>606</v>
@@ -23192,7 +23260,7 @@
     </row>
     <row r="444" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B444" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C444" s="257">
         <v>583.75</v>
@@ -23232,7 +23300,7 @@
     </row>
     <row r="446" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B446" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C446" s="257">
         <v>578.77</v>
@@ -23252,7 +23320,7 @@
     </row>
     <row r="447" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B447" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C447" s="257">
         <v>584.74</v>
@@ -23272,7 +23340,7 @@
     </row>
     <row r="448" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B448" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C448" s="257">
         <v>581.41</v>
@@ -23332,7 +23400,7 @@
     </row>
     <row r="451" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B451" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C451" s="257">
         <v>558.39</v>
@@ -23352,7 +23420,7 @@
     </row>
     <row r="452" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B452" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C452" s="257">
         <v>576.04999999999995</v>
@@ -23412,7 +23480,7 @@
     </row>
     <row r="455" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B455" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C455" s="257">
         <v>572.66999999999996</v>
@@ -23432,7 +23500,7 @@
     </row>
     <row r="456" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B456" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C456" s="257">
         <v>570.16</v>
@@ -23492,7 +23560,7 @@
     </row>
     <row r="459" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B459" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C459" s="257">
         <v>564.04</v>
@@ -23512,7 +23580,7 @@
     </row>
     <row r="460" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B460" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C460" s="257">
         <v>579.9</v>
@@ -23532,7 +23600,7 @@
     </row>
     <row r="461" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B461" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C461" s="257">
         <v>564.14</v>
@@ -23572,7 +23640,7 @@
     </row>
     <row r="463" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B463" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C463" s="257">
         <v>499.29</v>
@@ -23592,7 +23660,7 @@
     </row>
     <row r="464" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B464" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C464" s="257">
         <v>514.11</v>
@@ -23612,7 +23680,7 @@
     </row>
     <row r="465" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B465" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C465" s="257">
         <v>512.78</v>
@@ -23672,7 +23740,7 @@
     </row>
     <row r="468" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B468" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C468" s="257">
         <v>473.04</v>
@@ -23692,7 +23760,7 @@
     </row>
     <row r="469" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B469" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C469" s="257">
         <v>498.08</v>
@@ -23752,7 +23820,7 @@
     </row>
     <row r="472" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B472" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C472" s="257">
         <v>457.18</v>
@@ -23772,7 +23840,7 @@
     </row>
     <row r="473" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B473" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C473" s="257">
         <v>466.9</v>
@@ -23792,7 +23860,7 @@
     </row>
     <row r="474" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B474" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C474" s="257">
         <v>457.33</v>
@@ -23852,7 +23920,7 @@
     </row>
     <row r="477" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B477" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C477" s="257">
         <v>443.98</v>
@@ -23872,7 +23940,7 @@
     </row>
     <row r="478" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B478" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C478" s="257">
         <v>443.19</v>
@@ -23932,7 +24000,7 @@
     </row>
     <row r="481" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B481" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C481" s="257">
         <v>456.37</v>
@@ -23952,7 +24020,7 @@
     </row>
     <row r="482" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B482" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C482" s="257">
         <v>452.5</v>
@@ -23972,7 +24040,7 @@
     </row>
     <row r="483" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B483" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C483" s="257">
         <v>458</v>
@@ -24012,7 +24080,7 @@
     </row>
     <row r="485" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B485" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C485" s="257">
         <v>488.02</v>
@@ -24032,7 +24100,7 @@
     </row>
     <row r="486" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B486" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C486" s="257">
         <v>494.76</v>
@@ -24052,7 +24120,7 @@
     </row>
     <row r="487" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B487" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C487" s="257">
         <v>486.21</v>
@@ -24112,7 +24180,7 @@
     </row>
     <row r="490" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B490" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C490" s="257">
         <v>464.11</v>
@@ -24132,7 +24200,7 @@
     </row>
     <row r="491" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B491" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C491" s="257">
         <v>467.93</v>
@@ -24192,7 +24260,7 @@
     </row>
     <row r="494" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B494" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C494" s="257">
         <v>480.92</v>
@@ -24212,7 +24280,7 @@
     </row>
     <row r="495" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B495" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C495" s="257">
         <v>493.94</v>
@@ -24232,7 +24300,7 @@
     </row>
     <row r="496" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B496" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C496" s="257">
         <v>475.22</v>
@@ -24272,7 +24340,7 @@
     </row>
     <row r="498" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B498" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C498" s="257">
         <v>462.1</v>
@@ -24292,7 +24360,7 @@
     </row>
     <row r="499" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B499" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C499" s="257">
         <v>455.87</v>
@@ -24312,7 +24380,7 @@
     </row>
     <row r="500" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B500" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C500" s="257">
         <v>458.23</v>
@@ -24372,7 +24440,7 @@
     </row>
     <row r="503" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B503" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C503" s="257">
         <v>507.12</v>
@@ -24392,7 +24460,7 @@
     </row>
     <row r="504" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B504" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C504" s="257">
         <v>511.65</v>
@@ -24452,7 +24520,7 @@
     </row>
     <row r="507" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B507" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C507" s="257">
         <v>511.56</v>
@@ -24472,7 +24540,7 @@
     </row>
     <row r="508" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B508" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C508" s="257">
         <v>500.47</v>
@@ -24532,7 +24600,7 @@
     </row>
     <row r="511" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B511" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C511" s="257">
         <v>464.38</v>
@@ -24552,7 +24620,7 @@
     </row>
     <row r="512" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B512" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C512" s="257">
         <v>467.38</v>
@@ -24572,7 +24640,7 @@
     </row>
     <row r="513" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B513" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C513" s="257">
         <v>470.63</v>
@@ -24632,7 +24700,7 @@
     </row>
     <row r="516" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B516" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C516" s="257">
         <v>501.34</v>
@@ -24652,7 +24720,7 @@
     </row>
     <row r="517" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B517" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C517" s="257">
         <v>490.35</v>
@@ -24712,7 +24780,7 @@
     </row>
     <row r="520" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B520" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C520" s="257">
         <v>478.47</v>
@@ -24732,7 +24800,7 @@
     </row>
     <row r="521" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B521" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C521" s="257">
         <v>484.92</v>
@@ -24752,7 +24820,7 @@
     </row>
     <row r="522" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B522" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C522" s="257">
         <v>456.39</v>
@@ -24792,7 +24860,7 @@
     </row>
     <row r="524" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B524" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C524" s="257">
         <v>481.69</v>
@@ -24812,7 +24880,7 @@
     </row>
     <row r="525" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B525" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C525" s="257">
         <v>494.84</v>
@@ -24857,25 +24925,25 @@
       <c r="A1" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="260" t="str">
+      <c r="B1" s="261" t="str">
         <f>"Calculation for "&amp;'Data Sheet'!B1</f>
         <v>Calculation for INFOSYS LTD</v>
       </c>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
-      <c r="N1" s="260"/>
-      <c r="O1" s="260"/>
-      <c r="P1" s="260"/>
-      <c r="Q1" s="260"/>
+      <c r="C1" s="261"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="261"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="261"/>
+      <c r="O1" s="261"/>
+      <c r="P1" s="261"/>
+      <c r="Q1" s="261"/>
     </row>
     <row r="2" spans="1:23" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="21" t="str">
@@ -25023,13 +25091,13 @@
         <f t="shared" si="1"/>
         <v>288542.62039229897</v>
       </c>
-      <c r="S3" s="264" t="s">
-        <v>113</v>
-      </c>
-      <c r="T3" s="265"/>
-      <c r="U3" s="265"/>
-      <c r="V3" s="265"/>
-      <c r="W3" s="266"/>
+      <c r="S3" s="266" t="s">
+        <v>111</v>
+      </c>
+      <c r="T3" s="267"/>
+      <c r="U3" s="267"/>
+      <c r="V3" s="267"/>
+      <c r="W3" s="268"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.45">
       <c r="B4" s="98" t="s">
@@ -25363,13 +25431,13 @@
         <f t="shared" si="10"/>
         <v>11333.667392453124</v>
       </c>
-      <c r="S10" s="264" t="s">
-        <v>121</v>
-      </c>
-      <c r="T10" s="265"/>
-      <c r="U10" s="265"/>
-      <c r="V10" s="265"/>
-      <c r="W10" s="266"/>
+      <c r="S10" s="266" t="s">
+        <v>119</v>
+      </c>
+      <c r="T10" s="267"/>
+      <c r="U10" s="267"/>
+      <c r="V10" s="267"/>
+      <c r="W10" s="268"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="B11" s="103" t="s">
@@ -25792,13 +25860,13 @@
         <f t="shared" si="29"/>
         <v>34804.175896069559</v>
       </c>
-      <c r="S18" s="264" t="s">
-        <v>124</v>
-      </c>
-      <c r="T18" s="265"/>
-      <c r="U18" s="265"/>
-      <c r="V18" s="265"/>
-      <c r="W18" s="266"/>
+      <c r="S18" s="266" t="s">
+        <v>122</v>
+      </c>
+      <c r="T18" s="267"/>
+      <c r="U18" s="267"/>
+      <c r="V18" s="267"/>
+      <c r="W18" s="268"/>
     </row>
     <row r="19" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B19" s="105" t="str">
@@ -25888,7 +25956,7 @@
     </row>
     <row r="20" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B20" s="103" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C20" s="85">
         <f>C19/C18</f>
@@ -26161,7 +26229,7 @@
     </row>
     <row r="25" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B25" s="103" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C25" s="85">
         <f>C24/C3</f>
@@ -26395,7 +26463,7 @@
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B30" s="103" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C30" s="85">
         <f>IFERROR(C29/C28,0)</f>
@@ -26585,7 +26653,7 @@
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B37" s="103" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C37" s="85">
         <f>C36/C3</f>
@@ -26822,7 +26890,7 @@
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B42" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C42" s="85">
         <f>C41/C40</f>
@@ -26993,7 +27061,7 @@
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B46" s="103" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C46" s="85">
         <f>C45/'Historical Financial Statement'!C23</f>
@@ -27058,7 +27126,7 @@
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B47" s="103" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C47" s="85">
         <f>AVERAGE(C46:L46)</f>
@@ -27164,7 +27232,7 @@
     </row>
     <row r="50" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B50" s="103" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C50" s="85">
         <f>C49/C3</f>
@@ -27340,7 +27408,7 @@
     </row>
     <row r="55" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B55" s="103" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C55" s="84">
         <f>365/(C6/C54)</f>
@@ -27405,7 +27473,7 @@
     </row>
     <row r="56" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B56" s="103" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C56" s="84">
         <f>AVERAGE(C55:L55)</f>
@@ -27508,7 +27576,7 @@
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B59" s="103" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C59" s="62">
         <f>365/(C3/C58)</f>
@@ -27573,7 +27641,7 @@
     </row>
     <row r="60" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B60" s="103" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C60" s="62">
         <f>AVERAGE(C59:L59)</f>
@@ -27692,7 +27760,7 @@
     </row>
     <row r="63" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B63" s="103" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C63" s="30">
         <f>C62/C3</f>
@@ -27757,7 +27825,7 @@
     </row>
     <row r="64" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B64" s="103" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C64" s="30">
         <f>AVERAGE(C63:L63)</f>
@@ -27855,7 +27923,7 @@
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B67" s="103" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C67" s="85">
         <f>C66/C18</f>
@@ -27920,7 +27988,7 @@
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B68" s="103" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C68" s="85">
         <f>AVERAGE(C67:L67)</f>
@@ -28026,7 +28094,7 @@
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B71" s="103" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C71" s="59">
         <f>C70/C3</f>
@@ -28092,7 +28160,7 @@
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B72" s="103" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C72" s="59">
         <f>AVERAGE(C71:L71)</f>
@@ -28198,7 +28266,7 @@
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B75" s="103" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C75" s="59">
         <f>C74/C62</f>
@@ -28406,20 +28474,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B1" s="260" t="str">
+      <c r="B1" s="261" t="str">
         <f>"DCF Model for "&amp;'Data Sheet'!B1</f>
         <v>DCF Model for INFOSYS LTD</v>
       </c>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
+      <c r="C1" s="261"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="261"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
       <c r="M1" s="193"/>
       <c r="N1" s="193"/>
       <c r="O1" s="193"/>
@@ -28427,25 +28495,25 @@
       <c r="Q1" s="193"/>
     </row>
     <row r="2" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="267" t="str">
+      <c r="B2" s="269" t="str">
         <f>"WACC Calculation for "&amp;'Data Sheet'!B1</f>
         <v>WACC Calculation for INFOSYS LTD</v>
       </c>
-      <c r="C2" s="267"/>
-      <c r="F2" s="268" t="str">
+      <c r="C2" s="269"/>
+      <c r="F2" s="270" t="str">
         <f>"Discount Cash-Flow for "&amp;'Data Sheet'!B1</f>
         <v>Discount Cash-Flow for INFOSYS LTD</v>
       </c>
-      <c r="G2" s="269"/>
-      <c r="H2" s="269"/>
-      <c r="I2" s="269"/>
-      <c r="J2" s="269"/>
-      <c r="K2" s="269"/>
-      <c r="L2" s="270"/>
+      <c r="G2" s="271"/>
+      <c r="H2" s="271"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="271"/>
+      <c r="L2" s="272"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B3" s="213" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C3" s="198">
         <v>469200</v>
@@ -28472,7 +28540,7 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B4" s="213" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C4" s="198">
         <v>8525</v>
@@ -28507,7 +28575,7 @@
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B5" s="213" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C5" s="199">
         <f>C3/SUM(C3:C4)</f>
@@ -28543,14 +28611,14 @@
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B6" s="213" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C6" s="199">
         <f>C4/(SUM(C3:C4))</f>
         <v>1.7844994505206969E-2</v>
       </c>
       <c r="F6" s="215" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G6" s="216">
         <f>-'Historical Financial Statement'!L75</f>
@@ -28579,14 +28647,14 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B7" s="213" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C7" s="200">
         <f>('Historical Financial Statement'!L17/'DCF Model'!C4)*(1-'DCF Model'!C9)</f>
         <v>3.5915073313782991E-2</v>
       </c>
       <c r="F7" s="219" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G7" s="216">
         <f>SUM('Historical Financial Statement'!L55:L56)-'Historical Financial Statement'!L39</f>
@@ -28615,14 +28683,14 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B8" s="213" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C8" s="200">
         <f>C10+C12*(C11-C10)</f>
         <v>0.10010161114159957</v>
       </c>
       <c r="F8" s="215" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H8" s="84">
         <f>H7-G7</f>
@@ -28653,7 +28721,7 @@
         <v>0.26400000000000001</v>
       </c>
       <c r="F9" s="220" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G9" s="221"/>
       <c r="H9" s="222">
@@ -28679,7 +28747,7 @@
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B10" s="213" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C10" s="202">
         <v>7.46E-2</v>
@@ -28687,14 +28755,14 @@
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B11" s="213" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C11" s="200">
         <f>_xlfn.RRI(10,'BETA Calculation'!F525,'BETA Calculation'!F4)</f>
         <v>0.11215961227220483</v>
       </c>
       <c r="F11" s="117" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="242">
@@ -28703,14 +28771,14 @@
     </row>
     <row r="12" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B12" s="214" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C12" s="203">
         <f>'BETA Calculation'!J8</f>
         <v>0.67896364203076398</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H12" s="223">
         <f>C14</f>
@@ -28719,7 +28787,7 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.45">
       <c r="F13" s="12" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="H13" s="224">
         <f>(L9*(1+H11))/(H12-H11)</f>
@@ -28728,7 +28796,7 @@
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B14" s="196" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C14" s="197">
         <f>(C5*C8)+(C6*C7)</f>
@@ -28737,21 +28805,21 @@
     </row>
     <row r="15" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="F15" s="194" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G15" s="194" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="H15" s="194" t="s">
+        <v>545</v>
+      </c>
+      <c r="I15" s="194" t="s">
         <v>547</v>
-      </c>
-      <c r="I15" s="194" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B16" s="207" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C16" s="204"/>
       <c r="D16" s="210"/>
@@ -28774,7 +28842,7 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B17" s="208" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C17" s="205"/>
       <c r="D17" s="211"/>
@@ -28797,7 +28865,7 @@
     </row>
     <row r="18" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="209" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C18" s="206"/>
       <c r="D18" s="212"/>
@@ -28872,7 +28940,7 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.45">
       <c r="F25" s="12" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G25" s="86">
         <f>I22</f>
@@ -28881,7 +28949,7 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.45">
       <c r="F26" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G26" s="170">
         <f>'COMP Analysis'!F4</f>
@@ -28890,7 +28958,7 @@
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.45">
       <c r="F27" s="12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G27" s="86">
         <f>G25-G26</f>
@@ -28899,7 +28967,7 @@
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.45">
       <c r="F28" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G28" s="84">
         <f>'Data Sheet'!K93</f>
@@ -28907,23 +28975,23 @@
       </c>
     </row>
     <row r="29" spans="2:9" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="F29" s="273" t="s">
-        <v>551</v>
-      </c>
-      <c r="G29" s="274">
+      <c r="F29" s="259" t="s">
+        <v>549</v>
+      </c>
+      <c r="G29" s="260">
         <f>G27/G28</f>
         <v>2244.6113580122428</v>
       </c>
     </row>
     <row r="31" spans="2:9" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="E31" s="238" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F31" s="239" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G31" s="238" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H31" s="237"/>
     </row>
@@ -28932,11 +29000,11 @@
     </row>
     <row r="33" spans="6:8" ht="23.25" x14ac:dyDescent="0.7">
       <c r="F33" s="240" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G33" s="241"/>
       <c r="H33" s="243" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="34" spans="6:8" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -28973,74 +29041,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B1" s="260" t="str">
+      <c r="B1" s="261" t="str">
         <f>"COMP Analysis for "&amp;'Data Sheet'!B1</f>
         <v>COMP Analysis for INFOSYS LTD</v>
       </c>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
-      <c r="N1" s="260"/>
-      <c r="O1" s="260"/>
-      <c r="P1" s="260"/>
-      <c r="Q1" s="260"/>
+      <c r="C1" s="261"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="261"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="261"/>
+      <c r="O1" s="261"/>
+      <c r="P1" s="261"/>
+      <c r="Q1" s="261"/>
       <c r="R1" s="168"/>
       <c r="S1" s="168"/>
     </row>
     <row r="2" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B2" s="226"/>
-      <c r="C2" s="271" t="s">
+      <c r="C2" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2" s="273"/>
+      <c r="E2" s="273"/>
+      <c r="F2" s="273"/>
+      <c r="G2" s="273"/>
+      <c r="H2" s="227"/>
+      <c r="I2" s="274" t="s">
+        <v>174</v>
+      </c>
+      <c r="J2" s="274"/>
+      <c r="K2" s="274"/>
+      <c r="L2" s="274"/>
+      <c r="M2" s="226"/>
+      <c r="N2" s="274" t="s">
         <v>175</v>
       </c>
-      <c r="D2" s="271"/>
-      <c r="E2" s="271"/>
-      <c r="F2" s="271"/>
-      <c r="G2" s="271"/>
-      <c r="H2" s="227"/>
-      <c r="I2" s="272" t="s">
-        <v>176</v>
-      </c>
-      <c r="J2" s="272"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="272"/>
-      <c r="M2" s="226"/>
-      <c r="N2" s="272" t="s">
-        <v>177</v>
-      </c>
-      <c r="O2" s="272"/>
-      <c r="P2" s="272"/>
-      <c r="Q2" s="272"/>
+      <c r="O2" s="274"/>
+      <c r="P2" s="274"/>
+      <c r="Q2" s="274"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B3" s="226" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C3" s="228" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="228" t="s">
+        <v>198</v>
+      </c>
+      <c r="E3" s="228" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3" s="228" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="228" t="s">
-        <v>200</v>
-      </c>
-      <c r="E3" s="228" t="s">
-        <v>179</v>
-      </c>
-      <c r="F3" s="228" t="s">
-        <v>180</v>
-      </c>
       <c r="G3" s="228" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H3" s="229"/>
       <c r="I3" s="228" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J3" s="228" t="s">
         <v>81</v>
@@ -29053,21 +29121,21 @@
       </c>
       <c r="M3" s="229"/>
       <c r="N3" s="228" t="s">
+        <v>180</v>
+      </c>
+      <c r="O3" s="228" t="s">
+        <v>181</v>
+      </c>
+      <c r="P3" s="228" t="s">
         <v>182</v>
       </c>
-      <c r="O3" s="228" t="s">
+      <c r="Q3" s="228" t="s">
         <v>183</v>
-      </c>
-      <c r="P3" s="228" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q3" s="228" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B4" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C4" s="173">
         <v>1154</v>
@@ -29123,7 +29191,7 @@
     </row>
     <row r="5" spans="2:19" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B5" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C5" s="173">
         <v>2528</v>
@@ -29176,7 +29244,7 @@
     </row>
     <row r="6" spans="2:19" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C6" s="173">
         <v>1424</v>
@@ -29229,7 +29297,7 @@
     </row>
     <row r="7" spans="2:19" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C7" s="173">
         <v>190</v>
@@ -29283,7 +29351,7 @@
     </row>
     <row r="8" spans="2:19" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C8" s="173">
         <v>1789</v>
@@ -29337,7 +29405,7 @@
     <row r="9" spans="2:19" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="10" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B10" s="176" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C10" s="177"/>
       <c r="D10" s="177"/>
@@ -29369,7 +29437,7 @@
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B11" s="176" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C11" s="177"/>
       <c r="D11" s="177"/>
@@ -29401,7 +29469,7 @@
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B12" s="183" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C12" s="179"/>
       <c r="D12" s="179"/>
@@ -29433,7 +29501,7 @@
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B13" s="184" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C13" s="180"/>
       <c r="D13" s="180"/>
@@ -29465,7 +29533,7 @@
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B14" s="176" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C14" s="177"/>
       <c r="D14" s="177"/>
@@ -29497,7 +29565,7 @@
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B15" s="176" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C15" s="177"/>
       <c r="D15" s="177"/>
@@ -29535,12 +29603,12 @@
       <c r="Q16" s="185"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="N17" s="272" t="s">
-        <v>177</v>
-      </c>
-      <c r="O17" s="272"/>
-      <c r="P17" s="272"/>
-      <c r="Q17" s="272"/>
+      <c r="N17" s="274" t="s">
+        <v>175</v>
+      </c>
+      <c r="O17" s="274"/>
+      <c r="P17" s="274"/>
+      <c r="Q17" s="274"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B18" s="186" t="str">
@@ -29548,28 +29616,28 @@
         <v>INFOSYS LTD</v>
       </c>
       <c r="N18" s="228" t="s">
+        <v>180</v>
+      </c>
+      <c r="O18" s="228" t="s">
+        <v>181</v>
+      </c>
+      <c r="P18" s="228" t="s">
         <v>182</v>
       </c>
-      <c r="O18" s="228" t="s">
+      <c r="Q18" s="228" t="s">
         <v>183</v>
-      </c>
-      <c r="P18" s="228" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q18" s="228" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="19" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B19" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="N19" s="172">
         <f>N13*I4</f>
         <v>499496.07930088014</v>
       </c>
       <c r="O19" s="172">
-        <f t="shared" ref="O19:Q19" si="10">O13*J4</f>
+        <f t="shared" ref="O19:P19" si="10">O13*J4</f>
         <v>504961.44685565634</v>
       </c>
       <c r="P19" s="172">
@@ -29583,7 +29651,7 @@
     </row>
     <row r="20" spans="2:17" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N20" s="170">
         <f>$F4</f>
@@ -29604,14 +29672,14 @@
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N21" s="170">
         <f>N19-N20</f>
         <v>512521.07930088014</v>
       </c>
       <c r="O21" s="170">
-        <f t="shared" ref="O21:Q21" si="12">O19-O20</f>
+        <f t="shared" ref="O21:P21" si="12">O19-O20</f>
         <v>517986.44685565634</v>
       </c>
       <c r="P21" s="170">
@@ -29625,7 +29693,7 @@
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N22" s="170">
         <f>$D4</f>
@@ -29646,7 +29714,7 @@
     </row>
     <row r="23" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="187" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C23" s="187"/>
       <c r="D23" s="187"/>
@@ -29679,13 +29747,13 @@
     <row r="24" spans="2:17" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="25" spans="2:17" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="E25" s="238" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F25" s="239" t="s">
+        <v>552</v>
+      </c>
+      <c r="G25" s="238" t="s">
         <v>554</v>
-      </c>
-      <c r="G25" s="238" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="26" spans="2:17" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -29693,15 +29761,15 @@
     </row>
     <row r="27" spans="2:17" ht="23.25" x14ac:dyDescent="0.7">
       <c r="E27" s="240" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F27" s="241"/>
       <c r="G27" s="241"/>
       <c r="H27" s="243" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="I27" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -29727,35 +29795,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:24" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B1" s="260" t="str">
+      <c r="B1" s="261" t="str">
         <f>"Common Size Income Statement for "&amp;'Data Sheet'!B1</f>
         <v>Common Size Income Statement for INFOSYS LTD</v>
       </c>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
+      <c r="C1" s="261"/>
+      <c r="D1" s="261"/>
+      <c r="E1" s="261"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="261"/>
+      <c r="H1" s="261"/>
+      <c r="I1" s="261"/>
+      <c r="J1" s="261"/>
+      <c r="K1" s="261"/>
+      <c r="L1" s="261"/>
       <c r="M1" s="193"/>
-      <c r="N1" s="260" t="str">
+      <c r="N1" s="261" t="str">
         <f>"Common Size Balance Sheet for "&amp;'Data Sheet'!B1</f>
         <v>Common Size Balance Sheet for INFOSYS LTD</v>
       </c>
-      <c r="O1" s="260"/>
-      <c r="P1" s="260"/>
-      <c r="Q1" s="260"/>
-      <c r="R1" s="260"/>
-      <c r="S1" s="260"/>
-      <c r="T1" s="260"/>
-      <c r="U1" s="260"/>
-      <c r="V1" s="260"/>
-      <c r="W1" s="260"/>
-      <c r="X1" s="260"/>
+      <c r="O1" s="261"/>
+      <c r="P1" s="261"/>
+      <c r="Q1" s="261"/>
+      <c r="R1" s="261"/>
+      <c r="S1" s="261"/>
+      <c r="T1" s="261"/>
+      <c r="U1" s="261"/>
+      <c r="V1" s="261"/>
+      <c r="W1" s="261"/>
+      <c r="X1" s="261"/>
     </row>
     <row r="2" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B2" s="116" t="str">

--- a/Infosys.xlsx
+++ b/Infosys.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2855141d0bd7c7e8/Desktop/Finance Analytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2010" documentId="8_{516AF91F-FBEC-4432-867B-25B2131D13D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{009D4A26-D3D4-43B8-A6F0-D8924979AC28}"/>
+  <xr:revisionPtr revIDLastSave="2015" documentId="8_{516AF91F-FBEC-4432-867B-25B2131D13D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D47A3DB-3736-4900-81FC-11BE78CA302E}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" tabRatio="828" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" tabRatio="828" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Sheet" sheetId="6" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="561">
   <si>
     <t>COMPANY NAME</t>
   </si>
@@ -447,9 +447,6 @@
   </si>
   <si>
     <t>Average % Other Assets</t>
-  </si>
-  <si>
-    <t>% Dividends received</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -7993,7 +7990,7 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.45">
       <c r="B28" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="M28" s="141"/>
       <c r="N28" s="141"/>
@@ -8135,7 +8132,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.45">
       <c r="B31" s="31" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C31" s="50">
         <f>SUM(C29:C30)</f>
@@ -11538,7 +11535,7 @@
         <v>78</v>
       </c>
       <c r="B3" s="117" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M3" s="128"/>
       <c r="N3" s="128"/>
@@ -11808,7 +11805,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B8" s="47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" s="123">
         <f>'Historical Financial Statement'!C23/SUM('Historical Financial Statement'!C29:C30)</f>
@@ -11873,7 +11870,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B9" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="123">
         <f>'Historical Financial Statement'!C23/'Historical Financial Statement'!C60</f>
@@ -11938,7 +11935,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B10" s="47" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C10" s="123">
         <f>'Historical Financial Statement'!C14/SUM('Historical Financial Statement'!C29:C30,'Historical Financial Statement'!C34)</f>
@@ -12003,7 +12000,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B11" s="47" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C11" s="123">
         <f>'Historical Financial Statement'!C23/SUM('Historical Financial Statement'!C31,'Historical Financial Statement'!C34)</f>
@@ -12078,7 +12075,7 @@
         <v>78</v>
       </c>
       <c r="B13" s="117" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M13" s="128"/>
       <c r="N13" s="128"/>
@@ -12088,7 +12085,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B14" s="47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C14" s="124">
         <f>'Historical Financial Statement'!C34/SUM('Historical Financial Statement'!C29:C30)</f>
@@ -12153,7 +12150,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B15" s="47" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C15" s="124">
         <f>'Historical Financial Statement'!C34/'Historical Financial Statement'!C60</f>
@@ -12218,7 +12215,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B16" s="47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="124">
         <f>IFERROR('Historical Financial Statement'!C19/'Historical Financial Statement'!C17,0)</f>
@@ -12303,7 +12300,7 @@
         <v>78</v>
       </c>
       <c r="B18" s="117" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C18" s="124"/>
       <c r="D18" s="124"/>
@@ -12321,12 +12318,12 @@
       <c r="P18" s="132"/>
       <c r="Q18" s="132"/>
       <c r="S18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.45">
       <c r="B19" s="47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C19" s="124">
         <f>'Historical Financial Statement'!C3/'Historical Financial Statement'!C60</f>
@@ -12391,7 +12388,7 @@
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.45">
       <c r="B20" s="47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="124">
         <f>'Historical Financial Statement'!C3/'Historical Financial Statement'!C48</f>
@@ -12454,12 +12451,12 @@
         <v>8.2904597785601961</v>
       </c>
       <c r="W20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.45">
       <c r="B21" s="47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C21" s="124">
         <f>IFERROR('Historical Financial Statement'!C4/'Historical Financial Statement'!C56,0)</f>
@@ -12524,7 +12521,7 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.45">
       <c r="B22" s="47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" s="124">
         <f>'Historical Financial Statement'!C4/'Historical Financial Statement'!C39</f>
@@ -12589,7 +12586,7 @@
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.45">
       <c r="B23" s="47" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C23" s="124">
         <f>'Historical Financial Statement'!C3/'Historical Financial Statement'!C55</f>
@@ -12674,7 +12671,7 @@
         <v>78</v>
       </c>
       <c r="B25" s="117" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C25" s="124"/>
       <c r="D25" s="124"/>
@@ -12694,7 +12691,7 @@
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.45">
       <c r="B26" s="47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C26" s="124">
         <f>'Historical Financial Statement'!C58/'Historical Financial Statement'!C41</f>
@@ -12759,7 +12756,7 @@
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.45">
       <c r="B27" s="47" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C27" s="124">
         <f>(SUM('Historical Financial Statement'!C55,'Historical Financial Statement'!C57)-'Historical Financial Statement'!C56)/'Historical Financial Statement'!C41</f>
@@ -12824,7 +12821,7 @@
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.45">
       <c r="B28" s="47" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" s="124">
         <f>'Historical Financial Statement'!C57/'Historical Financial Statement'!C41</f>
@@ -12909,7 +12906,7 @@
         <v>78</v>
       </c>
       <c r="B30" s="117" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C30" s="124"/>
       <c r="D30" s="124"/>
@@ -12929,7 +12926,7 @@
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.45">
       <c r="B31" s="47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C31" s="120">
         <f>'Historical Financial Statement'!C23/'Data Sheet'!B93</f>
@@ -12992,12 +12989,12 @@
         <v>95.318626285679443</v>
       </c>
       <c r="T31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.45">
       <c r="B32" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C32" s="120">
         <f>'Data Sheet'!B90/'Ratios Analysis'!C31</f>
@@ -13062,7 +13059,7 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B33" s="47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" s="120">
         <f>SUM('Historical Financial Statement'!C29:C30)/'Data Sheet'!B93</f>
@@ -13137,7 +13134,7 @@
         <v>78</v>
       </c>
       <c r="B35" s="117" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M35" s="128"/>
       <c r="N35" s="128"/>
@@ -13147,7 +13144,7 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B36" s="47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C36" s="121">
         <f>IFERROR(365/C21,0)</f>
@@ -13212,7 +13209,7 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B37" s="47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C37" s="121">
         <f>365/C22</f>
@@ -13276,12 +13273,12 @@
       </c>
       <c r="R37" s="15"/>
       <c r="S37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B38" s="47" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C38" s="121">
         <f>365/C23</f>
@@ -13346,7 +13343,7 @@
     </row>
     <row r="39" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B39" s="117" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C39" s="122">
         <f>SUM(C36,C38)-C37</f>
@@ -13431,7 +13428,7 @@
         <v>78</v>
       </c>
       <c r="B41" s="117" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C41" s="121"/>
       <c r="D41" s="121"/>
@@ -13451,7 +13448,7 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B42" s="47" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C42" s="123">
         <f>'Data Sheet'!B31/'Historical Financial Statement'!C23</f>
@@ -13516,7 +13513,7 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B43" s="47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C43" s="123">
         <f>1-C42</f>
@@ -13581,7 +13578,7 @@
     </row>
     <row r="44" spans="1:19" s="12" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B44" s="117" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C44" s="126">
         <f>C43*C8</f>
@@ -13834,7 +13831,7 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B4" s="153" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C4" s="154">
         <f>'Historical Financial Statement'!C23/'Historical Financial Statement'!C19</f>
@@ -13899,7 +13896,7 @@
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B5" s="153" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C5" s="154">
         <f>'Historical Financial Statement'!C19/'Historical Financial Statement'!C14</f>
@@ -13964,7 +13961,7 @@
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B6" s="153" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C6" s="157">
         <f>'Ratios Analysis'!C6</f>
@@ -14029,7 +14026,7 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B7" s="153" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C7" s="154">
         <f>'Ratios Analysis'!C19</f>
@@ -14094,7 +14091,7 @@
     </row>
     <row r="8" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" s="148" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C8" s="160">
         <f>'Historical Financial Statement'!C60/SUM('Historical Financial Statement'!C29:C30)</f>
@@ -14159,7 +14156,7 @@
     </row>
     <row r="10" spans="2:17" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="261" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C10" s="261"/>
       <c r="D10" s="261"/>
@@ -14179,7 +14176,7 @@
     </row>
     <row r="11" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="163" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C11" s="164">
         <f>C3*C7*C8</f>
@@ -14244,7 +14241,7 @@
     </row>
     <row r="13" spans="2:17" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="261" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C13" s="261"/>
       <c r="D13" s="261"/>
@@ -14264,7 +14261,7 @@
     </row>
     <row r="14" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B14" s="163" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C14" s="164">
         <f>C4*C5*C6*C7*C8</f>
@@ -14371,39 +14368,39 @@
     </row>
     <row r="2" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B2" s="264" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C2" s="264"/>
       <c r="D2" s="264"/>
       <c r="E2" s="191"/>
       <c r="F2" s="264" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G2" s="264"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B3" s="190" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C3" s="192" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D3" s="192" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E3" s="192"/>
       <c r="F3" s="192" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G3" s="192" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I3" s="265"/>
       <c r="J3" s="265"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C4" s="256">
         <v>1153.8</v>
@@ -14421,14 +14418,14 @@
         <v>-2.5752075096373783E-2</v>
       </c>
       <c r="I4" s="194" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J4" s="195">
         <f>CORREL(D4:D525,G4:G525)</f>
         <v>0.40394328989545369</v>
       </c>
       <c r="K4" s="194" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L4" s="12">
         <f>_xlfn.COVARIANCE.S(D4:D525,G4:G525)</f>
@@ -14455,14 +14452,14 @@
         <v>1.844818479282373E-2</v>
       </c>
       <c r="I5" s="194" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J5" s="195">
         <f>_xlfn.STDEV.S(D4:D525)</f>
         <v>3.661319787923719E-2</v>
       </c>
       <c r="K5" s="194" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L5" s="12">
         <f>_xlfn.VAR.S(G4:G525)</f>
@@ -14489,7 +14486,7 @@
         <v>4.0717823197722325E-4</v>
       </c>
       <c r="I6" s="194" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J6" s="195">
         <f>_xlfn.STDEV.S(G4:G525)</f>
@@ -14498,7 +14495,7 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C7" s="256">
         <v>1035</v>
@@ -14518,7 +14515,7 @@
     </row>
     <row r="8" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B8" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C8" s="256">
         <v>1000.2</v>
@@ -14536,7 +14533,7 @@
         <v>-1.037847162174288E-2</v>
       </c>
       <c r="I8" s="235" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J8" s="236">
         <f>J4*(J5/J6)</f>
@@ -14545,7 +14542,7 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C9" s="256">
         <v>1051.4000000000001</v>
@@ -14563,7 +14560,7 @@
         <v>-1.1348479216320984E-3</v>
       </c>
       <c r="I9" s="233" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J9" s="234">
         <f>J8/(1+('DCF Model'!C4/'DCF Model'!C3)*(1-'DCF Model'!C9))</f>
@@ -14593,7 +14590,7 @@
     </row>
     <row r="11" spans="2:17" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B11" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C11" s="256">
         <v>1130</v>
@@ -14611,7 +14608,7 @@
         <v>-1.166242713639376E-2</v>
       </c>
       <c r="I11" s="235" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J11" s="236">
         <f>L4/L5</f>
@@ -14620,7 +14617,7 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C12" s="256">
         <v>1144</v>
@@ -14640,7 +14637,7 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C13" s="256">
         <v>1121</v>
@@ -14700,7 +14697,7 @@
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C16" s="256">
         <v>1130.0999999999999</v>
@@ -14720,7 +14717,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C17" s="256">
         <v>1040.9000000000001</v>
@@ -14780,7 +14777,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C20" s="256">
         <v>1047.2</v>
@@ -14800,7 +14797,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C21" s="256">
         <v>1041.2</v>
@@ -14820,7 +14817,7 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C22" s="256">
         <v>1051.4000000000001</v>
@@ -14860,7 +14857,7 @@
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C24" s="256">
         <v>1197.5</v>
@@ -14880,7 +14877,7 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C25" s="256">
         <v>1160.9000000000001</v>
@@ -14900,7 +14897,7 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C26" s="256">
         <v>1174.5</v>
@@ -14960,7 +14957,7 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C29" s="256">
         <v>1181.8</v>
@@ -14980,7 +14977,7 @@
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C30" s="256">
         <v>1154.5999999999999</v>
@@ -15040,7 +15037,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C33" s="256">
         <v>1300.8</v>
@@ -15060,7 +15057,7 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C34" s="256">
         <v>1269.7</v>
@@ -15080,7 +15077,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C35" s="256">
         <v>1255.9000000000001</v>
@@ -15140,7 +15137,7 @@
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C38" s="256">
         <v>1300.0999999999999</v>
@@ -15160,7 +15157,7 @@
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C39" s="256">
         <v>1353.2</v>
@@ -15220,7 +15217,7 @@
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C42" s="256">
         <v>1641</v>
@@ -15240,7 +15237,7 @@
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C43" s="256">
         <v>1670.8</v>
@@ -15300,7 +15297,7 @@
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C46" s="256">
         <v>1640.4</v>
@@ -15320,7 +15317,7 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C47" s="256">
         <v>1656.1</v>
@@ -15340,7 +15337,7 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C48" s="256">
         <v>1638.7</v>
@@ -15380,7 +15377,7 @@
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C50" s="256">
         <v>1616.2</v>
@@ -15400,7 +15397,7 @@
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C51" s="256">
         <v>1560.1</v>
@@ -15420,7 +15417,7 @@
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C52" s="256">
         <v>1545</v>
@@ -15480,7 +15477,7 @@
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C55" s="256">
         <v>1482.3</v>
@@ -15500,7 +15497,7 @@
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C56" s="256">
         <v>1525.4</v>
@@ -15560,7 +15557,7 @@
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C59" s="256">
         <v>1446.6</v>
@@ -15580,7 +15577,7 @@
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C60" s="256">
         <v>1448.9</v>
@@ -15600,7 +15597,7 @@
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C61" s="256">
         <v>1540.2</v>
@@ -15640,7 +15637,7 @@
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C63" s="256">
         <v>1444.6</v>
@@ -15660,7 +15657,7 @@
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C64" s="256">
         <v>1469.6</v>
@@ -15680,7 +15677,7 @@
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C65" s="256">
         <v>1487.5</v>
@@ -15740,7 +15737,7 @@
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C68" s="256">
         <v>1469.6</v>
@@ -15760,7 +15757,7 @@
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C69" s="256">
         <v>1515.7</v>
@@ -15780,7 +15777,7 @@
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C70" s="256">
         <v>1586.1</v>
@@ -15820,7 +15817,7 @@
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C72" s="256">
         <v>1640.7</v>
@@ -15840,7 +15837,7 @@
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C73" s="256">
         <v>1608</v>
@@ -15860,7 +15857,7 @@
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C74" s="256">
         <v>1622.9</v>
@@ -15920,7 +15917,7 @@
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C77" s="256">
         <v>1562.7</v>
@@ -15940,7 +15937,7 @@
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C78" s="256">
         <v>1564.8</v>
@@ -16000,7 +15997,7 @@
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C81" s="256">
         <v>1506.8</v>
@@ -16020,7 +16017,7 @@
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C82" s="256">
         <v>1480.2</v>
@@ -16040,7 +16037,7 @@
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C83" s="256">
         <v>1419.5</v>
@@ -16080,7 +16077,7 @@
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C85" s="256">
         <v>1451.65</v>
@@ -16100,7 +16097,7 @@
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C86" s="256">
         <v>1570.65</v>
@@ -16120,7 +16117,7 @@
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C87" s="256">
         <v>1592.55</v>
@@ -16180,7 +16177,7 @@
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C90" s="256">
         <v>1687.7</v>
@@ -16200,7 +16197,7 @@
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C91" s="256">
         <v>1815</v>
@@ -16260,7 +16257,7 @@
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C94" s="256">
         <v>1879.8</v>
@@ -16280,7 +16277,7 @@
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C95" s="256">
         <v>1875.45</v>
@@ -16340,7 +16337,7 @@
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C98" s="256">
         <v>1938.75</v>
@@ -16360,7 +16357,7 @@
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C99" s="256">
         <v>1916.75</v>
@@ -16380,7 +16377,7 @@
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C100" s="256">
         <v>1922.15</v>
@@ -16440,7 +16437,7 @@
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C103" s="256">
         <v>1857.85</v>
@@ -16460,7 +16457,7 @@
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C104" s="256">
         <v>1902.25</v>
@@ -16520,7 +16517,7 @@
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C107" s="256">
         <v>1760.85</v>
@@ -16540,7 +16537,7 @@
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C108" s="256">
         <v>1862.05</v>
@@ -16560,7 +16557,7 @@
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C109" s="256">
         <v>1879.6</v>
@@ -16600,7 +16597,7 @@
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C111" s="256">
         <v>1918.15</v>
@@ -16620,7 +16617,7 @@
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C112" s="256">
         <v>1906.75</v>
@@ -16640,7 +16637,7 @@
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C113" s="256">
         <v>1905.75</v>
@@ -16700,7 +16697,7 @@
     </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B116" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C116" s="256">
         <v>1943.7</v>
@@ -16720,7 +16717,7 @@
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B117" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C117" s="256">
         <v>1862.1</v>
@@ -16780,7 +16777,7 @@
     </row>
     <row r="120" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B120" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C120" s="256">
         <v>1821.2</v>
@@ -16800,7 +16797,7 @@
     </row>
     <row r="121" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B121" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C121" s="256">
         <v>1878.9</v>
@@ -16820,7 +16817,7 @@
     </row>
     <row r="122" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B122" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C122" s="256">
         <v>1792.95</v>
@@ -16860,7 +16857,7 @@
     </row>
     <row r="124" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B124" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C124" s="256">
         <v>1647.45</v>
@@ -16880,7 +16877,7 @@
     </row>
     <row r="125" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B125" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C125" s="256">
         <v>1566.75</v>
@@ -16900,7 +16897,7 @@
     </row>
     <row r="126" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B126" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C126" s="256">
         <v>1532.7</v>
@@ -16960,7 +16957,7 @@
     </row>
     <row r="129" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B129" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C129" s="256">
         <v>1406.9</v>
@@ -16980,7 +16977,7 @@
     </row>
     <row r="130" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B130" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C130" s="256">
         <v>1456.89</v>
@@ -17040,7 +17037,7 @@
     </row>
     <row r="133" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B133" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C133" s="256">
         <v>1408.36</v>
@@ -17060,7 +17057,7 @@
     </row>
     <row r="134" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B134" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C134" s="256">
         <v>1422.23</v>
@@ -17080,7 +17077,7 @@
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B135" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C135" s="256">
         <v>1403.34</v>
@@ -17120,7 +17117,7 @@
     </row>
     <row r="137" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B137" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C137" s="256">
         <v>1470.81</v>
@@ -17140,7 +17137,7 @@
     </row>
     <row r="138" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B138" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C138" s="256">
         <v>1489.66</v>
@@ -17160,7 +17157,7 @@
     </row>
     <row r="139" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B139" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C139" s="256">
         <v>1500.39</v>
@@ -17220,7 +17217,7 @@
     </row>
     <row r="142" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B142" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C142" s="256">
         <v>1645.43</v>
@@ -17240,7 +17237,7 @@
     </row>
     <row r="143" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B143" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C143" s="256">
         <v>1667.45</v>
@@ -17300,7 +17297,7 @@
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B146" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C146" s="256">
         <v>1683.86</v>
@@ -17320,7 +17317,7 @@
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B147" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C147" s="256">
         <v>1659.75</v>
@@ -17340,7 +17337,7 @@
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B148" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C148" s="256">
         <v>1649.9</v>
@@ -17380,7 +17377,7 @@
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B150" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C150" s="256">
         <v>1523.96</v>
@@ -17400,7 +17397,7 @@
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B151" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C151" s="256">
         <v>1534.25</v>
@@ -17420,7 +17417,7 @@
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B152" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C152" s="256">
         <v>1554.14</v>
@@ -17480,7 +17477,7 @@
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B155" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C155" s="256">
         <v>1444.16</v>
@@ -17500,7 +17497,7 @@
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B156" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C156" s="256">
         <v>1429.34</v>
@@ -17560,7 +17557,7 @@
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C159" s="256">
         <v>1381.27</v>
@@ -17580,7 +17577,7 @@
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B160" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C160" s="256">
         <v>1372.61</v>
@@ -17600,7 +17597,7 @@
     </row>
     <row r="161" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B161" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C161" s="256">
         <v>1419.25</v>
@@ -17660,7 +17657,7 @@
     </row>
     <row r="164" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B164" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C164" s="256">
         <v>1427.41</v>
@@ -17680,7 +17677,7 @@
     </row>
     <row r="165" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B165" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C165" s="256">
         <v>1487.77</v>
@@ -17740,7 +17737,7 @@
     </row>
     <row r="168" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B168" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C168" s="256">
         <v>1435.76</v>
@@ -17760,7 +17757,7 @@
     </row>
     <row r="169" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B169" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C169" s="256">
         <v>1412.14</v>
@@ -17780,7 +17777,7 @@
     </row>
     <row r="170" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B170" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C170" s="256">
         <v>1381.02</v>
@@ -17820,7 +17817,7 @@
     </row>
     <row r="172" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B172" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C172" s="256">
         <v>1370.63</v>
@@ -17840,7 +17837,7 @@
     </row>
     <row r="173" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B173" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C173" s="256">
         <v>1332.99</v>
@@ -17860,7 +17857,7 @@
     </row>
     <row r="174" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B174" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C174" s="256">
         <v>1324.14</v>
@@ -17920,7 +17917,7 @@
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B177" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C177" s="256">
         <v>1328.02</v>
@@ -17940,7 +17937,7 @@
     </row>
     <row r="178" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B178" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C178" s="256">
         <v>1257.9100000000001</v>
@@ -18000,7 +17997,7 @@
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B181" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C181" s="256">
         <v>1291.72</v>
@@ -18020,7 +18017,7 @@
     </row>
     <row r="182" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B182" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C182" s="256">
         <v>1310.07</v>
@@ -18040,7 +18037,7 @@
     </row>
     <row r="183" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B183" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C183" s="256">
         <v>1261.79</v>
@@ -18080,7 +18077,7 @@
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B185" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C185" s="256">
         <v>1252.04</v>
@@ -18100,7 +18097,7 @@
     </row>
     <row r="186" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B186" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C186" s="256">
         <v>1245.73</v>
@@ -18120,7 +18117,7 @@
     </row>
     <row r="187" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B187" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C187" s="256">
         <v>1220.47</v>
@@ -18180,7 +18177,7 @@
     </row>
     <row r="190" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B190" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C190" s="256">
         <v>1419.95</v>
@@ -18200,7 +18197,7 @@
     </row>
     <row r="191" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B191" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C191" s="256">
         <v>1372.91</v>
@@ -18260,7 +18257,7 @@
     </row>
     <row r="194" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B194" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C194" s="256">
         <v>1471.01</v>
@@ -18280,7 +18277,7 @@
     </row>
     <row r="195" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B195" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C195" s="256">
         <v>1541.96</v>
@@ -18340,7 +18337,7 @@
     </row>
     <row r="198" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B198" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C198" s="256">
         <v>1590.44</v>
@@ -18360,7 +18357,7 @@
     </row>
     <row r="199" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B199" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C199" s="256">
         <v>1510.64</v>
@@ -18380,7 +18377,7 @@
     </row>
     <row r="200" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B200" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C200" s="256">
         <v>1517</v>
@@ -18440,7 +18437,7 @@
     </row>
     <row r="203" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B203" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C203" s="256">
         <v>1499.75</v>
@@ -18460,7 +18457,7 @@
     </row>
     <row r="204" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B204" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C204" s="256">
         <v>1488.71</v>
@@ -18520,7 +18517,7 @@
     </row>
     <row r="207" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B207" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C207" s="256">
         <v>1628.72</v>
@@ -18540,7 +18537,7 @@
     </row>
     <row r="208" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B208" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C208" s="256">
         <v>1626.48</v>
@@ -18560,7 +18557,7 @@
     </row>
     <row r="209" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B209" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C209" s="256">
         <v>1584.47</v>
@@ -18600,7 +18597,7 @@
     </row>
     <row r="211" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B211" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C211" s="256">
         <v>1505.52</v>
@@ -18620,7 +18617,7 @@
     </row>
     <row r="212" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B212" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C212" s="256">
         <v>1504.77</v>
@@ -18640,7 +18637,7 @@
     </row>
     <row r="213" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B213" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C213" s="256">
         <v>1492.09</v>
@@ -18700,7 +18697,7 @@
     </row>
     <row r="216" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B216" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C216" s="256">
         <v>1405.53</v>
@@ -18720,7 +18717,7 @@
     </row>
     <row r="217" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B217" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C217" s="256">
         <v>1357.8</v>
@@ -18780,7 +18777,7 @@
     </row>
     <row r="220" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B220" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C220" s="256">
         <v>1444.86</v>
@@ -18800,7 +18797,7 @@
     </row>
     <row r="221" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B221" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C221" s="256">
         <v>1513.02</v>
@@ -18820,7 +18817,7 @@
     </row>
     <row r="222" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B222" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C222" s="256">
         <v>1588.15</v>
@@ -18860,7 +18857,7 @@
     </row>
     <row r="224" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B224" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C224" s="256">
         <v>1607.59</v>
@@ -18880,7 +18877,7 @@
     </row>
     <row r="225" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B225" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C225" s="256">
         <v>1541.02</v>
@@ -18900,7 +18897,7 @@
     </row>
     <row r="226" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B226" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C226" s="256">
         <v>1497.86</v>
@@ -18960,7 +18957,7 @@
     </row>
     <row r="229" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B229" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C229" s="256">
         <v>1471.11</v>
@@ -18980,7 +18977,7 @@
     </row>
     <row r="230" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B230" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C230" s="256">
         <v>1433.02</v>
@@ -19040,7 +19037,7 @@
     </row>
     <row r="233" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B233" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C233" s="256">
         <v>1513.17</v>
@@ -19060,7 +19057,7 @@
     </row>
     <row r="234" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B234" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C234" s="256">
         <v>1453.16</v>
@@ -19080,7 +19077,7 @@
     </row>
     <row r="235" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B235" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C235" s="256">
         <v>1446.99</v>
@@ -19140,7 +19137,7 @@
     </row>
     <row r="238" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B238" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C238" s="256">
         <v>1558.77</v>
@@ -19160,7 +19157,7 @@
     </row>
     <row r="239" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B239" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C239" s="256">
         <v>1576.56</v>
@@ -19220,7 +19217,7 @@
     </row>
     <row r="242" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B242" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C242" s="256">
         <v>1892.88</v>
@@ -19240,7 +19237,7 @@
     </row>
     <row r="243" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B243" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C243" s="256">
         <v>1866.03</v>
@@ -19260,7 +19257,7 @@
     </row>
     <row r="244" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B244" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C244" s="256">
         <v>1844.21</v>
@@ -19300,7 +19297,7 @@
     </row>
     <row r="246" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B246" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C246" s="256">
         <v>1713.64</v>
@@ -19320,7 +19317,7 @@
     </row>
     <row r="247" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C247" s="256">
         <v>1685.1</v>
@@ -19340,7 +19337,7 @@
     </row>
     <row r="248" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B248" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C248" s="256">
         <v>1697.38</v>
@@ -19380,7 +19377,7 @@
     </row>
     <row r="250" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B250" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C250" s="256">
         <v>1731.34</v>
@@ -19400,7 +19397,7 @@
     </row>
     <row r="251" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B251" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C251" s="256">
         <v>1676.75</v>
@@ -19420,7 +19417,7 @@
     </row>
     <row r="252" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B252" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C252" s="256">
         <v>1775.69</v>
@@ -19480,7 +19477,7 @@
     </row>
     <row r="255" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B255" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C255" s="256">
         <v>1877.17</v>
@@ -19500,7 +19497,7 @@
     </row>
     <row r="256" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B256" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C256" s="256">
         <v>1853.06</v>
@@ -19560,7 +19557,7 @@
     </row>
     <row r="259" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B259" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C259" s="256">
         <v>1725.82</v>
@@ -19580,7 +19577,7 @@
     </row>
     <row r="260" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B260" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C260" s="256">
         <v>1682.17</v>
@@ -19600,7 +19597,7 @@
     </row>
     <row r="261" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B261" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C261" s="256">
         <v>1769.43</v>
@@ -19640,7 +19637,7 @@
     </row>
     <row r="263" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B263" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C263" s="256">
         <v>1699.12</v>
@@ -19660,7 +19657,7 @@
     </row>
     <row r="264" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B264" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C264" s="256">
         <v>1658.4</v>
@@ -19680,7 +19677,7 @@
     </row>
     <row r="265" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B265" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C265" s="256">
         <v>1710.16</v>
@@ -19740,7 +19737,7 @@
     </row>
     <row r="268" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B268" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C268" s="256">
         <v>1655.82</v>
@@ -19760,7 +19757,7 @@
     </row>
     <row r="269" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B269" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C269" s="256">
         <v>1753.96</v>
@@ -19820,7 +19817,7 @@
     </row>
     <row r="272" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B272" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C272" s="256">
         <v>1691.12</v>
@@ -19840,7 +19837,7 @@
     </row>
     <row r="273" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B273" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C273" s="256">
         <v>1699.22</v>
@@ -19860,7 +19857,7 @@
     </row>
     <row r="274" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B274" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C274" s="256">
         <v>1723.24</v>
@@ -19920,7 +19917,7 @@
     </row>
     <row r="277" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B277" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C277" s="256">
         <v>1601.47</v>
@@ -19940,7 +19937,7 @@
     </row>
     <row r="278" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B278" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C278" s="256">
         <v>1581.54</v>
@@ -20000,7 +19997,7 @@
     </row>
     <row r="281" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B281" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C281" s="256">
         <v>1559.01</v>
@@ -20020,7 +20017,7 @@
     </row>
     <row r="282" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B282" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C282" s="256">
         <v>1565.38</v>
@@ -20040,7 +20037,7 @@
     </row>
     <row r="283" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B283" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C283" s="256">
         <v>1494.88</v>
@@ -20080,7 +20077,7 @@
     </row>
     <row r="285" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B285" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C285" s="256">
         <v>1377.89</v>
@@ -20100,7 +20097,7 @@
     </row>
     <row r="286" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B286" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C286" s="256">
         <v>1397.18</v>
@@ -20120,7 +20117,7 @@
     </row>
     <row r="287" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B287" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C287" s="256">
         <v>1346.91</v>
@@ -20180,7 +20177,7 @@
     </row>
     <row r="290" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B290" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C290" s="256">
         <v>1346.76</v>
@@ -20200,7 +20197,7 @@
     </row>
     <row r="291" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B291" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C291" s="256">
         <v>1326.32</v>
@@ -20260,7 +20257,7 @@
     </row>
     <row r="294" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B294" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C294" s="256">
         <v>1377.44</v>
@@ -20280,7 +20277,7 @@
     </row>
     <row r="295" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B295" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C295" s="256">
         <v>1328.71</v>
@@ -20300,7 +20297,7 @@
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B296" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C296" s="256">
         <v>1336.92</v>
@@ -20340,7 +20337,7 @@
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B298" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C298" s="256">
         <v>1309.32</v>
@@ -20360,7 +20357,7 @@
     </row>
     <row r="299" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B299" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C299" s="256">
         <v>1246.28</v>
@@ -20380,7 +20377,7 @@
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B300" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C300" s="256">
         <v>1284.06</v>
@@ -20420,7 +20417,7 @@
     </row>
     <row r="302" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B302" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C302" s="256">
         <v>1264.97</v>
@@ -20440,7 +20437,7 @@
     </row>
     <row r="303" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B303" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C303" s="256">
         <v>1232.1099999999999</v>
@@ -20460,7 +20457,7 @@
     </row>
     <row r="304" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B304" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C304" s="256">
         <v>1333.34</v>
@@ -20520,7 +20517,7 @@
     </row>
     <row r="307" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B307" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C307" s="256">
         <v>1253.3900000000001</v>
@@ -20540,7 +20537,7 @@
     </row>
     <row r="308" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B308" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C308" s="256">
         <v>1229.1199999999999</v>
@@ -20560,7 +20557,7 @@
     </row>
     <row r="309" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B309" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C309" s="256">
         <v>1183.1300000000001</v>
@@ -20600,7 +20597,7 @@
     </row>
     <row r="311" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B311" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C311" s="256">
         <v>1128.29</v>
@@ -20620,7 +20617,7 @@
     </row>
     <row r="312" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B312" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C312" s="256">
         <v>1093.8399999999999</v>
@@ -20640,7 +20637,7 @@
     </row>
     <row r="313" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B313" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C313" s="256">
         <v>1097.17</v>
@@ -20700,7 +20697,7 @@
     </row>
     <row r="316" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B316" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C316" s="256">
         <v>1054.6600000000001</v>
@@ -20720,7 +20717,7 @@
     </row>
     <row r="317" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B317" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C317" s="256">
         <v>1116.21</v>
@@ -20780,7 +20777,7 @@
     </row>
     <row r="320" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B320" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C320" s="256">
         <v>1011.95</v>
@@ -20800,7 +20797,7 @@
     </row>
     <row r="321" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B321" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C321" s="256">
         <v>1005.78</v>
@@ -20820,7 +20817,7 @@
     </row>
     <row r="322" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B322" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C322" s="257">
         <v>996.53</v>
@@ -20860,7 +20857,7 @@
     </row>
     <row r="324" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B324" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C324" s="257">
         <v>914</v>
@@ -20880,7 +20877,7 @@
     </row>
     <row r="325" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B325" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C325" s="257">
         <v>930.01</v>
@@ -20900,7 +20897,7 @@
     </row>
     <row r="326" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B326" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C326" s="257">
         <v>943.48</v>
@@ -20960,7 +20957,7 @@
     </row>
     <row r="329" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B329" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C329" s="257">
         <v>960.59</v>
@@ -20980,7 +20977,7 @@
     </row>
     <row r="330" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B330" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C330" s="257">
         <v>917.68</v>
@@ -21040,7 +21037,7 @@
     </row>
     <row r="333" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B333" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C333" s="257">
         <v>758.43</v>
@@ -21060,7 +21057,7 @@
     </row>
     <row r="334" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B334" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C334" s="257">
         <v>744.01</v>
@@ -21080,7 +21077,7 @@
     </row>
     <row r="335" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B335" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C335" s="257">
         <v>701.6</v>
@@ -21120,7 +21117,7 @@
     </row>
     <row r="337" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B337" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C337" s="257">
         <v>699.61</v>
@@ -21140,7 +21137,7 @@
     </row>
     <row r="338" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B338" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C338" s="257">
         <v>687.13</v>
@@ -21160,7 +21157,7 @@
     </row>
     <row r="339" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B339" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C339" s="257">
         <v>688.47</v>
@@ -21220,7 +21217,7 @@
     </row>
     <row r="342" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B342" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C342" s="257">
         <v>711.49</v>
@@ -21240,7 +21237,7 @@
     </row>
     <row r="343" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B343" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C343" s="257">
         <v>654.30999999999995</v>
@@ -21300,7 +21297,7 @@
     </row>
     <row r="346" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B346" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C346" s="257">
         <v>582.41999999999996</v>
@@ -21320,7 +21317,7 @@
     </row>
     <row r="347" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B347" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C347" s="257">
         <v>649.04</v>
@@ -21340,7 +21337,7 @@
     </row>
     <row r="348" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B348" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C348" s="257">
         <v>581.91999999999996</v>
@@ -21400,7 +21397,7 @@
     </row>
     <row r="351" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B351" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C351" s="257">
         <v>727.6</v>
@@ -21420,7 +21417,7 @@
     </row>
     <row r="352" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B352" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C352" s="257">
         <v>792.53</v>
@@ -21480,7 +21477,7 @@
     </row>
     <row r="355" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B355" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C355" s="257">
         <v>771.6</v>
@@ -21500,7 +21497,7 @@
     </row>
     <row r="356" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B356" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C356" s="257">
         <v>778.36</v>
@@ -21560,7 +21557,7 @@
     </row>
     <row r="359" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B359" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C359" s="257">
         <v>741.82</v>
@@ -21580,7 +21577,7 @@
     </row>
     <row r="360" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B360" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C360" s="257">
         <v>732.82</v>
@@ -21600,7 +21597,7 @@
     </row>
     <row r="361" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B361" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C361" s="257">
         <v>727.45</v>
@@ -21660,7 +21657,7 @@
     </row>
     <row r="364" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B364" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C364" s="257">
         <v>692.45</v>
@@ -21680,7 +21677,7 @@
     </row>
     <row r="365" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B365" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C365" s="257">
         <v>689.32</v>
@@ -21740,7 +21737,7 @@
     </row>
     <row r="368" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B368" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C368" s="257">
         <v>684.04</v>
@@ -21760,7 +21757,7 @@
     </row>
     <row r="369" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B369" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C369" s="257">
         <v>633.88</v>
@@ -21780,7 +21777,7 @@
     </row>
     <row r="370" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B370" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C370" s="257">
         <v>763.55</v>
@@ -21820,7 +21817,7 @@
     </row>
     <row r="372" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B372" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C372" s="257">
         <v>789</v>
@@ -21840,7 +21837,7 @@
     </row>
     <row r="373" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B373" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C373" s="257">
         <v>777.82</v>
@@ -21860,7 +21857,7 @@
     </row>
     <row r="374" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B374" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C374" s="257">
         <v>800.49</v>
@@ -21920,7 +21917,7 @@
     </row>
     <row r="377" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B377" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C377" s="257">
         <v>810.33</v>
@@ -21940,7 +21937,7 @@
     </row>
     <row r="378" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B378" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C378" s="257">
         <v>797.7</v>
@@ -22000,7 +21997,7 @@
     </row>
     <row r="381" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B381" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C381" s="257">
         <v>771.25</v>
@@ -22020,7 +22017,7 @@
     </row>
     <row r="382" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B382" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C382" s="257">
         <v>782.59</v>
@@ -22040,7 +22037,7 @@
     </row>
     <row r="383" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B383" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C383" s="257">
         <v>781</v>
@@ -22080,7 +22077,7 @@
     </row>
     <row r="385" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B385" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C385" s="257">
         <v>713.98</v>
@@ -22100,7 +22097,7 @@
     </row>
     <row r="386" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B386" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C386" s="257">
         <v>727.9</v>
@@ -22120,7 +22117,7 @@
     </row>
     <row r="387" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B387" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C387" s="257">
         <v>746</v>
@@ -22180,7 +22177,7 @@
     </row>
     <row r="390" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B390" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C390" s="257">
         <v>733.62</v>
@@ -22200,7 +22197,7 @@
     </row>
     <row r="391" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B391" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C391" s="257">
         <v>705.23</v>
@@ -22260,7 +22257,7 @@
     </row>
     <row r="394" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B394" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C394" s="257">
         <v>719.54</v>
@@ -22280,7 +22277,7 @@
     </row>
     <row r="395" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B395" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C395" s="257">
         <v>733.86</v>
@@ -22300,7 +22297,7 @@
     </row>
     <row r="396" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B396" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C396" s="257">
         <v>713.03</v>
@@ -22340,7 +22337,7 @@
     </row>
     <row r="398" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B398" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C398" s="257">
         <v>755.04</v>
@@ -22360,7 +22357,7 @@
     </row>
     <row r="399" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B399" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C399" s="257">
         <v>743.85</v>
@@ -22380,7 +22377,7 @@
     </row>
     <row r="400" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B400" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C400" s="257">
         <v>743.1</v>
@@ -22440,7 +22437,7 @@
     </row>
     <row r="403" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B403" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C403" s="257">
         <v>741.9</v>
@@ -22460,7 +22457,7 @@
     </row>
     <row r="404" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B404" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C404" s="257">
         <v>734.95</v>
@@ -22520,7 +22517,7 @@
     </row>
     <row r="407" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B407" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C407" s="257">
         <v>757.05</v>
@@ -22540,7 +22537,7 @@
     </row>
     <row r="408" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B408" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C408" s="257">
         <v>730.35</v>
@@ -22560,7 +22557,7 @@
     </row>
     <row r="409" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B409" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C409" s="257">
         <v>726.95</v>
@@ -22600,7 +22597,7 @@
     </row>
     <row r="411" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B411" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C411" s="257">
         <v>657.44</v>
@@ -22620,7 +22617,7 @@
     </row>
     <row r="412" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B412" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C412" s="257">
         <v>653.36</v>
@@ -22640,7 +22637,7 @@
     </row>
     <row r="413" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B413" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C413" s="257">
         <v>642.66999999999996</v>
@@ -22700,7 +22697,7 @@
     </row>
     <row r="416" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B416" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C416" s="257">
         <v>663.8</v>
@@ -22720,7 +22717,7 @@
     </row>
     <row r="417" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B417" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C417" s="257">
         <v>617.36</v>
@@ -22780,7 +22777,7 @@
     </row>
     <row r="420" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B420" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C420" s="257">
         <v>658.63</v>
@@ -22800,7 +22797,7 @@
     </row>
     <row r="421" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B421" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C421" s="257">
         <v>630.14</v>
@@ -22820,7 +22817,7 @@
     </row>
     <row r="422" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B422" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C422" s="257">
         <v>679.81</v>
@@ -22860,7 +22857,7 @@
     </row>
     <row r="424" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B424" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C424" s="257">
         <v>720.64</v>
@@ -22880,7 +22877,7 @@
     </row>
     <row r="425" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B425" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C425" s="257">
         <v>726.06</v>
@@ -22900,7 +22897,7 @@
     </row>
     <row r="426" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B426" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C426" s="257">
         <v>701.44</v>
@@ -22960,7 +22957,7 @@
     </row>
     <row r="429" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B429" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C429" s="257">
         <v>716.61</v>
@@ -22980,7 +22977,7 @@
     </row>
     <row r="430" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B430" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C430" s="257">
         <v>685.38</v>
@@ -23040,7 +23037,7 @@
     </row>
     <row r="433" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B433" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C433" s="257">
         <v>678.32</v>
@@ -23060,7 +23057,7 @@
     </row>
     <row r="434" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B434" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C434" s="257">
         <v>682.97</v>
@@ -23080,7 +23077,7 @@
     </row>
     <row r="435" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B435" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C435" s="257">
         <v>670.36</v>
@@ -23140,7 +23137,7 @@
     </row>
     <row r="438" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B438" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C438" s="257">
         <v>650.03</v>
@@ -23160,7 +23157,7 @@
     </row>
     <row r="439" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B439" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C439" s="257">
         <v>620.51</v>
@@ -23220,7 +23217,7 @@
     </row>
     <row r="442" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B442" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C442" s="257">
         <v>602.29999999999995</v>
@@ -23240,7 +23237,7 @@
     </row>
     <row r="443" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B443" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C443" s="257">
         <v>606</v>
@@ -23260,7 +23257,7 @@
     </row>
     <row r="444" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B444" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C444" s="257">
         <v>583.75</v>
@@ -23300,7 +23297,7 @@
     </row>
     <row r="446" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B446" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C446" s="257">
         <v>578.77</v>
@@ -23320,7 +23317,7 @@
     </row>
     <row r="447" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B447" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C447" s="257">
         <v>584.74</v>
@@ -23340,7 +23337,7 @@
     </row>
     <row r="448" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B448" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C448" s="257">
         <v>581.41</v>
@@ -23400,7 +23397,7 @@
     </row>
     <row r="451" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B451" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C451" s="257">
         <v>558.39</v>
@@ -23420,7 +23417,7 @@
     </row>
     <row r="452" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B452" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C452" s="257">
         <v>576.04999999999995</v>
@@ -23480,7 +23477,7 @@
     </row>
     <row r="455" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B455" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C455" s="257">
         <v>572.66999999999996</v>
@@ -23500,7 +23497,7 @@
     </row>
     <row r="456" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B456" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C456" s="257">
         <v>570.16</v>
@@ -23560,7 +23557,7 @@
     </row>
     <row r="459" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B459" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C459" s="257">
         <v>564.04</v>
@@ -23580,7 +23577,7 @@
     </row>
     <row r="460" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B460" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C460" s="257">
         <v>579.9</v>
@@ -23600,7 +23597,7 @@
     </row>
     <row r="461" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B461" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C461" s="257">
         <v>564.14</v>
@@ -23640,7 +23637,7 @@
     </row>
     <row r="463" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B463" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C463" s="257">
         <v>499.29</v>
@@ -23660,7 +23657,7 @@
     </row>
     <row r="464" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B464" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C464" s="257">
         <v>514.11</v>
@@ -23680,7 +23677,7 @@
     </row>
     <row r="465" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B465" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C465" s="257">
         <v>512.78</v>
@@ -23740,7 +23737,7 @@
     </row>
     <row r="468" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B468" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C468" s="257">
         <v>473.04</v>
@@ -23760,7 +23757,7 @@
     </row>
     <row r="469" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B469" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C469" s="257">
         <v>498.08</v>
@@ -23820,7 +23817,7 @@
     </row>
     <row r="472" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B472" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C472" s="257">
         <v>457.18</v>
@@ -23840,7 +23837,7 @@
     </row>
     <row r="473" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B473" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C473" s="257">
         <v>466.9</v>
@@ -23860,7 +23857,7 @@
     </row>
     <row r="474" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B474" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C474" s="257">
         <v>457.33</v>
@@ -23920,7 +23917,7 @@
     </row>
     <row r="477" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B477" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C477" s="257">
         <v>443.98</v>
@@ -23940,7 +23937,7 @@
     </row>
     <row r="478" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B478" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C478" s="257">
         <v>443.19</v>
@@ -24000,7 +23997,7 @@
     </row>
     <row r="481" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B481" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C481" s="257">
         <v>456.37</v>
@@ -24020,7 +24017,7 @@
     </row>
     <row r="482" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B482" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C482" s="257">
         <v>452.5</v>
@@ -24040,7 +24037,7 @@
     </row>
     <row r="483" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B483" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C483" s="257">
         <v>458</v>
@@ -24080,7 +24077,7 @@
     </row>
     <row r="485" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B485" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C485" s="257">
         <v>488.02</v>
@@ -24100,7 +24097,7 @@
     </row>
     <row r="486" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B486" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C486" s="257">
         <v>494.76</v>
@@ -24120,7 +24117,7 @@
     </row>
     <row r="487" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B487" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C487" s="257">
         <v>486.21</v>
@@ -24180,7 +24177,7 @@
     </row>
     <row r="490" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B490" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C490" s="257">
         <v>464.11</v>
@@ -24200,7 +24197,7 @@
     </row>
     <row r="491" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B491" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C491" s="257">
         <v>467.93</v>
@@ -24260,7 +24257,7 @@
     </row>
     <row r="494" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B494" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C494" s="257">
         <v>480.92</v>
@@ -24280,7 +24277,7 @@
     </row>
     <row r="495" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B495" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C495" s="257">
         <v>493.94</v>
@@ -24300,7 +24297,7 @@
     </row>
     <row r="496" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B496" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C496" s="257">
         <v>475.22</v>
@@ -24340,7 +24337,7 @@
     </row>
     <row r="498" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B498" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C498" s="257">
         <v>462.1</v>
@@ -24360,7 +24357,7 @@
     </row>
     <row r="499" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B499" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C499" s="257">
         <v>455.87</v>
@@ -24380,7 +24377,7 @@
     </row>
     <row r="500" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B500" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C500" s="257">
         <v>458.23</v>
@@ -24440,7 +24437,7 @@
     </row>
     <row r="503" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B503" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C503" s="257">
         <v>507.12</v>
@@ -24460,7 +24457,7 @@
     </row>
     <row r="504" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B504" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C504" s="257">
         <v>511.65</v>
@@ -24520,7 +24517,7 @@
     </row>
     <row r="507" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B507" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C507" s="257">
         <v>511.56</v>
@@ -24540,7 +24537,7 @@
     </row>
     <row r="508" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B508" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C508" s="257">
         <v>500.47</v>
@@ -24600,7 +24597,7 @@
     </row>
     <row r="511" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B511" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C511" s="257">
         <v>464.38</v>
@@ -24620,7 +24617,7 @@
     </row>
     <row r="512" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B512" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C512" s="257">
         <v>467.38</v>
@@ -24640,7 +24637,7 @@
     </row>
     <row r="513" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B513" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C513" s="257">
         <v>470.63</v>
@@ -24700,7 +24697,7 @@
     </row>
     <row r="516" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B516" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C516" s="257">
         <v>501.34</v>
@@ -24720,7 +24717,7 @@
     </row>
     <row r="517" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B517" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C517" s="257">
         <v>490.35</v>
@@ -24780,7 +24777,7 @@
     </row>
     <row r="520" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B520" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C520" s="257">
         <v>478.47</v>
@@ -24800,7 +24797,7 @@
     </row>
     <row r="521" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B521" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C521" s="257">
         <v>484.92</v>
@@ -24820,7 +24817,7 @@
     </row>
     <row r="522" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B522" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C522" s="257">
         <v>456.39</v>
@@ -24860,7 +24857,7 @@
     </row>
     <row r="524" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B524" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C524" s="257">
         <v>481.69</v>
@@ -24880,7 +24877,7 @@
     </row>
     <row r="525" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B525" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C525" s="257">
         <v>494.84</v>
@@ -28199,160 +28196,38 @@
       <c r="Q73" s="101"/>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B74" s="98" t="str">
-        <f>'Historical Financial Statement'!B79</f>
-        <v>Dividends received</v>
-      </c>
-      <c r="C74">
-        <f>'Historical Financial Statement'!C79</f>
-        <v>2753</v>
-      </c>
-      <c r="D74">
-        <f>'Historical Financial Statement'!D79</f>
-        <v>1768</v>
-      </c>
-      <c r="E74">
-        <f>'Historical Financial Statement'!E79</f>
-        <v>1557</v>
-      </c>
-      <c r="F74">
-        <f>'Historical Financial Statement'!F79</f>
-        <v>1929</v>
-      </c>
-      <c r="G74">
-        <f>'Historical Financial Statement'!G79</f>
-        <v>1418</v>
-      </c>
-      <c r="H74">
-        <f>'Historical Financial Statement'!H79</f>
-        <v>1898</v>
-      </c>
-      <c r="I74">
-        <f>'Historical Financial Statement'!I79</f>
-        <v>1525</v>
-      </c>
-      <c r="J74">
-        <f>'Historical Financial Statement'!J79</f>
-        <v>1768</v>
-      </c>
-      <c r="K74">
-        <f>'Historical Financial Statement'!K79</f>
-        <v>2040</v>
-      </c>
-      <c r="L74">
-        <f>'Historical Financial Statement'!L79</f>
-        <v>2713</v>
-      </c>
-      <c r="M74" s="91">
-        <f>M62*C76</f>
-        <v>3644.7534223506877</v>
-      </c>
-      <c r="N74" s="16">
-        <f t="shared" ref="N74:Q74" si="100">N62*D76</f>
-        <v>3637.811747189015</v>
-      </c>
-      <c r="O74" s="16">
-        <f t="shared" si="100"/>
-        <v>3828.6349872254914</v>
-      </c>
-      <c r="P74" s="16">
-        <f t="shared" si="100"/>
-        <v>4139.3737399547817</v>
-      </c>
-      <c r="Q74" s="106">
-        <f t="shared" si="100"/>
-        <v>4253.032424338322</v>
-      </c>
+      <c r="B74" s="98"/>
+      <c r="M74" s="91"/>
+      <c r="N74" s="16"/>
+      <c r="O74" s="16"/>
+      <c r="P74" s="16"/>
+      <c r="Q74" s="106"/>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B75" s="103" t="s">
-        <v>132</v>
-      </c>
-      <c r="C75" s="59">
-        <f>C74/C62</f>
-        <v>0.16763076173658892</v>
-      </c>
-      <c r="D75" s="59">
-        <f t="shared" ref="D75:Q75" si="101">D74/D62</f>
-        <v>0.1453588752774809</v>
-      </c>
-      <c r="E75" s="59">
-        <f t="shared" si="101"/>
-        <v>0.13826480774353966</v>
-      </c>
-      <c r="F75" s="59">
-        <f t="shared" si="101"/>
-        <v>0.21940400363967244</v>
-      </c>
-      <c r="G75" s="59">
-        <f t="shared" si="101"/>
-        <v>9.9824005631819784E-2</v>
-      </c>
-      <c r="H75" s="59">
-        <f t="shared" si="101"/>
-        <v>9.3387128518008261E-2</v>
-      </c>
-      <c r="I75" s="59">
-        <f t="shared" si="101"/>
-        <v>7.8293459287401168E-2</v>
-      </c>
-      <c r="J75" s="59">
-        <f t="shared" si="101"/>
-        <v>7.1802786013077199E-2</v>
-      </c>
-      <c r="K75" s="59">
-        <f t="shared" si="101"/>
-        <v>8.6657321269274876E-2</v>
-      </c>
-      <c r="L75" s="59">
-        <f t="shared" si="101"/>
-        <v>0.12399451553930531</v>
-      </c>
-      <c r="M75" s="96">
-        <f t="shared" si="101"/>
-        <v>0.12246176646561686</v>
-      </c>
-      <c r="N75" s="59">
-        <f t="shared" si="101"/>
-        <v>0.11794486693851966</v>
-      </c>
-      <c r="O75" s="59">
-        <f t="shared" si="101"/>
-        <v>0.11520346610462351</v>
-      </c>
-      <c r="P75" s="59">
-        <f t="shared" si="101"/>
-        <v>0.11289733194073191</v>
-      </c>
-      <c r="Q75" s="112">
-        <f t="shared" si="101"/>
-        <v>0.10224666477083784</v>
-      </c>
+      <c r="B75" s="103"/>
+      <c r="C75" s="59"/>
+      <c r="D75" s="59"/>
+      <c r="E75" s="59"/>
+      <c r="F75" s="59"/>
+      <c r="G75" s="59"/>
+      <c r="H75" s="59"/>
+      <c r="I75" s="59"/>
+      <c r="J75" s="59"/>
+      <c r="K75" s="59"/>
+      <c r="L75" s="59"/>
+      <c r="M75" s="96"/>
+      <c r="N75" s="59"/>
+      <c r="O75" s="59"/>
+      <c r="P75" s="59"/>
+      <c r="Q75" s="112"/>
     </row>
     <row r="76" spans="2:18" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B76" s="113" t="s">
-        <v>94</v>
-      </c>
-      <c r="C76" s="114">
-        <f>AVERAGE(C75:L75)</f>
-        <v>0.12246176646561686</v>
-      </c>
-      <c r="D76" s="114">
-        <f t="shared" ref="D76:G76" si="102">AVERAGE(D75:M75)</f>
-        <v>0.11794486693851966</v>
-      </c>
-      <c r="E76" s="114">
-        <f t="shared" si="102"/>
-        <v>0.11520346610462351</v>
-      </c>
-      <c r="F76" s="114">
-        <f t="shared" si="102"/>
-        <v>0.1128973319407319</v>
-      </c>
-      <c r="G76" s="114">
-        <f t="shared" si="102"/>
-        <v>0.10224666477083785</v>
-      </c>
+      <c r="B76" s="113"/>
+      <c r="C76" s="114"/>
+      <c r="D76" s="114"/>
+      <c r="E76" s="114"/>
+      <c r="F76" s="114"/>
+      <c r="G76" s="114"/>
       <c r="H76" s="114"/>
       <c r="I76" s="114"/>
       <c r="J76" s="114"/>
@@ -28513,7 +28388,7 @@
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B3" s="213" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C3" s="198">
         <v>469200</v>
@@ -28540,7 +28415,7 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B4" s="213" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C4" s="198">
         <v>8525</v>
@@ -28575,7 +28450,7 @@
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B5" s="213" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C5" s="199">
         <f>C3/SUM(C3:C4)</f>
@@ -28611,14 +28486,14 @@
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B6" s="213" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C6" s="199">
         <f>C4/(SUM(C3:C4))</f>
         <v>1.7844994505206969E-2</v>
       </c>
       <c r="F6" s="215" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G6" s="216">
         <f>-'Historical Financial Statement'!L75</f>
@@ -28647,14 +28522,14 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B7" s="213" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C7" s="200">
         <f>('Historical Financial Statement'!L17/'DCF Model'!C4)*(1-'DCF Model'!C9)</f>
         <v>3.5915073313782991E-2</v>
       </c>
       <c r="F7" s="219" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G7" s="216">
         <f>SUM('Historical Financial Statement'!L55:L56)-'Historical Financial Statement'!L39</f>
@@ -28683,14 +28558,14 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B8" s="213" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C8" s="200">
         <f>C10+C12*(C11-C10)</f>
         <v>0.10010161114159957</v>
       </c>
       <c r="F8" s="215" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H8" s="84">
         <f>H7-G7</f>
@@ -28721,7 +28596,7 @@
         <v>0.26400000000000001</v>
       </c>
       <c r="F9" s="220" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G9" s="221"/>
       <c r="H9" s="222">
@@ -28747,7 +28622,7 @@
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B10" s="213" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C10" s="202">
         <v>7.46E-2</v>
@@ -28755,14 +28630,14 @@
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B11" s="213" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C11" s="200">
         <f>_xlfn.RRI(10,'BETA Calculation'!F525,'BETA Calculation'!F4)</f>
         <v>0.11215961227220483</v>
       </c>
       <c r="F11" s="117" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="242">
@@ -28771,14 +28646,14 @@
     </row>
     <row r="12" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B12" s="214" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C12" s="203">
         <f>'BETA Calculation'!J8</f>
         <v>0.67896364203076398</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H12" s="223">
         <f>C14</f>
@@ -28787,7 +28662,7 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.45">
       <c r="F13" s="12" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H13" s="224">
         <f>(L9*(1+H11))/(H12-H11)</f>
@@ -28796,7 +28671,7 @@
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B14" s="196" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C14" s="197">
         <f>(C5*C8)+(C6*C7)</f>
@@ -28805,21 +28680,21 @@
     </row>
     <row r="15" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="F15" s="194" t="s">
+        <v>545</v>
+      </c>
+      <c r="G15" s="194" t="s">
+        <v>541</v>
+      </c>
+      <c r="H15" s="194" t="s">
+        <v>544</v>
+      </c>
+      <c r="I15" s="194" t="s">
         <v>546</v>
-      </c>
-      <c r="G15" s="194" t="s">
-        <v>542</v>
-      </c>
-      <c r="H15" s="194" t="s">
-        <v>545</v>
-      </c>
-      <c r="I15" s="194" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B16" s="207" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C16" s="204"/>
       <c r="D16" s="210"/>
@@ -28842,7 +28717,7 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B17" s="208" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C17" s="205"/>
       <c r="D17" s="211"/>
@@ -28865,7 +28740,7 @@
     </row>
     <row r="18" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="209" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C18" s="206"/>
       <c r="D18" s="212"/>
@@ -28940,7 +28815,7 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.45">
       <c r="F25" s="12" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G25" s="86">
         <f>I22</f>
@@ -28949,7 +28824,7 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.45">
       <c r="F26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G26" s="170">
         <f>'COMP Analysis'!F4</f>
@@ -28958,7 +28833,7 @@
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.45">
       <c r="F27" s="12" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G27" s="86">
         <f>G25-G26</f>
@@ -28967,7 +28842,7 @@
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.45">
       <c r="F28" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G28" s="84">
         <f>'Data Sheet'!K93</f>
@@ -28976,7 +28851,7 @@
     </row>
     <row r="29" spans="2:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="F29" s="259" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G29" s="260">
         <f>G27/G28</f>
@@ -28985,13 +28860,13 @@
     </row>
     <row r="31" spans="2:9" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="E31" s="238" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F31" s="239" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G31" s="238" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H31" s="237"/>
     </row>
@@ -29000,11 +28875,11 @@
     </row>
     <row r="33" spans="6:8" ht="23.25" x14ac:dyDescent="0.7">
       <c r="F33" s="240" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G33" s="241"/>
       <c r="H33" s="243" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="34" spans="6:8" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -29066,7 +28941,7 @@
     <row r="2" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B2" s="226"/>
       <c r="C2" s="273" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D2" s="273"/>
       <c r="E2" s="273"/>
@@ -29074,14 +28949,14 @@
       <c r="G2" s="273"/>
       <c r="H2" s="227"/>
       <c r="I2" s="274" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J2" s="274"/>
       <c r="K2" s="274"/>
       <c r="L2" s="274"/>
       <c r="M2" s="226"/>
       <c r="N2" s="274" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O2" s="274"/>
       <c r="P2" s="274"/>
@@ -29089,26 +28964,26 @@
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B3" s="226" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C3" s="228" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" s="228" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" s="228" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="228" t="s">
-        <v>198</v>
-      </c>
-      <c r="E3" s="228" t="s">
+      <c r="F3" s="228" t="s">
         <v>177</v>
       </c>
-      <c r="F3" s="228" t="s">
-        <v>178</v>
-      </c>
       <c r="G3" s="228" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H3" s="229"/>
       <c r="I3" s="228" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J3" s="228" t="s">
         <v>81</v>
@@ -29121,21 +28996,21 @@
       </c>
       <c r="M3" s="229"/>
       <c r="N3" s="228" t="s">
+        <v>179</v>
+      </c>
+      <c r="O3" s="228" t="s">
         <v>180</v>
       </c>
-      <c r="O3" s="228" t="s">
+      <c r="P3" s="228" t="s">
         <v>181</v>
       </c>
-      <c r="P3" s="228" t="s">
+      <c r="Q3" s="228" t="s">
         <v>182</v>
-      </c>
-      <c r="Q3" s="228" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B4" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C4" s="173">
         <v>1154</v>
@@ -29191,7 +29066,7 @@
     </row>
     <row r="5" spans="2:19" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B5" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C5" s="173">
         <v>2528</v>
@@ -29244,7 +29119,7 @@
     </row>
     <row r="6" spans="2:19" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C6" s="173">
         <v>1424</v>
@@ -29297,7 +29172,7 @@
     </row>
     <row r="7" spans="2:19" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C7" s="173">
         <v>190</v>
@@ -29351,7 +29226,7 @@
     </row>
     <row r="8" spans="2:19" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C8" s="173">
         <v>1789</v>
@@ -29405,7 +29280,7 @@
     <row r="9" spans="2:19" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="10" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B10" s="176" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C10" s="177"/>
       <c r="D10" s="177"/>
@@ -29437,7 +29312,7 @@
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B11" s="176" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C11" s="177"/>
       <c r="D11" s="177"/>
@@ -29469,7 +29344,7 @@
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B12" s="183" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C12" s="179"/>
       <c r="D12" s="179"/>
@@ -29501,7 +29376,7 @@
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B13" s="184" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C13" s="180"/>
       <c r="D13" s="180"/>
@@ -29533,7 +29408,7 @@
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B14" s="176" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C14" s="177"/>
       <c r="D14" s="177"/>
@@ -29565,7 +29440,7 @@
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B15" s="176" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C15" s="177"/>
       <c r="D15" s="177"/>
@@ -29604,7 +29479,7 @@
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.45">
       <c r="N17" s="274" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O17" s="274"/>
       <c r="P17" s="274"/>
@@ -29616,21 +29491,21 @@
         <v>INFOSYS LTD</v>
       </c>
       <c r="N18" s="228" t="s">
+        <v>179</v>
+      </c>
+      <c r="O18" s="228" t="s">
         <v>180</v>
       </c>
-      <c r="O18" s="228" t="s">
+      <c r="P18" s="228" t="s">
         <v>181</v>
       </c>
-      <c r="P18" s="228" t="s">
+      <c r="Q18" s="228" t="s">
         <v>182</v>
-      </c>
-      <c r="Q18" s="228" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="19" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N19" s="172">
         <f>N13*I4</f>
@@ -29651,7 +29526,7 @@
     </row>
     <row r="20" spans="2:17" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N20" s="170">
         <f>$F4</f>
@@ -29672,7 +29547,7 @@
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N21" s="170">
         <f>N19-N20</f>
@@ -29693,7 +29568,7 @@
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N22" s="170">
         <f>$D4</f>
@@ -29714,7 +29589,7 @@
     </row>
     <row r="23" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B23" s="187" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C23" s="187"/>
       <c r="D23" s="187"/>
@@ -29747,13 +29622,13 @@
     <row r="24" spans="2:17" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="25" spans="2:17" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="E25" s="238" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F25" s="239" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G25" s="238" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="26" spans="2:17" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -29761,15 +29636,15 @@
     </row>
     <row r="27" spans="2:17" ht="23.25" x14ac:dyDescent="0.7">
       <c r="E27" s="240" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F27" s="241"/>
       <c r="G27" s="241"/>
       <c r="H27" s="243" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
